--- a/qs.xlsx
+++ b/qs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OmarServer\OneDrive - Questindustries\Desktop\CIA 2026\CIA part 2\TP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cyn20598134-my.sharepoint.com/personal/cx2691_msdn365_net/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36BC63BE-84FA-4E99-9A4C-54200D0A93C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{36BC63BE-84FA-4E99-9A4C-54200D0A93C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9D7177F-55D4-4A4C-B585-ED5B5D9B4FF6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="1190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="1197">
   <si>
     <t>Form</t>
   </si>
@@ -3603,6 +3603,27 @@
   </si>
   <si>
     <t>Old number</t>
+  </si>
+  <si>
+    <t>د- تنفيذ</t>
+  </si>
+  <si>
+    <t>أ- مهام التدقيق</t>
+  </si>
+  <si>
+    <t>ج- تخطيط</t>
+  </si>
+  <si>
+    <t>هـ- الابلاغ</t>
+  </si>
+  <si>
+    <t>ب- تنسيق</t>
+  </si>
+  <si>
+    <t>الدرس</t>
+  </si>
+  <si>
+    <t>الدرس المعدل</t>
   </si>
 </sst>
 </file>
@@ -3763,55 +3784,54 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3820,6 +3840,16 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{CF73B589-3A71-41BD-93A9-80867E296F12}"/>
   </cellStyles>
   <dxfs count="17">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -3837,30 +3867,6 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -3944,6 +3950,13 @@
       </fill>
     </dxf>
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFD1D5DB"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -3959,21 +3972,28 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FFD1D5DB"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3989,23 +4009,34 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E5854F4D-195B-480B-8DEF-6E512026576C}" name="Table1" displayName="Table1" ref="A1:L209" totalsRowShown="0" headerRowDxfId="2" dataDxfId="5" headerRowBorderDxfId="14" tableBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E5854F4D-195B-480B-8DEF-6E512026576C}" name="Table1" displayName="Table1" ref="A1:L209" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13">
   <autoFilter ref="A1:L209" xr:uid="{E5854F4D-195B-480B-8DEF-6E512026576C}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{2051CF24-7DAC-4F6B-8197-05C7C1C70668}" name="Form" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{B11E43A6-8751-426D-BDCA-8D231219A4E3}" name="Form Title" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{993C43D2-F1BE-48FF-8757-29410E0DCE1D}" name="Question No." dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{79DA49F4-33C7-4D56-992B-9DA561BF07AA}" name="Lesson" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{BC0C681B-9283-4418-9C39-700FC8BC49CF}" name="Question" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{C4A61FD1-6D11-43A8-9F8D-7F6A2A51629D}" name="Option A" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{7EB9F918-F521-4393-A511-DE1B851F24F7}" name="Option B" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{23795A09-2AF7-4E3B-A609-6CC4FEBADA69}" name="Option C" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{2051CF24-7DAC-4F6B-8197-05C7C1C70668}" name="Form" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{B11E43A6-8751-426D-BDCA-8D231219A4E3}" name="Form Title" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{993C43D2-F1BE-48FF-8757-29410E0DCE1D}" name="Question No." dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{79DA49F4-33C7-4D56-992B-9DA561BF07AA}" name="Lesson" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{BC0C681B-9283-4418-9C39-700FC8BC49CF}" name="Question" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{C4A61FD1-6D11-43A8-9F8D-7F6A2A51629D}" name="Option A" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{7EB9F918-F521-4393-A511-DE1B851F24F7}" name="Option B" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{23795A09-2AF7-4E3B-A609-6CC4FEBADA69}" name="Option C" dataDxfId="5"/>
     <tableColumn id="9" xr3:uid="{EFC7D106-5258-4441-A928-4E24345249E3}" name="Option D" dataDxfId="4"/>
     <tableColumn id="10" xr3:uid="{492489E1-BCF7-425C-8262-A39D6CA4941B}" name="Correct Answer" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{30CB9AAF-31B8-499E-9CED-39A18CB68145}" name="Modifications / Corrections" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{9D99E0A3-0063-4DC7-9F73-D46FD9EFBCA6}" name="Old number" dataDxfId="0"/>
+    <tableColumn id="11" xr3:uid="{30CB9AAF-31B8-499E-9CED-39A18CB68145}" name="Modifications / Corrections" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{9D99E0A3-0063-4DC7-9F73-D46FD9EFBCA6}" name="Old number" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{671F747F-6BC6-4B9D-8A33-28F5FE4FB658}" name="Table2" displayName="Table2" ref="V1:W6" totalsRowShown="0">
+  <autoFilter ref="V1:W6" xr:uid="{671F747F-6BC6-4B9D-8A33-28F5FE4FB658}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{FE33DDC7-9BE6-41E8-B315-808671B91541}" name="الدرس"/>
+    <tableColumn id="2" xr3:uid="{AD85DE3E-7EC6-49E6-AD6B-B43FB1454326}" name="الدرس المعدل"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -4158,7 +4189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L209"/>
+  <dimension ref="A1:W209"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4169,47 +4200,55 @@
     <col min="6" max="9" width="44" customWidth="1"/>
     <col min="10" max="10" width="13.875" customWidth="1"/>
     <col min="11" max="11" width="48" customWidth="1"/>
+    <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:23" ht="30">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="15" t="s">
         <v>1189</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="42.75">
+      <c r="V1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="W1" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>1187</v>
       </c>
@@ -4220,7 +4259,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>12</v>
@@ -4243,11 +4282,17 @@
       <c r="K2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="14">
+      <c r="L2" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="42.75">
+      <c r="V2" t="s">
+        <v>11</v>
+      </c>
+      <c r="W2" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="42.75">
       <c r="A3" s="5" t="s">
         <v>1187</v>
       </c>
@@ -4258,7 +4303,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>19</v>
+        <v>1191</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>20</v>
@@ -4281,11 +4326,17 @@
       <c r="K3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="13">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="42.75">
+      <c r="V3" t="s">
+        <v>19</v>
+      </c>
+      <c r="W3" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="42.75">
       <c r="A4" s="5" t="s">
         <v>1187</v>
       </c>
@@ -4296,7 +4347,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>27</v>
@@ -4319,11 +4370,17 @@
       <c r="K4" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="13">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="42.75">
+      <c r="V4" t="s">
+        <v>26</v>
+      </c>
+      <c r="W4" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="42.75">
       <c r="A5" s="5" t="s">
         <v>1187</v>
       </c>
@@ -4334,7 +4391,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>34</v>
@@ -4357,11 +4414,17 @@
       <c r="K5" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="13">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="28.5">
+      <c r="V5" t="s">
+        <v>52</v>
+      </c>
+      <c r="W5" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="28.5">
       <c r="A6" s="5" t="s">
         <v>1187</v>
       </c>
@@ -4372,7 +4435,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>40</v>
@@ -4395,11 +4458,17 @@
       <c r="K6" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="L6" s="14">
+      <c r="L6" s="13">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="42.75">
+      <c r="V6" t="s">
+        <v>65</v>
+      </c>
+      <c r="W6" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="42.75">
       <c r="A7" s="5" t="s">
         <v>1187</v>
       </c>
@@ -4410,7 +4479,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>46</v>
@@ -4433,11 +4502,11 @@
       <c r="K7" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="13">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="28.5">
+    <row r="8" spans="1:23" ht="28.5">
       <c r="A8" s="5" t="s">
         <v>1187</v>
       </c>
@@ -4448,7 +4517,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>52</v>
+        <v>1193</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>53</v>
@@ -4471,11 +4540,11 @@
       <c r="K8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="13">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="42.75">
+    <row r="9" spans="1:23" ht="42.75">
       <c r="A9" s="5" t="s">
         <v>1187</v>
       </c>
@@ -4486,7 +4555,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>59</v>
@@ -4509,11 +4578,11 @@
       <c r="K9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="L9" s="14">
+      <c r="L9" s="13">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="28.5">
+    <row r="10" spans="1:23" ht="28.5">
       <c r="A10" s="5" t="s">
         <v>1187</v>
       </c>
@@ -4524,7 +4593,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>65</v>
+        <v>1194</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>66</v>
@@ -4547,11 +4616,11 @@
       <c r="K10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L10" s="14">
+      <c r="L10" s="13">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="57">
+    <row r="11" spans="1:23" ht="57">
       <c r="A11" s="5" t="s">
         <v>1187</v>
       </c>
@@ -4562,7 +4631,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>71</v>
@@ -4585,11 +4654,11 @@
       <c r="K11" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="L11" s="14">
+      <c r="L11" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="42.75">
+    <row r="12" spans="1:23" ht="42.75">
       <c r="A12" s="5" t="s">
         <v>1187</v>
       </c>
@@ -4600,7 +4669,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>77</v>
@@ -4623,11 +4692,11 @@
       <c r="K12" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="L12" s="14">
+      <c r="L12" s="13">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="28.5">
+    <row r="13" spans="1:23" ht="28.5">
       <c r="A13" s="5" t="s">
         <v>1187</v>
       </c>
@@ -4638,7 +4707,7 @@
         <v>12</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>19</v>
+        <v>1191</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>83</v>
@@ -4661,11 +4730,11 @@
       <c r="K13" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="L13" s="14">
+      <c r="L13" s="13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="28.5">
+    <row r="14" spans="1:23" ht="28.5">
       <c r="A14" s="5" t="s">
         <v>1187</v>
       </c>
@@ -4676,7 +4745,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>89</v>
@@ -4699,11 +4768,11 @@
       <c r="K14" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L14" s="14">
+      <c r="L14" s="13">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="42.75">
+    <row r="15" spans="1:23" ht="42.75">
       <c r="A15" s="5" t="s">
         <v>1187</v>
       </c>
@@ -4714,7 +4783,7 @@
         <v>14</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>94</v>
@@ -4737,11 +4806,11 @@
       <c r="K15" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="L15" s="14">
+      <c r="L15" s="13">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="42.75">
+    <row r="16" spans="1:23" ht="42.75">
       <c r="A16" s="5" t="s">
         <v>1187</v>
       </c>
@@ -4752,7 +4821,7 @@
         <v>15</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>100</v>
@@ -4775,7 +4844,7 @@
       <c r="K16" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L16" s="14">
+      <c r="L16" s="13">
         <v>15</v>
       </c>
     </row>
@@ -4790,7 +4859,7 @@
         <v>16</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>105</v>
@@ -4813,7 +4882,7 @@
       <c r="K17" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L17" s="14">
+      <c r="L17" s="13">
         <v>16</v>
       </c>
     </row>
@@ -4828,7 +4897,7 @@
         <v>17</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>110</v>
@@ -4851,7 +4920,7 @@
       <c r="K18" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="L18" s="14">
+      <c r="L18" s="13">
         <v>17</v>
       </c>
     </row>
@@ -4866,7 +4935,7 @@
         <v>18</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>19</v>
+        <v>1191</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>116</v>
@@ -4889,7 +4958,7 @@
       <c r="K19" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="L19" s="14">
+      <c r="L19" s="13">
         <v>18</v>
       </c>
     </row>
@@ -4904,7 +4973,7 @@
         <v>19</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>52</v>
+        <v>1193</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>122</v>
@@ -4927,7 +4996,7 @@
       <c r="K20" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L20" s="14">
+      <c r="L20" s="13">
         <v>19</v>
       </c>
     </row>
@@ -4942,7 +5011,7 @@
         <v>20</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>127</v>
@@ -4965,7 +5034,7 @@
       <c r="K21" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="L21" s="14">
+      <c r="L21" s="13">
         <v>20</v>
       </c>
     </row>
@@ -4980,7 +5049,7 @@
         <v>21</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>133</v>
@@ -5003,7 +5072,7 @@
       <c r="K22" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="L22" s="14">
+      <c r="L22" s="13">
         <v>21</v>
       </c>
     </row>
@@ -5018,7 +5087,7 @@
         <v>22</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>138</v>
@@ -5041,7 +5110,7 @@
       <c r="K23" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L23" s="14">
+      <c r="L23" s="13">
         <v>22</v>
       </c>
     </row>
@@ -5056,7 +5125,7 @@
         <v>23</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>143</v>
@@ -5079,7 +5148,7 @@
       <c r="K24" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="L24" s="14">
+      <c r="L24" s="13">
         <v>23</v>
       </c>
     </row>
@@ -5094,7 +5163,7 @@
         <v>24</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>149</v>
@@ -5117,7 +5186,7 @@
       <c r="K25" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="L25" s="14">
+      <c r="L25" s="13">
         <v>24</v>
       </c>
     </row>
@@ -5132,7 +5201,7 @@
         <v>25</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>154</v>
@@ -5155,7 +5224,7 @@
       <c r="K26" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="L26" s="14">
+      <c r="L26" s="13">
         <v>25</v>
       </c>
     </row>
@@ -5170,7 +5239,7 @@
         <v>26</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>160</v>
@@ -5193,7 +5262,7 @@
       <c r="K27" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L27" s="14">
+      <c r="L27" s="13">
         <v>26</v>
       </c>
     </row>
@@ -5208,7 +5277,7 @@
         <v>27</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>19</v>
+        <v>1191</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>165</v>
@@ -5231,7 +5300,7 @@
       <c r="K28" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="L28" s="14">
+      <c r="L28" s="13">
         <v>27</v>
       </c>
     </row>
@@ -5246,7 +5315,7 @@
         <v>28</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>171</v>
@@ -5269,7 +5338,7 @@
       <c r="K29" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L29" s="14">
+      <c r="L29" s="13">
         <v>28</v>
       </c>
     </row>
@@ -5284,7 +5353,7 @@
         <v>29</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>176</v>
@@ -5307,7 +5376,7 @@
       <c r="K30" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="14">
+      <c r="L30" s="13">
         <v>29</v>
       </c>
     </row>
@@ -5322,7 +5391,7 @@
         <v>30</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>181</v>
@@ -5345,7 +5414,7 @@
       <c r="K31" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="L31" s="14">
+      <c r="L31" s="13">
         <v>30</v>
       </c>
     </row>
@@ -5360,7 +5429,7 @@
         <v>31</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>187</v>
@@ -5383,7 +5452,7 @@
       <c r="K32" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L32" s="14">
+      <c r="L32" s="13">
         <v>31</v>
       </c>
     </row>
@@ -5398,7 +5467,7 @@
         <v>32</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>192</v>
@@ -5421,7 +5490,7 @@
       <c r="K33" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="L33" s="14">
+      <c r="L33" s="13">
         <v>32</v>
       </c>
     </row>
@@ -5436,7 +5505,7 @@
         <v>33</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>19</v>
+        <v>1191</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>197</v>
@@ -5459,7 +5528,7 @@
       <c r="K34" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="L34" s="14">
+      <c r="L34" s="13">
         <v>33</v>
       </c>
     </row>
@@ -5474,7 +5543,7 @@
         <v>34</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>202</v>
@@ -5497,7 +5566,7 @@
       <c r="K35" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L35" s="14">
+      <c r="L35" s="13">
         <v>34</v>
       </c>
     </row>
@@ -5512,7 +5581,7 @@
         <v>35</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>207</v>
@@ -5535,7 +5604,7 @@
       <c r="K36" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="L36" s="14">
+      <c r="L36" s="13">
         <v>35</v>
       </c>
     </row>
@@ -5550,7 +5619,7 @@
         <v>36</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>65</v>
+        <v>1194</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>213</v>
@@ -5573,7 +5642,7 @@
       <c r="K37" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="L37" s="14">
+      <c r="L37" s="13">
         <v>36</v>
       </c>
     </row>
@@ -5588,7 +5657,7 @@
         <v>37</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>52</v>
+        <v>1193</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>218</v>
@@ -5611,7 +5680,7 @@
       <c r="K38" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="L38" s="14">
+      <c r="L38" s="13">
         <v>37</v>
       </c>
     </row>
@@ -5626,7 +5695,7 @@
         <v>38</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>224</v>
@@ -5649,7 +5718,7 @@
       <c r="K39" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="13">
         <v>38</v>
       </c>
     </row>
@@ -5664,7 +5733,7 @@
         <v>39</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>230</v>
@@ -5687,7 +5756,7 @@
       <c r="K40" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="13">
         <v>39</v>
       </c>
     </row>
@@ -5702,7 +5771,7 @@
         <v>40</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>52</v>
+        <v>1193</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>236</v>
@@ -5725,7 +5794,7 @@
       <c r="K41" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="13">
         <v>40</v>
       </c>
     </row>
@@ -5740,7 +5809,7 @@
         <v>41</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>241</v>
@@ -5763,7 +5832,7 @@
       <c r="K42" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="13">
         <v>41</v>
       </c>
     </row>
@@ -5778,7 +5847,7 @@
         <v>42</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>246</v>
@@ -5801,7 +5870,7 @@
       <c r="K43" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="13">
         <v>42</v>
       </c>
     </row>
@@ -5816,7 +5885,7 @@
         <v>43</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>251</v>
@@ -5839,7 +5908,7 @@
       <c r="K44" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="13">
         <v>43</v>
       </c>
     </row>
@@ -5854,7 +5923,7 @@
         <v>44</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>19</v>
+        <v>1191</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>256</v>
@@ -5877,7 +5946,7 @@
       <c r="K45" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="13">
         <v>44</v>
       </c>
     </row>
@@ -5892,7 +5961,7 @@
         <v>45</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>19</v>
+        <v>1191</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>261</v>
@@ -5915,7 +5984,7 @@
       <c r="K46" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L46" s="14">
+      <c r="L46" s="13">
         <v>45</v>
       </c>
     </row>
@@ -5930,7 +5999,7 @@
         <v>46</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>266</v>
@@ -5953,7 +6022,7 @@
       <c r="K47" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="L47" s="14">
+      <c r="L47" s="13">
         <v>46</v>
       </c>
     </row>
@@ -5968,7 +6037,7 @@
         <v>47</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>272</v>
@@ -5991,7 +6060,7 @@
       <c r="K48" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="L48" s="14">
+      <c r="L48" s="13">
         <v>47</v>
       </c>
     </row>
@@ -6006,7 +6075,7 @@
         <v>48</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>277</v>
@@ -6029,7 +6098,7 @@
       <c r="K49" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L49" s="14">
+      <c r="L49" s="13">
         <v>48</v>
       </c>
     </row>
@@ -6044,7 +6113,7 @@
         <v>49</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>282</v>
@@ -6067,7 +6136,7 @@
       <c r="K50" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="L50" s="14">
+      <c r="L50" s="13">
         <v>49</v>
       </c>
     </row>
@@ -6082,7 +6151,7 @@
         <v>50</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>288</v>
@@ -6105,7 +6174,7 @@
       <c r="K51" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="L51" s="14">
+      <c r="L51" s="13">
         <v>50</v>
       </c>
     </row>
@@ -6120,7 +6189,7 @@
         <v>51</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>294</v>
@@ -6143,7 +6212,7 @@
       <c r="K52" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="L52" s="14">
+      <c r="L52" s="13">
         <v>51</v>
       </c>
     </row>
@@ -6158,7 +6227,7 @@
         <v>52</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>299</v>
@@ -6181,7 +6250,7 @@
       <c r="K53" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="L53" s="14">
+      <c r="L53" s="13">
         <v>52</v>
       </c>
     </row>
@@ -6196,7 +6265,7 @@
         <v>53</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>52</v>
+        <v>1193</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>304</v>
@@ -6219,7 +6288,7 @@
       <c r="K54" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="L54" s="14">
+      <c r="L54" s="13">
         <v>53</v>
       </c>
     </row>
@@ -6234,7 +6303,7 @@
         <v>54</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>308</v>
@@ -6257,7 +6326,7 @@
       <c r="K55" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L55" s="14">
+      <c r="L55" s="13">
         <v>54</v>
       </c>
     </row>
@@ -6272,7 +6341,7 @@
         <v>55</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>19</v>
+        <v>1191</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>313</v>
@@ -6295,7 +6364,7 @@
       <c r="K56" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="L56" s="14">
+      <c r="L56" s="13">
         <v>55</v>
       </c>
     </row>
@@ -6310,7 +6379,7 @@
         <v>56</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>19</v>
+        <v>1194</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>319</v>
@@ -6333,7 +6402,7 @@
       <c r="K57" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="L57" s="14">
+      <c r="L57" s="13">
         <v>56</v>
       </c>
     </row>
@@ -6348,7 +6417,7 @@
         <v>57</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>325</v>
@@ -6371,7 +6440,7 @@
       <c r="K58" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="L58" s="14">
+      <c r="L58" s="13">
         <v>57</v>
       </c>
     </row>
@@ -6386,7 +6455,7 @@
         <v>58</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>65</v>
+        <v>1194</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>331</v>
@@ -6409,7 +6478,7 @@
       <c r="K59" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="L59" s="14">
+      <c r="L59" s="13">
         <v>58</v>
       </c>
     </row>
@@ -6424,7 +6493,7 @@
         <v>59</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>337</v>
@@ -6447,7 +6516,7 @@
       <c r="K60" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="L60" s="14">
+      <c r="L60" s="13">
         <v>59</v>
       </c>
     </row>
@@ -6462,7 +6531,7 @@
         <v>60</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>343</v>
@@ -6485,7 +6554,7 @@
       <c r="K61" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="L61" s="14">
+      <c r="L61" s="13">
         <v>60</v>
       </c>
     </row>
@@ -6500,7 +6569,7 @@
         <v>61</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>349</v>
@@ -6523,7 +6592,7 @@
       <c r="K62" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="L62" s="14">
+      <c r="L62" s="13">
         <v>61</v>
       </c>
     </row>
@@ -6538,7 +6607,7 @@
         <v>62</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>355</v>
@@ -6561,7 +6630,7 @@
       <c r="K63" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="L63" s="14">
+      <c r="L63" s="13">
         <v>62</v>
       </c>
     </row>
@@ -6576,7 +6645,7 @@
         <v>63</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>361</v>
@@ -6599,7 +6668,7 @@
       <c r="K64" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="L64" s="14">
+      <c r="L64" s="13">
         <v>63</v>
       </c>
     </row>
@@ -6614,7 +6683,7 @@
         <v>64</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>52</v>
+        <v>1193</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>364</v>
@@ -6637,7 +6706,7 @@
       <c r="K65" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="L65" s="14">
+      <c r="L65" s="13">
         <v>64</v>
       </c>
     </row>
@@ -6652,7 +6721,7 @@
         <v>65</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>370</v>
@@ -6675,7 +6744,7 @@
       <c r="K66" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="L66" s="14">
+      <c r="L66" s="13">
         <v>65</v>
       </c>
     </row>
@@ -6690,7 +6759,7 @@
         <v>66</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>376</v>
@@ -6713,7 +6782,7 @@
       <c r="K67" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="L67" s="14">
+      <c r="L67" s="13">
         <v>66</v>
       </c>
     </row>
@@ -6728,7 +6797,7 @@
         <v>67</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>382</v>
@@ -6751,7 +6820,7 @@
       <c r="K68" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="L68" s="14">
+      <c r="L68" s="13">
         <v>67</v>
       </c>
     </row>
@@ -6766,7 +6835,7 @@
         <v>68</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>52</v>
+        <v>1193</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>388</v>
@@ -6789,7 +6858,7 @@
       <c r="K69" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="L69" s="14">
+      <c r="L69" s="13">
         <v>68</v>
       </c>
     </row>
@@ -6804,7 +6873,7 @@
         <v>69</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>394</v>
@@ -6827,7 +6896,7 @@
       <c r="K70" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="L70" s="14">
+      <c r="L70" s="13">
         <v>69</v>
       </c>
     </row>
@@ -6842,7 +6911,7 @@
         <v>70</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>65</v>
+        <v>1194</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>400</v>
@@ -6865,7 +6934,7 @@
       <c r="K71" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="L71" s="14">
+      <c r="L71" s="13">
         <v>70</v>
       </c>
     </row>
@@ -6880,7 +6949,7 @@
         <v>71</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>406</v>
@@ -6903,7 +6972,7 @@
       <c r="K72" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="L72" s="14">
+      <c r="L72" s="13">
         <v>71</v>
       </c>
     </row>
@@ -6918,7 +6987,7 @@
         <v>72</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>19</v>
+        <v>1191</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>412</v>
@@ -6941,7 +7010,7 @@
       <c r="K73" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="L73" s="14">
+      <c r="L73" s="13">
         <v>72</v>
       </c>
     </row>
@@ -6956,7 +7025,7 @@
         <v>73</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>418</v>
@@ -6979,7 +7048,7 @@
       <c r="K74" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="L74" s="14">
+      <c r="L74" s="13">
         <v>73</v>
       </c>
     </row>
@@ -6994,7 +7063,7 @@
         <v>74</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>65</v>
+        <v>1194</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>424</v>
@@ -7017,7 +7086,7 @@
       <c r="K75" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="L75" s="14">
+      <c r="L75" s="13">
         <v>74</v>
       </c>
     </row>
@@ -7032,7 +7101,7 @@
         <v>75</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>52</v>
+        <v>1193</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>430</v>
@@ -7055,7 +7124,7 @@
       <c r="K76" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="L76" s="14">
+      <c r="L76" s="13">
         <v>75</v>
       </c>
     </row>
@@ -7070,7 +7139,7 @@
         <v>76</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E77" s="7" t="s">
         <v>436</v>
@@ -7093,7 +7162,7 @@
       <c r="K77" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="L77" s="14">
+      <c r="L77" s="13">
         <v>76</v>
       </c>
     </row>
@@ -7108,7 +7177,7 @@
         <v>77</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>52</v>
+        <v>1193</v>
       </c>
       <c r="E78" s="7" t="s">
         <v>442</v>
@@ -7131,7 +7200,7 @@
       <c r="K78" s="8" t="s">
         <v>447</v>
       </c>
-      <c r="L78" s="14">
+      <c r="L78" s="13">
         <v>77</v>
       </c>
     </row>
@@ -7146,7 +7215,7 @@
         <v>78</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>52</v>
+        <v>1193</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>448</v>
@@ -7169,7 +7238,7 @@
       <c r="K79" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="L79" s="14">
+      <c r="L79" s="13">
         <v>78</v>
       </c>
     </row>
@@ -7184,7 +7253,7 @@
         <v>79</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E80" s="7" t="s">
         <v>453</v>
@@ -7207,7 +7276,7 @@
       <c r="K80" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="L80" s="14">
+      <c r="L80" s="13">
         <v>79</v>
       </c>
     </row>
@@ -7222,7 +7291,7 @@
         <v>80</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>52</v>
+        <v>1193</v>
       </c>
       <c r="E81" s="7" t="s">
         <v>458</v>
@@ -7245,7 +7314,7 @@
       <c r="K81" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="L81" s="14">
+      <c r="L81" s="13">
         <v>80</v>
       </c>
     </row>
@@ -7260,7 +7329,7 @@
         <v>81</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E82" s="7" t="s">
         <v>463</v>
@@ -7283,7 +7352,7 @@
       <c r="K82" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="L82" s="14">
+      <c r="L82" s="13">
         <v>81</v>
       </c>
     </row>
@@ -7298,7 +7367,7 @@
         <v>82</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E83" s="7" t="s">
         <v>469</v>
@@ -7321,7 +7390,7 @@
       <c r="K83" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L83" s="14">
+      <c r="L83" s="13">
         <v>82</v>
       </c>
     </row>
@@ -7336,7 +7405,7 @@
         <v>83</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E84" s="7" t="s">
         <v>474</v>
@@ -7359,7 +7428,7 @@
       <c r="K84" s="8" t="s">
         <v>479</v>
       </c>
-      <c r="L84" s="14">
+      <c r="L84" s="13">
         <v>83</v>
       </c>
     </row>
@@ -7374,7 +7443,7 @@
         <v>84</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E85" s="7" t="s">
         <v>480</v>
@@ -7397,7 +7466,7 @@
       <c r="K85" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="L85" s="14">
+      <c r="L85" s="13">
         <v>84</v>
       </c>
     </row>
@@ -7412,7 +7481,7 @@
         <v>85</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>65</v>
+        <v>1194</v>
       </c>
       <c r="E86" s="7" t="s">
         <v>485</v>
@@ -7435,7 +7504,7 @@
       <c r="K86" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="L86" s="14">
+      <c r="L86" s="13">
         <v>85</v>
       </c>
     </row>
@@ -7450,7 +7519,7 @@
         <v>86</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>490</v>
@@ -7473,7 +7542,7 @@
       <c r="K87" s="8" t="s">
         <v>495</v>
       </c>
-      <c r="L87" s="14">
+      <c r="L87" s="13">
         <v>86</v>
       </c>
     </row>
@@ -7488,7 +7557,7 @@
         <v>87</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>52</v>
+        <v>1193</v>
       </c>
       <c r="E88" s="7" t="s">
         <v>496</v>
@@ -7511,7 +7580,7 @@
       <c r="K88" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="L88" s="14">
+      <c r="L88" s="13">
         <v>87</v>
       </c>
     </row>
@@ -7526,7 +7595,7 @@
         <v>88</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E89" s="7" t="s">
         <v>501</v>
@@ -7549,7 +7618,7 @@
       <c r="K89" s="8" t="s">
         <v>504</v>
       </c>
-      <c r="L89" s="14">
+      <c r="L89" s="13">
         <v>88</v>
       </c>
     </row>
@@ -7564,7 +7633,7 @@
         <v>89</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>52</v>
+        <v>1193</v>
       </c>
       <c r="E90" s="7" t="s">
         <v>505</v>
@@ -7587,7 +7656,7 @@
       <c r="K90" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="L90" s="14">
+      <c r="L90" s="13">
         <v>89</v>
       </c>
     </row>
@@ -7602,7 +7671,7 @@
         <v>90</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E91" s="7" t="s">
         <v>510</v>
@@ -7625,7 +7694,7 @@
       <c r="K91" s="8" t="s">
         <v>515</v>
       </c>
-      <c r="L91" s="14">
+      <c r="L91" s="13">
         <v>90</v>
       </c>
     </row>
@@ -7640,7 +7709,7 @@
         <v>91</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E92" s="7" t="s">
         <v>516</v>
@@ -7663,7 +7732,7 @@
       <c r="K92" s="8" t="s">
         <v>521</v>
       </c>
-      <c r="L92" s="14">
+      <c r="L92" s="13">
         <v>91</v>
       </c>
     </row>
@@ -7678,7 +7747,7 @@
         <v>92</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E93" s="7" t="s">
         <v>522</v>
@@ -7701,7 +7770,7 @@
       <c r="K93" s="8" t="s">
         <v>527</v>
       </c>
-      <c r="L93" s="14">
+      <c r="L93" s="13">
         <v>92</v>
       </c>
     </row>
@@ -7716,7 +7785,7 @@
         <v>93</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E94" s="7" t="s">
         <v>528</v>
@@ -7739,7 +7808,7 @@
       <c r="K94" s="8" t="s">
         <v>533</v>
       </c>
-      <c r="L94" s="14">
+      <c r="L94" s="13">
         <v>93</v>
       </c>
     </row>
@@ -7754,7 +7823,7 @@
         <v>94</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E95" s="7" t="s">
         <v>534</v>
@@ -7777,7 +7846,7 @@
       <c r="K95" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="L95" s="14">
+      <c r="L95" s="13">
         <v>94</v>
       </c>
     </row>
@@ -7792,7 +7861,7 @@
         <v>95</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>52</v>
+        <v>1193</v>
       </c>
       <c r="E96" s="7" t="s">
         <v>539</v>
@@ -7815,7 +7884,7 @@
       <c r="K96" s="8" t="s">
         <v>544</v>
       </c>
-      <c r="L96" s="14">
+      <c r="L96" s="13">
         <v>95</v>
       </c>
     </row>
@@ -7830,7 +7899,7 @@
         <v>96</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E97" s="7" t="s">
         <v>545</v>
@@ -7853,7 +7922,7 @@
       <c r="K97" s="8" t="s">
         <v>550</v>
       </c>
-      <c r="L97" s="14">
+      <c r="L97" s="13">
         <v>96</v>
       </c>
     </row>
@@ -7868,7 +7937,7 @@
         <v>97</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>19</v>
+        <v>1191</v>
       </c>
       <c r="E98" s="7" t="s">
         <v>551</v>
@@ -7891,7 +7960,7 @@
       <c r="K98" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="L98" s="14">
+      <c r="L98" s="13">
         <v>97</v>
       </c>
     </row>
@@ -7906,7 +7975,7 @@
         <v>98</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>19</v>
+        <v>1191</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>556</v>
@@ -7929,7 +7998,7 @@
       <c r="K99" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="L99" s="14">
+      <c r="L99" s="13">
         <v>98</v>
       </c>
     </row>
@@ -7944,7 +8013,7 @@
         <v>99</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>52</v>
+        <v>1193</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>561</v>
@@ -7967,7 +8036,7 @@
       <c r="K100" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="L100" s="14">
+      <c r="L100" s="13">
         <v>99</v>
       </c>
     </row>
@@ -7982,7 +8051,7 @@
         <v>100</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>19</v>
+        <v>1191</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>566</v>
@@ -8005,7 +8074,7 @@
       <c r="K101" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="L101" s="14">
+      <c r="L101" s="13">
         <v>100</v>
       </c>
     </row>
@@ -8020,7 +8089,7 @@
         <v>101</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>52</v>
+        <v>1193</v>
       </c>
       <c r="E102" s="7" t="s">
         <v>571</v>
@@ -8043,7 +8112,7 @@
       <c r="K102" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="L102" s="14">
+      <c r="L102" s="13">
         <v>101</v>
       </c>
     </row>
@@ -8058,7 +8127,7 @@
         <v>102</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="E103" s="7" t="s">
         <v>576</v>
@@ -8081,7 +8150,7 @@
       <c r="K103" s="8" t="s">
         <v>581</v>
       </c>
-      <c r="L103" s="14">
+      <c r="L103" s="13">
         <v>102</v>
       </c>
     </row>
@@ -8096,7 +8165,7 @@
         <v>103</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>52</v>
+        <v>1193</v>
       </c>
       <c r="E104" s="7" t="s">
         <v>582</v>
@@ -8119,7 +8188,7 @@
       <c r="K104" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="L104" s="14">
+      <c r="L104" s="13">
         <v>103</v>
       </c>
     </row>
@@ -8134,7 +8203,7 @@
         <v>104</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>11</v>
+        <v>1190</v>
       </c>
       <c r="E105" s="11" t="s">
         <v>587</v>
@@ -8157,3965 +8226,3965 @@
       <c r="K105" s="12" t="s">
         <v>592</v>
       </c>
-      <c r="L105" s="14">
+      <c r="L105" s="13">
         <v>104</v>
       </c>
     </row>
     <row r="106" spans="1:12">
-      <c r="A106" s="13" t="s">
+      <c r="A106" t="s">
         <v>1188</v>
       </c>
-      <c r="B106" s="13" t="s">
+      <c r="B106" t="s">
         <v>593</v>
       </c>
       <c r="C106" s="6">
         <v>105</v>
       </c>
-      <c r="D106" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E106" s="13" t="s">
+      <c r="D106" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E106" t="s">
         <v>594</v>
       </c>
-      <c r="F106" s="13" t="s">
+      <c r="F106" t="s">
         <v>595</v>
       </c>
-      <c r="G106" s="13" t="s">
+      <c r="G106" t="s">
         <v>596</v>
       </c>
-      <c r="H106" s="13" t="s">
+      <c r="H106" t="s">
         <v>597</v>
       </c>
-      <c r="I106" s="13" t="s">
+      <c r="I106" t="s">
         <v>598</v>
       </c>
-      <c r="J106" s="14" t="s">
+      <c r="J106" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K106" s="13" t="s">
+      <c r="K106" t="s">
         <v>1100</v>
       </c>
-      <c r="L106" s="14">
+      <c r="L106" s="13">
         <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:12">
-      <c r="A107" s="13" t="s">
+      <c r="A107" t="s">
         <v>1188</v>
       </c>
-      <c r="B107" s="13" t="s">
+      <c r="B107" t="s">
         <v>593</v>
       </c>
       <c r="C107" s="2">
         <v>106</v>
       </c>
-      <c r="D107" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E107" s="13" t="s">
+      <c r="D107" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E107" t="s">
         <v>599</v>
       </c>
-      <c r="F107" s="13" t="s">
+      <c r="F107" t="s">
         <v>600</v>
       </c>
-      <c r="G107" s="13" t="s">
+      <c r="G107" t="s">
         <v>601</v>
       </c>
-      <c r="H107" s="13" t="s">
+      <c r="H107" t="s">
         <v>602</v>
       </c>
-      <c r="I107" s="13" t="s">
+      <c r="I107" t="s">
         <v>603</v>
       </c>
-      <c r="J107" s="14" t="s">
+      <c r="J107" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K107" s="13" t="s">
+      <c r="K107" t="s">
         <v>1101</v>
       </c>
-      <c r="L107" s="14">
+      <c r="L107" s="13">
         <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:12">
-      <c r="A108" s="13" t="s">
+      <c r="A108" t="s">
         <v>1188</v>
       </c>
-      <c r="B108" s="13" t="s">
+      <c r="B108" t="s">
         <v>593</v>
       </c>
       <c r="C108" s="6">
         <v>107</v>
       </c>
-      <c r="D108" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E108" s="13" t="s">
+      <c r="D108" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E108" t="s">
         <v>604</v>
       </c>
-      <c r="F108" s="13" t="s">
+      <c r="F108" t="s">
         <v>605</v>
       </c>
-      <c r="G108" s="13" t="s">
+      <c r="G108" t="s">
         <v>606</v>
       </c>
-      <c r="H108" s="13" t="s">
+      <c r="H108" t="s">
         <v>607</v>
       </c>
-      <c r="I108" s="13" t="s">
+      <c r="I108" t="s">
         <v>608</v>
       </c>
-      <c r="J108" s="14" t="s">
+      <c r="J108" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K108" s="13" t="s">
+      <c r="K108" t="s">
         <v>1102</v>
       </c>
-      <c r="L108" s="14">
+      <c r="L108" s="13">
         <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:12">
-      <c r="A109" s="13" t="s">
+      <c r="A109" t="s">
         <v>1188</v>
       </c>
-      <c r="B109" s="13" t="s">
+      <c r="B109" t="s">
         <v>593</v>
       </c>
       <c r="C109" s="6">
         <v>108</v>
       </c>
-      <c r="D109" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E109" s="13" t="s">
+      <c r="D109" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E109" t="s">
         <v>609</v>
       </c>
-      <c r="F109" s="13" t="s">
+      <c r="F109" t="s">
         <v>610</v>
       </c>
-      <c r="G109" s="13" t="s">
+      <c r="G109" t="s">
         <v>611</v>
       </c>
-      <c r="H109" s="13" t="s">
+      <c r="H109" t="s">
         <v>612</v>
       </c>
-      <c r="I109" s="13" t="s">
+      <c r="I109" t="s">
         <v>613</v>
       </c>
-      <c r="J109" s="14" t="s">
+      <c r="J109" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K109" s="13" t="s">
+      <c r="K109" t="s">
         <v>1103</v>
       </c>
-      <c r="L109" s="14">
+      <c r="L109" s="13">
         <v>4</v>
       </c>
     </row>
     <row r="110" spans="1:12">
-      <c r="A110" s="13" t="s">
+      <c r="A110" t="s">
         <v>1188</v>
       </c>
-      <c r="B110" s="13" t="s">
+      <c r="B110" t="s">
         <v>593</v>
       </c>
       <c r="C110" s="2">
         <v>109</v>
       </c>
-      <c r="D110" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E110" s="13" t="s">
+      <c r="D110" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E110" t="s">
         <v>614</v>
       </c>
-      <c r="F110" s="13" t="s">
+      <c r="F110" t="s">
         <v>615</v>
       </c>
-      <c r="G110" s="13" t="s">
+      <c r="G110" t="s">
         <v>616</v>
       </c>
-      <c r="H110" s="13" t="s">
+      <c r="H110" t="s">
         <v>617</v>
       </c>
-      <c r="I110" s="13" t="s">
+      <c r="I110" t="s">
         <v>618</v>
       </c>
-      <c r="J110" s="14" t="s">
+      <c r="J110" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K110" s="13" t="s">
+      <c r="K110" t="s">
         <v>1104</v>
       </c>
-      <c r="L110" s="14">
+      <c r="L110" s="13">
         <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:12">
-      <c r="A111" s="13" t="s">
+      <c r="A111" t="s">
         <v>1188</v>
       </c>
-      <c r="B111" s="13" t="s">
+      <c r="B111" t="s">
         <v>593</v>
       </c>
       <c r="C111" s="6">
         <v>110</v>
       </c>
-      <c r="D111" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E111" s="13" t="s">
+      <c r="D111" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E111" t="s">
         <v>619</v>
       </c>
-      <c r="F111" s="13" t="s">
+      <c r="F111" t="s">
         <v>620</v>
       </c>
-      <c r="G111" s="13" t="s">
+      <c r="G111" t="s">
         <v>621</v>
       </c>
-      <c r="H111" s="13" t="s">
+      <c r="H111" t="s">
         <v>622</v>
       </c>
-      <c r="I111" s="13" t="s">
+      <c r="I111" t="s">
         <v>623</v>
       </c>
-      <c r="J111" s="14" t="s">
+      <c r="J111" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K111" s="13" t="s">
+      <c r="K111" t="s">
         <v>1105</v>
       </c>
-      <c r="L111" s="14">
+      <c r="L111" s="13">
         <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:12">
-      <c r="A112" s="13" t="s">
+      <c r="A112" t="s">
         <v>1188</v>
       </c>
-      <c r="B112" s="13" t="s">
+      <c r="B112" t="s">
         <v>593</v>
       </c>
       <c r="C112" s="6">
         <v>111</v>
       </c>
-      <c r="D112" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E112" s="13" t="s">
+      <c r="D112" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E112" t="s">
         <v>624</v>
       </c>
-      <c r="F112" s="13" t="s">
+      <c r="F112" t="s">
         <v>625</v>
       </c>
-      <c r="G112" s="13" t="s">
+      <c r="G112" t="s">
         <v>626</v>
       </c>
-      <c r="H112" s="13" t="s">
+      <c r="H112" t="s">
         <v>627</v>
       </c>
-      <c r="I112" s="13" t="s">
+      <c r="I112" t="s">
         <v>628</v>
       </c>
-      <c r="J112" s="14" t="s">
+      <c r="J112" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K112" s="13" t="s">
+      <c r="K112" t="s">
         <v>1106</v>
       </c>
-      <c r="L112" s="14">
+      <c r="L112" s="13">
         <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:12">
-      <c r="A113" s="13" t="s">
+      <c r="A113" t="s">
         <v>1188</v>
       </c>
-      <c r="B113" s="13" t="s">
+      <c r="B113" t="s">
         <v>593</v>
       </c>
       <c r="C113" s="2">
         <v>112</v>
       </c>
-      <c r="D113" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E113" s="13" t="s">
+      <c r="D113" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E113" t="s">
         <v>629</v>
       </c>
-      <c r="F113" s="13" t="s">
+      <c r="F113" t="s">
         <v>630</v>
       </c>
-      <c r="G113" s="13" t="s">
+      <c r="G113" t="s">
         <v>631</v>
       </c>
-      <c r="H113" s="13" t="s">
+      <c r="H113" t="s">
         <v>632</v>
       </c>
-      <c r="I113" s="13" t="s">
+      <c r="I113" t="s">
         <v>633</v>
       </c>
-      <c r="J113" s="14" t="s">
+      <c r="J113" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K113" s="13" t="s">
+      <c r="K113" t="s">
         <v>1107</v>
       </c>
-      <c r="L113" s="14">
+      <c r="L113" s="13">
         <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:12">
-      <c r="A114" s="13" t="s">
+      <c r="A114" t="s">
         <v>1188</v>
       </c>
-      <c r="B114" s="13" t="s">
+      <c r="B114" t="s">
         <v>593</v>
       </c>
       <c r="C114" s="6">
         <v>113</v>
       </c>
-      <c r="D114" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E114" s="13" t="s">
+      <c r="D114" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E114" t="s">
         <v>634</v>
       </c>
-      <c r="F114" s="13" t="s">
+      <c r="F114" t="s">
         <v>635</v>
       </c>
-      <c r="G114" s="13" t="s">
+      <c r="G114" t="s">
         <v>636</v>
       </c>
-      <c r="H114" s="13" t="s">
+      <c r="H114" t="s">
         <v>637</v>
       </c>
-      <c r="I114" s="13" t="s">
+      <c r="I114" t="s">
         <v>638</v>
       </c>
-      <c r="J114" s="14" t="s">
+      <c r="J114" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K114" s="13" t="s">
+      <c r="K114" t="s">
         <v>1108</v>
       </c>
-      <c r="L114" s="14">
+      <c r="L114" s="13">
         <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:12">
-      <c r="A115" s="13" t="s">
+      <c r="A115" t="s">
         <v>1188</v>
       </c>
-      <c r="B115" s="13" t="s">
+      <c r="B115" t="s">
         <v>593</v>
       </c>
       <c r="C115" s="6">
         <v>114</v>
       </c>
-      <c r="D115" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E115" s="13" t="s">
+      <c r="D115" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E115" t="s">
         <v>639</v>
       </c>
-      <c r="F115" s="13" t="s">
+      <c r="F115" t="s">
         <v>640</v>
       </c>
-      <c r="G115" s="13" t="s">
+      <c r="G115" t="s">
         <v>641</v>
       </c>
-      <c r="H115" s="13" t="s">
+      <c r="H115" t="s">
         <v>642</v>
       </c>
-      <c r="I115" s="13" t="s">
+      <c r="I115" t="s">
         <v>643</v>
       </c>
-      <c r="J115" s="14" t="s">
+      <c r="J115" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K115" s="13" t="s">
+      <c r="K115" t="s">
         <v>1109</v>
       </c>
-      <c r="L115" s="14">
+      <c r="L115" s="13">
         <v>10</v>
       </c>
     </row>
     <row r="116" spans="1:12">
-      <c r="A116" s="13" t="s">
+      <c r="A116" t="s">
         <v>1188</v>
       </c>
-      <c r="B116" s="13" t="s">
+      <c r="B116" t="s">
         <v>593</v>
       </c>
       <c r="C116" s="2">
         <v>115</v>
       </c>
-      <c r="D116" s="13" t="s">
+      <c r="D116" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E116" t="s">
+        <v>644</v>
+      </c>
+      <c r="F116" t="s">
+        <v>297</v>
+      </c>
+      <c r="G116" t="s">
+        <v>645</v>
+      </c>
+      <c r="H116" t="s">
+        <v>646</v>
+      </c>
+      <c r="I116" t="s">
+        <v>647</v>
+      </c>
+      <c r="J116" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K116" t="s">
+        <v>1104</v>
+      </c>
+      <c r="L116" s="13">
         <v>11</v>
       </c>
-      <c r="E116" s="13" t="s">
-        <v>644</v>
-      </c>
-      <c r="F116" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="G116" s="13" t="s">
-        <v>645</v>
-      </c>
-      <c r="H116" s="13" t="s">
-        <v>646</v>
-      </c>
-      <c r="I116" s="13" t="s">
-        <v>647</v>
-      </c>
-      <c r="J116" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="K116" s="13" t="s">
-        <v>1104</v>
-      </c>
-      <c r="L116" s="14">
-        <v>11</v>
-      </c>
     </row>
     <row r="117" spans="1:12">
-      <c r="A117" s="13" t="s">
+      <c r="A117" t="s">
         <v>1188</v>
       </c>
-      <c r="B117" s="13" t="s">
+      <c r="B117" t="s">
         <v>593</v>
       </c>
       <c r="C117" s="6">
         <v>116</v>
       </c>
-      <c r="D117" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E117" s="13" t="s">
+      <c r="D117" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E117" t="s">
         <v>648</v>
       </c>
-      <c r="F117" s="13" t="s">
+      <c r="F117" t="s">
         <v>649</v>
       </c>
-      <c r="G117" s="13" t="s">
+      <c r="G117" t="s">
         <v>650</v>
       </c>
-      <c r="H117" s="13" t="s">
+      <c r="H117" t="s">
         <v>651</v>
       </c>
-      <c r="I117" s="13" t="s">
+      <c r="I117" t="s">
         <v>652</v>
       </c>
-      <c r="J117" s="14" t="s">
+      <c r="J117" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K117" s="13" t="s">
+      <c r="K117" t="s">
         <v>1110</v>
       </c>
-      <c r="L117" s="14">
+      <c r="L117" s="13">
         <v>12</v>
       </c>
     </row>
     <row r="118" spans="1:12">
-      <c r="A118" s="13" t="s">
+      <c r="A118" t="s">
         <v>1188</v>
       </c>
-      <c r="B118" s="13" t="s">
+      <c r="B118" t="s">
         <v>593</v>
       </c>
       <c r="C118" s="6">
         <v>117</v>
       </c>
-      <c r="D118" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E118" s="13" t="s">
+      <c r="D118" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E118" t="s">
         <v>653</v>
       </c>
-      <c r="F118" s="13" t="s">
+      <c r="F118" t="s">
         <v>654</v>
       </c>
-      <c r="G118" s="13" t="s">
+      <c r="G118" t="s">
         <v>655</v>
       </c>
-      <c r="H118" s="13" t="s">
+      <c r="H118" t="s">
         <v>656</v>
       </c>
-      <c r="I118" s="13" t="s">
+      <c r="I118" t="s">
         <v>657</v>
       </c>
-      <c r="J118" s="14" t="s">
+      <c r="J118" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K118" s="13" t="s">
+      <c r="K118" t="s">
         <v>1111</v>
       </c>
-      <c r="L118" s="14">
+      <c r="L118" s="13">
         <v>13</v>
       </c>
     </row>
     <row r="119" spans="1:12">
-      <c r="A119" s="13" t="s">
+      <c r="A119" t="s">
         <v>1188</v>
       </c>
-      <c r="B119" s="13" t="s">
+      <c r="B119" t="s">
         <v>593</v>
       </c>
       <c r="C119" s="2">
         <v>118</v>
       </c>
-      <c r="D119" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E119" s="13" t="s">
+      <c r="D119" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E119" t="s">
         <v>658</v>
       </c>
-      <c r="F119" s="13" t="s">
+      <c r="F119" t="s">
         <v>659</v>
       </c>
-      <c r="G119" s="13" t="s">
+      <c r="G119" t="s">
         <v>660</v>
       </c>
-      <c r="H119" s="13" t="s">
+      <c r="H119" t="s">
         <v>661</v>
       </c>
-      <c r="I119" s="13" t="s">
+      <c r="I119" t="s">
         <v>662</v>
       </c>
-      <c r="J119" s="14" t="s">
+      <c r="J119" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K119" s="13" t="s">
+      <c r="K119" t="s">
         <v>1112</v>
       </c>
-      <c r="L119" s="14">
+      <c r="L119" s="13">
         <v>14</v>
       </c>
     </row>
     <row r="120" spans="1:12">
-      <c r="A120" s="13" t="s">
+      <c r="A120" t="s">
         <v>1188</v>
       </c>
-      <c r="B120" s="13" t="s">
+      <c r="B120" t="s">
         <v>593</v>
       </c>
       <c r="C120" s="6">
         <v>119</v>
       </c>
-      <c r="D120" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E120" s="13" t="s">
+      <c r="D120" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E120" t="s">
         <v>663</v>
       </c>
-      <c r="F120" s="13" t="s">
+      <c r="F120" t="s">
         <v>664</v>
       </c>
-      <c r="G120" s="13" t="s">
+      <c r="G120" t="s">
         <v>665</v>
       </c>
-      <c r="H120" s="13" t="s">
+      <c r="H120" t="s">
         <v>666</v>
       </c>
-      <c r="I120" s="13" t="s">
+      <c r="I120" t="s">
         <v>667</v>
       </c>
-      <c r="J120" s="14" t="s">
+      <c r="J120" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K120" s="13" t="s">
+      <c r="K120" t="s">
         <v>1113</v>
       </c>
-      <c r="L120" s="14">
+      <c r="L120" s="13">
         <v>15</v>
       </c>
     </row>
     <row r="121" spans="1:12">
-      <c r="A121" s="13" t="s">
+      <c r="A121" t="s">
         <v>1188</v>
       </c>
-      <c r="B121" s="13" t="s">
+      <c r="B121" t="s">
         <v>593</v>
       </c>
       <c r="C121" s="6">
         <v>120</v>
       </c>
-      <c r="D121" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E121" s="13" t="s">
+      <c r="D121" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E121" t="s">
         <v>668</v>
       </c>
-      <c r="F121" s="13" t="s">
+      <c r="F121" t="s">
         <v>669</v>
       </c>
-      <c r="G121" s="13" t="s">
+      <c r="G121" t="s">
         <v>670</v>
       </c>
-      <c r="H121" s="13" t="s">
+      <c r="H121" t="s">
         <v>671</v>
       </c>
-      <c r="I121" s="13" t="s">
+      <c r="I121" t="s">
         <v>672</v>
       </c>
-      <c r="J121" s="14" t="s">
+      <c r="J121" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K121" s="13" t="s">
+      <c r="K121" t="s">
         <v>1114</v>
       </c>
-      <c r="L121" s="14">
+      <c r="L121" s="13">
         <v>16</v>
       </c>
     </row>
     <row r="122" spans="1:12">
-      <c r="A122" s="13" t="s">
+      <c r="A122" t="s">
         <v>1188</v>
       </c>
-      <c r="B122" s="13" t="s">
+      <c r="B122" t="s">
         <v>593</v>
       </c>
       <c r="C122" s="2">
         <v>121</v>
       </c>
-      <c r="D122" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E122" s="13" t="s">
+      <c r="D122" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E122" t="s">
         <v>673</v>
       </c>
-      <c r="F122" s="13" t="s">
+      <c r="F122" t="s">
         <v>674</v>
       </c>
-      <c r="G122" s="13" t="s">
+      <c r="G122" t="s">
         <v>675</v>
       </c>
-      <c r="H122" s="13" t="s">
+      <c r="H122" t="s">
         <v>676</v>
       </c>
-      <c r="I122" s="13" t="s">
+      <c r="I122" t="s">
         <v>677</v>
       </c>
-      <c r="J122" s="14" t="s">
+      <c r="J122" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K122" s="13" t="s">
+      <c r="K122" t="s">
         <v>1115</v>
       </c>
-      <c r="L122" s="14">
+      <c r="L122" s="13">
         <v>17</v>
       </c>
     </row>
     <row r="123" spans="1:12">
-      <c r="A123" s="13" t="s">
+      <c r="A123" t="s">
         <v>1188</v>
       </c>
-      <c r="B123" s="13" t="s">
+      <c r="B123" t="s">
         <v>593</v>
       </c>
       <c r="C123" s="6">
         <v>122</v>
       </c>
-      <c r="D123" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E123" s="13" t="s">
+      <c r="D123" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E123" t="s">
         <v>678</v>
       </c>
-      <c r="F123" s="13" t="s">
+      <c r="F123" t="s">
         <v>679</v>
       </c>
-      <c r="G123" s="13" t="s">
+      <c r="G123" t="s">
         <v>680</v>
       </c>
-      <c r="H123" s="13" t="s">
+      <c r="H123" t="s">
         <v>681</v>
       </c>
-      <c r="I123" s="13" t="s">
+      <c r="I123" t="s">
         <v>682</v>
       </c>
-      <c r="J123" s="14" t="s">
+      <c r="J123" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K123" s="13" t="s">
+      <c r="K123" t="s">
         <v>1116</v>
       </c>
-      <c r="L123" s="14">
+      <c r="L123" s="13">
         <v>18</v>
       </c>
     </row>
     <row r="124" spans="1:12">
-      <c r="A124" s="13" t="s">
+      <c r="A124" t="s">
         <v>1188</v>
       </c>
-      <c r="B124" s="13" t="s">
+      <c r="B124" t="s">
         <v>593</v>
       </c>
       <c r="C124" s="6">
         <v>123</v>
       </c>
-      <c r="D124" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E124" s="13" t="s">
+      <c r="D124" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E124" t="s">
         <v>683</v>
       </c>
-      <c r="F124" s="13" t="s">
+      <c r="F124" t="s">
         <v>684</v>
       </c>
-      <c r="G124" s="13" t="s">
+      <c r="G124" t="s">
         <v>685</v>
       </c>
-      <c r="H124" s="13" t="s">
+      <c r="H124" t="s">
         <v>686</v>
       </c>
-      <c r="I124" s="13" t="s">
+      <c r="I124" t="s">
         <v>687</v>
       </c>
-      <c r="J124" s="14" t="s">
+      <c r="J124" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K124" s="13" t="s">
+      <c r="K124" t="s">
         <v>1117</v>
       </c>
-      <c r="L124" s="14">
+      <c r="L124" s="13">
         <v>19</v>
       </c>
     </row>
     <row r="125" spans="1:12">
-      <c r="A125" s="13" t="s">
+      <c r="A125" t="s">
         <v>1188</v>
       </c>
-      <c r="B125" s="13" t="s">
+      <c r="B125" t="s">
         <v>593</v>
       </c>
       <c r="C125" s="2">
         <v>124</v>
       </c>
-      <c r="D125" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E125" s="13" t="s">
+      <c r="D125" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E125" t="s">
         <v>688</v>
       </c>
-      <c r="F125" s="13" t="s">
+      <c r="F125" t="s">
         <v>689</v>
       </c>
-      <c r="G125" s="13" t="s">
+      <c r="G125" t="s">
         <v>690</v>
       </c>
-      <c r="H125" s="13" t="s">
+      <c r="H125" t="s">
         <v>691</v>
       </c>
-      <c r="I125" s="13" t="s">
+      <c r="I125" t="s">
         <v>692</v>
       </c>
-      <c r="J125" s="14" t="s">
+      <c r="J125" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K125" s="13" t="s">
+      <c r="K125" t="s">
         <v>1118</v>
       </c>
-      <c r="L125" s="14">
+      <c r="L125" s="13">
         <v>20</v>
       </c>
     </row>
     <row r="126" spans="1:12">
-      <c r="A126" s="13" t="s">
+      <c r="A126" t="s">
         <v>1188</v>
       </c>
-      <c r="B126" s="13" t="s">
+      <c r="B126" t="s">
         <v>593</v>
       </c>
       <c r="C126" s="6">
         <v>125</v>
       </c>
-      <c r="D126" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E126" s="13" t="s">
+      <c r="D126" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E126" t="s">
         <v>693</v>
       </c>
-      <c r="F126" s="13" t="s">
+      <c r="F126" t="s">
         <v>694</v>
       </c>
-      <c r="G126" s="13" t="s">
+      <c r="G126" t="s">
         <v>695</v>
       </c>
-      <c r="H126" s="13" t="s">
+      <c r="H126" t="s">
         <v>696</v>
       </c>
-      <c r="I126" s="13" t="s">
+      <c r="I126" t="s">
         <v>697</v>
       </c>
-      <c r="J126" s="14" t="s">
+      <c r="J126" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K126" s="13" t="s">
+      <c r="K126" t="s">
         <v>1119</v>
       </c>
-      <c r="L126" s="14">
+      <c r="L126" s="13">
         <v>21</v>
       </c>
     </row>
     <row r="127" spans="1:12">
-      <c r="A127" s="13" t="s">
+      <c r="A127" t="s">
         <v>1188</v>
       </c>
-      <c r="B127" s="13" t="s">
+      <c r="B127" t="s">
         <v>593</v>
       </c>
       <c r="C127" s="6">
         <v>126</v>
       </c>
-      <c r="D127" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E127" s="13" t="s">
+      <c r="D127" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E127" t="s">
         <v>698</v>
       </c>
-      <c r="F127" s="13" t="s">
+      <c r="F127" t="s">
         <v>699</v>
       </c>
-      <c r="G127" s="13" t="s">
+      <c r="G127" t="s">
         <v>700</v>
       </c>
-      <c r="H127" s="13" t="s">
+      <c r="H127" t="s">
         <v>701</v>
       </c>
-      <c r="I127" s="13" t="s">
+      <c r="I127" t="s">
         <v>702</v>
       </c>
-      <c r="J127" s="14" t="s">
+      <c r="J127" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K127" s="13" t="s">
+      <c r="K127" t="s">
         <v>1120</v>
       </c>
-      <c r="L127" s="14">
+      <c r="L127" s="13">
         <v>22</v>
       </c>
     </row>
     <row r="128" spans="1:12">
-      <c r="A128" s="13" t="s">
+      <c r="A128" t="s">
         <v>1188</v>
       </c>
-      <c r="B128" s="13" t="s">
+      <c r="B128" t="s">
         <v>593</v>
       </c>
       <c r="C128" s="2">
         <v>127</v>
       </c>
-      <c r="D128" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E128" s="13" t="s">
+      <c r="D128" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E128" t="s">
         <v>703</v>
       </c>
-      <c r="F128" s="13" t="s">
+      <c r="F128" t="s">
         <v>704</v>
       </c>
-      <c r="G128" s="13" t="s">
+      <c r="G128" t="s">
         <v>705</v>
       </c>
-      <c r="H128" s="13" t="s">
+      <c r="H128" t="s">
         <v>706</v>
       </c>
-      <c r="I128" s="13" t="s">
+      <c r="I128" t="s">
         <v>707</v>
       </c>
-      <c r="J128" s="14" t="s">
+      <c r="J128" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K128" s="13" t="s">
+      <c r="K128" t="s">
         <v>1121</v>
       </c>
-      <c r="L128" s="14">
+      <c r="L128" s="13">
         <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:12">
-      <c r="A129" s="13" t="s">
+      <c r="A129" t="s">
         <v>1188</v>
       </c>
-      <c r="B129" s="13" t="s">
+      <c r="B129" t="s">
         <v>593</v>
       </c>
       <c r="C129" s="6">
         <v>128</v>
       </c>
-      <c r="D129" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E129" s="13" t="s">
+      <c r="D129" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E129" t="s">
         <v>708</v>
       </c>
-      <c r="F129" s="13" t="s">
+      <c r="F129" t="s">
         <v>252</v>
       </c>
-      <c r="G129" s="13" t="s">
+      <c r="G129" t="s">
         <v>709</v>
       </c>
-      <c r="H129" s="13" t="s">
+      <c r="H129" t="s">
         <v>307</v>
       </c>
-      <c r="I129" s="13" t="s">
+      <c r="I129" t="s">
         <v>710</v>
       </c>
-      <c r="J129" s="14" t="s">
+      <c r="J129" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K129" s="13" t="s">
+      <c r="K129" t="s">
         <v>1122</v>
       </c>
-      <c r="L129" s="14">
+      <c r="L129" s="13">
         <v>24</v>
       </c>
     </row>
     <row r="130" spans="1:12">
-      <c r="A130" s="13" t="s">
+      <c r="A130" t="s">
         <v>1188</v>
       </c>
-      <c r="B130" s="13" t="s">
+      <c r="B130" t="s">
         <v>593</v>
       </c>
       <c r="C130" s="6">
         <v>129</v>
       </c>
-      <c r="D130" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E130" s="13" t="s">
+      <c r="D130" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E130" t="s">
         <v>711</v>
       </c>
-      <c r="F130" s="13" t="s">
+      <c r="F130" t="s">
         <v>712</v>
       </c>
-      <c r="G130" s="13" t="s">
+      <c r="G130" t="s">
         <v>713</v>
       </c>
-      <c r="H130" s="13" t="s">
+      <c r="H130" t="s">
         <v>714</v>
       </c>
-      <c r="I130" s="13" t="s">
+      <c r="I130" t="s">
         <v>715</v>
       </c>
-      <c r="J130" s="14" t="s">
+      <c r="J130" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K130" s="13" t="s">
+      <c r="K130" t="s">
         <v>1123</v>
       </c>
-      <c r="L130" s="14">
+      <c r="L130" s="13">
         <v>25</v>
       </c>
     </row>
     <row r="131" spans="1:12">
-      <c r="A131" s="13" t="s">
+      <c r="A131" t="s">
         <v>1188</v>
       </c>
-      <c r="B131" s="13" t="s">
+      <c r="B131" t="s">
         <v>593</v>
       </c>
       <c r="C131" s="2">
         <v>130</v>
       </c>
-      <c r="D131" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E131" s="13" t="s">
+      <c r="D131" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E131" t="s">
         <v>716</v>
       </c>
-      <c r="F131" s="13" t="s">
+      <c r="F131" t="s">
         <v>717</v>
       </c>
-      <c r="G131" s="13" t="s">
+      <c r="G131" t="s">
         <v>718</v>
       </c>
-      <c r="H131" s="13" t="s">
+      <c r="H131" t="s">
         <v>719</v>
       </c>
-      <c r="I131" s="13" t="s">
+      <c r="I131" t="s">
         <v>720</v>
       </c>
-      <c r="J131" s="14" t="s">
+      <c r="J131" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K131" s="13" t="s">
+      <c r="K131" t="s">
         <v>1113</v>
       </c>
-      <c r="L131" s="14">
+      <c r="L131" s="13">
         <v>26</v>
       </c>
     </row>
     <row r="132" spans="1:12">
-      <c r="A132" s="13" t="s">
+      <c r="A132" t="s">
         <v>1188</v>
       </c>
-      <c r="B132" s="13" t="s">
+      <c r="B132" t="s">
         <v>593</v>
       </c>
       <c r="C132" s="6">
         <v>131</v>
       </c>
-      <c r="D132" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E132" s="13" t="s">
+      <c r="D132" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E132" t="s">
         <v>721</v>
       </c>
-      <c r="F132" s="13" t="s">
+      <c r="F132" t="s">
         <v>722</v>
       </c>
-      <c r="G132" s="13" t="s">
+      <c r="G132" t="s">
         <v>723</v>
       </c>
-      <c r="H132" s="13" t="s">
+      <c r="H132" t="s">
         <v>724</v>
       </c>
-      <c r="I132" s="13" t="s">
+      <c r="I132" t="s">
         <v>725</v>
       </c>
-      <c r="J132" s="14" t="s">
+      <c r="J132" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K132" s="13" t="s">
+      <c r="K132" t="s">
         <v>1124</v>
       </c>
-      <c r="L132" s="14">
+      <c r="L132" s="13">
         <v>27</v>
       </c>
     </row>
     <row r="133" spans="1:12">
-      <c r="A133" s="13" t="s">
+      <c r="A133" t="s">
         <v>1188</v>
       </c>
-      <c r="B133" s="13" t="s">
+      <c r="B133" t="s">
         <v>593</v>
       </c>
       <c r="C133" s="6">
         <v>132</v>
       </c>
-      <c r="D133" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E133" s="13" t="s">
+      <c r="D133" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E133" t="s">
         <v>726</v>
       </c>
-      <c r="F133" s="13" t="s">
+      <c r="F133" t="s">
         <v>727</v>
       </c>
-      <c r="G133" s="13" t="s">
+      <c r="G133" t="s">
         <v>728</v>
       </c>
-      <c r="H133" s="13" t="s">
+      <c r="H133" t="s">
         <v>729</v>
       </c>
-      <c r="I133" s="13" t="s">
+      <c r="I133" t="s">
         <v>730</v>
       </c>
-      <c r="J133" s="14" t="s">
+      <c r="J133" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K133" s="13" t="s">
+      <c r="K133" t="s">
         <v>1125</v>
       </c>
-      <c r="L133" s="14">
+      <c r="L133" s="13">
         <v>28</v>
       </c>
     </row>
     <row r="134" spans="1:12">
-      <c r="A134" s="13" t="s">
+      <c r="A134" t="s">
         <v>1188</v>
       </c>
-      <c r="B134" s="13" t="s">
+      <c r="B134" t="s">
         <v>593</v>
       </c>
       <c r="C134" s="2">
         <v>133</v>
       </c>
-      <c r="D134" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E134" s="13" t="s">
+      <c r="D134" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E134" t="s">
         <v>731</v>
       </c>
-      <c r="F134" s="13" t="s">
+      <c r="F134" t="s">
         <v>732</v>
       </c>
-      <c r="G134" s="13" t="s">
+      <c r="G134" t="s">
         <v>733</v>
       </c>
-      <c r="H134" s="13" t="s">
+      <c r="H134" t="s">
         <v>734</v>
       </c>
-      <c r="I134" s="13" t="s">
+      <c r="I134" t="s">
         <v>735</v>
       </c>
-      <c r="J134" s="14" t="s">
+      <c r="J134" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K134" s="13" t="s">
+      <c r="K134" t="s">
         <v>1126</v>
       </c>
-      <c r="L134" s="14">
+      <c r="L134" s="13">
         <v>29</v>
       </c>
     </row>
     <row r="135" spans="1:12">
-      <c r="A135" s="13" t="s">
+      <c r="A135" t="s">
         <v>1188</v>
       </c>
-      <c r="B135" s="13" t="s">
+      <c r="B135" t="s">
         <v>593</v>
       </c>
       <c r="C135" s="6">
         <v>134</v>
       </c>
-      <c r="D135" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E135" s="13" t="s">
+      <c r="D135" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E135" t="s">
         <v>736</v>
       </c>
-      <c r="F135" s="13" t="s">
+      <c r="F135" t="s">
         <v>737</v>
       </c>
-      <c r="G135" s="13" t="s">
+      <c r="G135" t="s">
         <v>738</v>
       </c>
-      <c r="H135" s="13" t="s">
+      <c r="H135" t="s">
         <v>739</v>
       </c>
-      <c r="I135" s="13" t="s">
+      <c r="I135" t="s">
         <v>740</v>
       </c>
-      <c r="J135" s="14" t="s">
+      <c r="J135" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K135" s="13" t="s">
+      <c r="K135" t="s">
         <v>1127</v>
       </c>
-      <c r="L135" s="14">
+      <c r="L135" s="13">
         <v>30</v>
       </c>
     </row>
     <row r="136" spans="1:12">
-      <c r="A136" s="13" t="s">
+      <c r="A136" t="s">
         <v>1188</v>
       </c>
-      <c r="B136" s="13" t="s">
+      <c r="B136" t="s">
         <v>593</v>
       </c>
       <c r="C136" s="6">
         <v>135</v>
       </c>
-      <c r="D136" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E136" s="13" t="s">
+      <c r="D136" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E136" t="s">
         <v>741</v>
       </c>
-      <c r="F136" s="13" t="s">
+      <c r="F136" t="s">
         <v>742</v>
       </c>
-      <c r="G136" s="13" t="s">
+      <c r="G136" t="s">
         <v>743</v>
       </c>
-      <c r="H136" s="13" t="s">
+      <c r="H136" t="s">
         <v>744</v>
       </c>
-      <c r="I136" s="13" t="s">
+      <c r="I136" t="s">
         <v>745</v>
       </c>
-      <c r="J136" s="14" t="s">
+      <c r="J136" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K136" s="13" t="s">
+      <c r="K136" t="s">
         <v>1128</v>
       </c>
-      <c r="L136" s="14">
+      <c r="L136" s="13">
         <v>31</v>
       </c>
     </row>
     <row r="137" spans="1:12">
-      <c r="A137" s="13" t="s">
+      <c r="A137" t="s">
         <v>1188</v>
       </c>
-      <c r="B137" s="13" t="s">
+      <c r="B137" t="s">
         <v>593</v>
       </c>
       <c r="C137" s="2">
         <v>136</v>
       </c>
-      <c r="D137" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="E137" s="13" t="s">
+      <c r="D137" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E137" t="s">
         <v>746</v>
       </c>
-      <c r="F137" s="13" t="s">
+      <c r="F137" t="s">
         <v>747</v>
       </c>
-      <c r="G137" s="13" t="s">
+      <c r="G137" t="s">
         <v>748</v>
       </c>
-      <c r="H137" s="13" t="s">
+      <c r="H137" t="s">
         <v>749</v>
       </c>
-      <c r="I137" s="13" t="s">
+      <c r="I137" t="s">
         <v>750</v>
       </c>
-      <c r="J137" s="14" t="s">
+      <c r="J137" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K137" s="13" t="s">
+      <c r="K137" t="s">
         <v>1129</v>
       </c>
-      <c r="L137" s="14">
+      <c r="L137" s="13">
         <v>32</v>
       </c>
     </row>
     <row r="138" spans="1:12">
-      <c r="A138" s="13" t="s">
+      <c r="A138" t="s">
         <v>1188</v>
       </c>
-      <c r="B138" s="13" t="s">
+      <c r="B138" t="s">
         <v>593</v>
       </c>
       <c r="C138" s="6">
         <v>137</v>
       </c>
-      <c r="D138" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E138" s="13" t="s">
+      <c r="D138" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E138" t="s">
         <v>751</v>
       </c>
-      <c r="F138" s="13" t="s">
+      <c r="F138" t="s">
         <v>752</v>
       </c>
-      <c r="G138" s="13" t="s">
+      <c r="G138" t="s">
         <v>753</v>
       </c>
-      <c r="H138" s="13" t="s">
+      <c r="H138" t="s">
         <v>754</v>
       </c>
-      <c r="I138" s="13" t="s">
+      <c r="I138" t="s">
         <v>755</v>
       </c>
-      <c r="J138" s="14" t="s">
+      <c r="J138" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K138" s="13" t="s">
+      <c r="K138" t="s">
         <v>1130</v>
       </c>
-      <c r="L138" s="14">
+      <c r="L138" s="13">
         <v>33</v>
       </c>
     </row>
     <row r="139" spans="1:12">
-      <c r="A139" s="13" t="s">
+      <c r="A139" t="s">
         <v>1188</v>
       </c>
-      <c r="B139" s="13" t="s">
+      <c r="B139" t="s">
         <v>593</v>
       </c>
       <c r="C139" s="6">
         <v>138</v>
       </c>
-      <c r="D139" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E139" s="13" t="s">
+      <c r="D139" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E139" t="s">
         <v>756</v>
       </c>
-      <c r="F139" s="13" t="s">
+      <c r="F139" t="s">
         <v>757</v>
       </c>
-      <c r="G139" s="13" t="s">
+      <c r="G139" t="s">
         <v>758</v>
       </c>
-      <c r="H139" s="13" t="s">
+      <c r="H139" t="s">
         <v>759</v>
       </c>
-      <c r="I139" s="13" t="s">
+      <c r="I139" t="s">
         <v>760</v>
       </c>
-      <c r="J139" s="14" t="s">
+      <c r="J139" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K139" s="13" t="s">
+      <c r="K139" t="s">
         <v>1131</v>
       </c>
-      <c r="L139" s="14">
+      <c r="L139" s="13">
         <v>34</v>
       </c>
     </row>
     <row r="140" spans="1:12">
-      <c r="A140" s="13" t="s">
+      <c r="A140" t="s">
         <v>1188</v>
       </c>
-      <c r="B140" s="13" t="s">
+      <c r="B140" t="s">
         <v>593</v>
       </c>
       <c r="C140" s="2">
         <v>139</v>
       </c>
-      <c r="D140" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E140" s="13" t="s">
+      <c r="D140" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E140" t="s">
         <v>761</v>
       </c>
-      <c r="F140" s="13" t="s">
+      <c r="F140" t="s">
         <v>762</v>
       </c>
-      <c r="G140" s="13" t="s">
+      <c r="G140" t="s">
         <v>763</v>
       </c>
-      <c r="H140" s="13" t="s">
+      <c r="H140" t="s">
         <v>764</v>
       </c>
-      <c r="I140" s="13" t="s">
+      <c r="I140" t="s">
         <v>765</v>
       </c>
-      <c r="J140" s="14" t="s">
+      <c r="J140" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K140" s="13" t="s">
+      <c r="K140" t="s">
         <v>1132</v>
       </c>
-      <c r="L140" s="14">
+      <c r="L140" s="13">
         <v>35</v>
       </c>
     </row>
     <row r="141" spans="1:12">
-      <c r="A141" s="13" t="s">
+      <c r="A141" t="s">
         <v>1188</v>
       </c>
-      <c r="B141" s="13" t="s">
+      <c r="B141" t="s">
         <v>593</v>
       </c>
       <c r="C141" s="6">
         <v>140</v>
       </c>
-      <c r="D141" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E141" s="13" t="s">
+      <c r="D141" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E141" t="s">
         <v>766</v>
       </c>
-      <c r="F141" s="13" t="s">
+      <c r="F141" t="s">
         <v>767</v>
       </c>
-      <c r="G141" s="13" t="s">
+      <c r="G141" t="s">
         <v>768</v>
       </c>
-      <c r="H141" s="13" t="s">
+      <c r="H141" t="s">
         <v>769</v>
       </c>
-      <c r="I141" s="13" t="s">
+      <c r="I141" t="s">
         <v>770</v>
       </c>
-      <c r="J141" s="14" t="s">
+      <c r="J141" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K141" s="13" t="s">
+      <c r="K141" t="s">
         <v>1133</v>
       </c>
-      <c r="L141" s="14">
+      <c r="L141" s="13">
         <v>36</v>
       </c>
     </row>
     <row r="142" spans="1:12">
-      <c r="A142" s="13" t="s">
+      <c r="A142" t="s">
         <v>1188</v>
       </c>
-      <c r="B142" s="13" t="s">
+      <c r="B142" t="s">
         <v>593</v>
       </c>
       <c r="C142" s="6">
         <v>141</v>
       </c>
-      <c r="D142" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E142" s="13" t="s">
+      <c r="D142" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E142" t="s">
         <v>771</v>
       </c>
-      <c r="F142" s="13" t="s">
+      <c r="F142" t="s">
         <v>772</v>
       </c>
-      <c r="G142" s="13" t="s">
+      <c r="G142" t="s">
         <v>773</v>
       </c>
-      <c r="H142" s="13" t="s">
+      <c r="H142" t="s">
         <v>774</v>
       </c>
-      <c r="I142" s="13" t="s">
+      <c r="I142" t="s">
         <v>775</v>
       </c>
-      <c r="J142" s="14" t="s">
+      <c r="J142" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K142" s="13" t="s">
+      <c r="K142" t="s">
         <v>1134</v>
       </c>
-      <c r="L142" s="14">
+      <c r="L142" s="13">
         <v>37</v>
       </c>
     </row>
     <row r="143" spans="1:12">
-      <c r="A143" s="13" t="s">
+      <c r="A143" t="s">
         <v>1188</v>
       </c>
-      <c r="B143" s="13" t="s">
+      <c r="B143" t="s">
         <v>593</v>
       </c>
       <c r="C143" s="2">
         <v>142</v>
       </c>
-      <c r="D143" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E143" s="13" t="s">
+      <c r="D143" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E143" t="s">
         <v>776</v>
       </c>
-      <c r="F143" s="13" t="s">
+      <c r="F143" t="s">
         <v>777</v>
       </c>
-      <c r="G143" s="13" t="s">
+      <c r="G143" t="s">
         <v>363</v>
       </c>
-      <c r="H143" s="13" t="s">
+      <c r="H143" t="s">
         <v>778</v>
       </c>
-      <c r="I143" s="13" t="s">
+      <c r="I143" t="s">
         <v>111</v>
       </c>
-      <c r="J143" s="14" t="s">
+      <c r="J143" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K143" s="13" t="s">
+      <c r="K143" t="s">
         <v>1135</v>
       </c>
-      <c r="L143" s="14">
+      <c r="L143" s="13">
         <v>38</v>
       </c>
     </row>
     <row r="144" spans="1:12">
-      <c r="A144" s="13" t="s">
+      <c r="A144" t="s">
         <v>1188</v>
       </c>
-      <c r="B144" s="13" t="s">
+      <c r="B144" t="s">
         <v>593</v>
       </c>
       <c r="C144" s="6">
         <v>143</v>
       </c>
-      <c r="D144" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E144" s="13" t="s">
+      <c r="D144" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E144" t="s">
         <v>779</v>
       </c>
-      <c r="F144" s="13" t="s">
+      <c r="F144" t="s">
         <v>780</v>
       </c>
-      <c r="G144" s="13" t="s">
+      <c r="G144" t="s">
         <v>781</v>
       </c>
-      <c r="H144" s="13" t="s">
+      <c r="H144" t="s">
         <v>782</v>
       </c>
-      <c r="I144" s="13" t="s">
+      <c r="I144" t="s">
         <v>783</v>
       </c>
-      <c r="J144" s="14" t="s">
+      <c r="J144" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K144" s="13" t="s">
+      <c r="K144" t="s">
         <v>1136</v>
       </c>
-      <c r="L144" s="14">
+      <c r="L144" s="13">
         <v>39</v>
       </c>
     </row>
     <row r="145" spans="1:12">
-      <c r="A145" s="13" t="s">
+      <c r="A145" t="s">
         <v>1188</v>
       </c>
-      <c r="B145" s="13" t="s">
+      <c r="B145" t="s">
         <v>593</v>
       </c>
       <c r="C145" s="6">
         <v>144</v>
       </c>
-      <c r="D145" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="E145" s="13" t="s">
+      <c r="D145" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E145" t="s">
         <v>784</v>
       </c>
-      <c r="F145" s="13" t="s">
+      <c r="F145" t="s">
         <v>785</v>
       </c>
-      <c r="G145" s="13" t="s">
+      <c r="G145" t="s">
         <v>786</v>
       </c>
-      <c r="H145" s="13" t="s">
+      <c r="H145" t="s">
         <v>787</v>
       </c>
-      <c r="I145" s="13" t="s">
+      <c r="I145" t="s">
         <v>788</v>
       </c>
-      <c r="J145" s="14" t="s">
+      <c r="J145" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K145" s="13" t="s">
+      <c r="K145" t="s">
         <v>1137</v>
       </c>
-      <c r="L145" s="14">
+      <c r="L145" s="13">
         <v>40</v>
       </c>
     </row>
     <row r="146" spans="1:12">
-      <c r="A146" s="13" t="s">
+      <c r="A146" t="s">
         <v>1188</v>
       </c>
-      <c r="B146" s="13" t="s">
+      <c r="B146" t="s">
         <v>593</v>
       </c>
       <c r="C146" s="2">
         <v>145</v>
       </c>
-      <c r="D146" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E146" s="13" t="s">
+      <c r="D146" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E146" t="s">
         <v>789</v>
       </c>
-      <c r="F146" s="13" t="s">
+      <c r="F146" t="s">
         <v>790</v>
       </c>
-      <c r="G146" s="13" t="s">
+      <c r="G146" t="s">
         <v>791</v>
       </c>
-      <c r="H146" s="13" t="s">
+      <c r="H146" t="s">
         <v>198</v>
       </c>
-      <c r="I146" s="13" t="s">
+      <c r="I146" t="s">
         <v>792</v>
       </c>
-      <c r="J146" s="14" t="s">
+      <c r="J146" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K146" s="13" t="s">
+      <c r="K146" t="s">
         <v>1138</v>
       </c>
-      <c r="L146" s="14">
+      <c r="L146" s="13">
         <v>41</v>
       </c>
     </row>
     <row r="147" spans="1:12">
-      <c r="A147" s="13" t="s">
+      <c r="A147" t="s">
         <v>1188</v>
       </c>
-      <c r="B147" s="13" t="s">
+      <c r="B147" t="s">
         <v>593</v>
       </c>
       <c r="C147" s="6">
         <v>146</v>
       </c>
-      <c r="D147" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E147" s="13" t="s">
+      <c r="D147" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E147" t="s">
         <v>793</v>
       </c>
-      <c r="F147" s="13" t="s">
+      <c r="F147" t="s">
         <v>794</v>
       </c>
-      <c r="G147" s="13" t="s">
+      <c r="G147" t="s">
         <v>795</v>
       </c>
-      <c r="H147" s="13" t="s">
+      <c r="H147" t="s">
         <v>796</v>
       </c>
-      <c r="I147" s="13" t="s">
+      <c r="I147" t="s">
         <v>797</v>
       </c>
-      <c r="J147" s="14" t="s">
+      <c r="J147" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K147" s="13" t="s">
+      <c r="K147" t="s">
         <v>1129</v>
       </c>
-      <c r="L147" s="14">
+      <c r="L147" s="13">
         <v>42</v>
       </c>
     </row>
     <row r="148" spans="1:12">
-      <c r="A148" s="13" t="s">
+      <c r="A148" t="s">
         <v>1188</v>
       </c>
-      <c r="B148" s="13" t="s">
+      <c r="B148" t="s">
         <v>593</v>
       </c>
       <c r="C148" s="6">
         <v>147</v>
       </c>
-      <c r="D148" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E148" s="13" t="s">
+      <c r="D148" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E148" t="s">
         <v>798</v>
       </c>
-      <c r="F148" s="13" t="s">
+      <c r="F148" t="s">
         <v>799</v>
       </c>
-      <c r="G148" s="13" t="s">
+      <c r="G148" t="s">
         <v>800</v>
       </c>
-      <c r="H148" s="13" t="s">
+      <c r="H148" t="s">
         <v>801</v>
       </c>
-      <c r="I148" s="13" t="s">
+      <c r="I148" t="s">
         <v>802</v>
       </c>
-      <c r="J148" s="14" t="s">
+      <c r="J148" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K148" s="13" t="s">
+      <c r="K148" t="s">
         <v>1129</v>
       </c>
-      <c r="L148" s="14">
+      <c r="L148" s="13">
         <v>43</v>
       </c>
     </row>
     <row r="149" spans="1:12">
-      <c r="A149" s="13" t="s">
+      <c r="A149" t="s">
         <v>1188</v>
       </c>
-      <c r="B149" s="13" t="s">
+      <c r="B149" t="s">
         <v>593</v>
       </c>
       <c r="C149" s="2">
         <v>148</v>
       </c>
-      <c r="D149" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E149" s="13" t="s">
+      <c r="D149" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E149" t="s">
         <v>803</v>
       </c>
-      <c r="F149" s="13" t="s">
+      <c r="F149" t="s">
         <v>804</v>
       </c>
-      <c r="G149" s="13" t="s">
+      <c r="G149" t="s">
         <v>805</v>
       </c>
-      <c r="H149" s="13" t="s">
+      <c r="H149" t="s">
         <v>806</v>
       </c>
-      <c r="I149" s="13" t="s">
+      <c r="I149" t="s">
         <v>807</v>
       </c>
-      <c r="J149" s="14" t="s">
+      <c r="J149" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K149" s="13" t="s">
+      <c r="K149" t="s">
         <v>1139</v>
       </c>
-      <c r="L149" s="14">
+      <c r="L149" s="13">
         <v>44</v>
       </c>
     </row>
     <row r="150" spans="1:12">
-      <c r="A150" s="13" t="s">
+      <c r="A150" t="s">
         <v>1188</v>
       </c>
-      <c r="B150" s="13" t="s">
+      <c r="B150" t="s">
         <v>593</v>
       </c>
       <c r="C150" s="6">
         <v>149</v>
       </c>
-      <c r="D150" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E150" s="13" t="s">
+      <c r="D150" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E150" t="s">
         <v>808</v>
       </c>
-      <c r="F150" s="13" t="s">
+      <c r="F150" t="s">
         <v>809</v>
       </c>
-      <c r="G150" s="13" t="s">
+      <c r="G150" t="s">
         <v>810</v>
       </c>
-      <c r="H150" s="13" t="s">
+      <c r="H150" t="s">
         <v>811</v>
       </c>
-      <c r="I150" s="13" t="s">
+      <c r="I150" t="s">
         <v>812</v>
       </c>
-      <c r="J150" s="14" t="s">
+      <c r="J150" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K150" s="13" t="s">
+      <c r="K150" t="s">
         <v>1140</v>
       </c>
-      <c r="L150" s="14">
+      <c r="L150" s="13">
         <v>45</v>
       </c>
     </row>
     <row r="151" spans="1:12">
-      <c r="A151" s="13" t="s">
+      <c r="A151" t="s">
         <v>1188</v>
       </c>
-      <c r="B151" s="13" t="s">
+      <c r="B151" t="s">
         <v>593</v>
       </c>
       <c r="C151" s="6">
         <v>150</v>
       </c>
-      <c r="D151" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E151" s="13" t="s">
+      <c r="D151" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E151" t="s">
         <v>813</v>
       </c>
-      <c r="F151" s="13" t="s">
+      <c r="F151" t="s">
         <v>814</v>
       </c>
-      <c r="G151" s="13" t="s">
+      <c r="G151" t="s">
         <v>815</v>
       </c>
-      <c r="H151" s="13" t="s">
+      <c r="H151" t="s">
         <v>816</v>
       </c>
-      <c r="I151" s="13" t="s">
+      <c r="I151" t="s">
         <v>817</v>
       </c>
-      <c r="J151" s="14" t="s">
+      <c r="J151" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K151" s="13" t="s">
+      <c r="K151" t="s">
         <v>1141</v>
       </c>
-      <c r="L151" s="14">
+      <c r="L151" s="13">
         <v>46</v>
       </c>
     </row>
     <row r="152" spans="1:12">
-      <c r="A152" s="13" t="s">
+      <c r="A152" t="s">
         <v>1188</v>
       </c>
-      <c r="B152" s="13" t="s">
+      <c r="B152" t="s">
         <v>593</v>
       </c>
       <c r="C152" s="2">
         <v>151</v>
       </c>
-      <c r="D152" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E152" s="13" t="s">
+      <c r="D152" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E152" t="s">
         <v>818</v>
       </c>
-      <c r="F152" s="13" t="s">
+      <c r="F152" t="s">
         <v>819</v>
       </c>
-      <c r="G152" s="13" t="s">
+      <c r="G152" t="s">
         <v>820</v>
       </c>
-      <c r="H152" s="13" t="s">
+      <c r="H152" t="s">
         <v>821</v>
       </c>
-      <c r="I152" s="13" t="s">
+      <c r="I152" t="s">
         <v>822</v>
       </c>
-      <c r="J152" s="14" t="s">
+      <c r="J152" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K152" s="13" t="s">
+      <c r="K152" t="s">
         <v>1142</v>
       </c>
-      <c r="L152" s="14">
+      <c r="L152" s="13">
         <v>47</v>
       </c>
     </row>
     <row r="153" spans="1:12">
-      <c r="A153" s="13" t="s">
+      <c r="A153" t="s">
         <v>1188</v>
       </c>
-      <c r="B153" s="13" t="s">
+      <c r="B153" t="s">
         <v>593</v>
       </c>
       <c r="C153" s="6">
         <v>152</v>
       </c>
-      <c r="D153" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E153" s="13" t="s">
+      <c r="D153" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E153" t="s">
         <v>823</v>
       </c>
-      <c r="F153" s="13" t="s">
+      <c r="F153" t="s">
         <v>824</v>
       </c>
-      <c r="G153" s="13" t="s">
+      <c r="G153" t="s">
         <v>825</v>
       </c>
-      <c r="H153" s="13" t="s">
+      <c r="H153" t="s">
         <v>826</v>
       </c>
-      <c r="I153" s="13" t="s">
+      <c r="I153" t="s">
         <v>661</v>
       </c>
-      <c r="J153" s="14" t="s">
+      <c r="J153" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K153" s="13" t="s">
+      <c r="K153" t="s">
         <v>1129</v>
       </c>
-      <c r="L153" s="14">
+      <c r="L153" s="13">
         <v>48</v>
       </c>
     </row>
     <row r="154" spans="1:12">
-      <c r="A154" s="13" t="s">
+      <c r="A154" t="s">
         <v>1188</v>
       </c>
-      <c r="B154" s="13" t="s">
+      <c r="B154" t="s">
         <v>593</v>
       </c>
       <c r="C154" s="6">
         <v>153</v>
       </c>
-      <c r="D154" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E154" s="13" t="s">
+      <c r="D154" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E154" t="s">
         <v>827</v>
       </c>
-      <c r="F154" s="13" t="s">
+      <c r="F154" t="s">
         <v>828</v>
       </c>
-      <c r="G154" s="13" t="s">
+      <c r="G154" t="s">
         <v>829</v>
       </c>
-      <c r="H154" s="13" t="s">
+      <c r="H154" t="s">
         <v>830</v>
       </c>
-      <c r="I154" s="13" t="s">
+      <c r="I154" t="s">
         <v>831</v>
       </c>
-      <c r="J154" s="14" t="s">
+      <c r="J154" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K154" s="13" t="s">
+      <c r="K154" t="s">
         <v>1129</v>
       </c>
-      <c r="L154" s="14">
+      <c r="L154" s="13">
         <v>49</v>
       </c>
     </row>
     <row r="155" spans="1:12">
-      <c r="A155" s="13" t="s">
+      <c r="A155" t="s">
         <v>1188</v>
       </c>
-      <c r="B155" s="13" t="s">
+      <c r="B155" t="s">
         <v>593</v>
       </c>
       <c r="C155" s="2">
         <v>154</v>
       </c>
-      <c r="D155" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E155" s="13" t="s">
+      <c r="D155" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E155" t="s">
         <v>832</v>
       </c>
-      <c r="F155" s="13" t="s">
+      <c r="F155" t="s">
         <v>833</v>
       </c>
-      <c r="G155" s="13" t="s">
+      <c r="G155" t="s">
         <v>834</v>
       </c>
-      <c r="H155" s="13" t="s">
+      <c r="H155" t="s">
         <v>835</v>
       </c>
-      <c r="I155" s="13" t="s">
+      <c r="I155" t="s">
         <v>836</v>
       </c>
-      <c r="J155" s="14" t="s">
+      <c r="J155" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K155" s="13" t="s">
+      <c r="K155" t="s">
         <v>1143</v>
       </c>
-      <c r="L155" s="14">
+      <c r="L155" s="13">
         <v>50</v>
       </c>
     </row>
     <row r="156" spans="1:12">
-      <c r="A156" s="13" t="s">
+      <c r="A156" t="s">
         <v>1188</v>
       </c>
-      <c r="B156" s="13" t="s">
+      <c r="B156" t="s">
         <v>593</v>
       </c>
       <c r="C156" s="6">
         <v>155</v>
       </c>
-      <c r="D156" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E156" s="13" t="s">
+      <c r="D156" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E156" t="s">
         <v>837</v>
       </c>
-      <c r="F156" s="13" t="s">
+      <c r="F156" t="s">
         <v>838</v>
       </c>
-      <c r="G156" s="13" t="s">
+      <c r="G156" t="s">
         <v>839</v>
       </c>
-      <c r="H156" s="13" t="s">
+      <c r="H156" t="s">
         <v>840</v>
       </c>
-      <c r="I156" s="13" t="s">
+      <c r="I156" t="s">
         <v>841</v>
       </c>
-      <c r="J156" s="14" t="s">
+      <c r="J156" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K156" s="13" t="s">
+      <c r="K156" t="s">
         <v>1144</v>
       </c>
-      <c r="L156" s="14">
+      <c r="L156" s="13">
         <v>51</v>
       </c>
     </row>
     <row r="157" spans="1:12">
-      <c r="A157" s="13" t="s">
+      <c r="A157" t="s">
         <v>1188</v>
       </c>
-      <c r="B157" s="13" t="s">
+      <c r="B157" t="s">
         <v>593</v>
       </c>
       <c r="C157" s="6">
         <v>156</v>
       </c>
-      <c r="D157" s="13" t="s">
+      <c r="D157" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E157" t="s">
+        <v>842</v>
+      </c>
+      <c r="F157" t="s">
+        <v>843</v>
+      </c>
+      <c r="G157" t="s">
+        <v>844</v>
+      </c>
+      <c r="H157" t="s">
+        <v>845</v>
+      </c>
+      <c r="I157" t="s">
+        <v>846</v>
+      </c>
+      <c r="J157" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="K157" t="s">
+        <v>1145</v>
+      </c>
+      <c r="L157" s="13">
         <v>52</v>
       </c>
-      <c r="E157" s="13" t="s">
-        <v>842</v>
-      </c>
-      <c r="F157" s="13" t="s">
-        <v>843</v>
-      </c>
-      <c r="G157" s="13" t="s">
-        <v>844</v>
-      </c>
-      <c r="H157" s="13" t="s">
-        <v>845</v>
-      </c>
-      <c r="I157" s="13" t="s">
-        <v>846</v>
-      </c>
-      <c r="J157" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="K157" s="13" t="s">
-        <v>1145</v>
-      </c>
-      <c r="L157" s="14">
-        <v>52</v>
-      </c>
     </row>
     <row r="158" spans="1:12">
-      <c r="A158" s="13" t="s">
+      <c r="A158" t="s">
         <v>1188</v>
       </c>
-      <c r="B158" s="13" t="s">
+      <c r="B158" t="s">
         <v>593</v>
       </c>
       <c r="C158" s="2">
         <v>157</v>
       </c>
-      <c r="D158" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E158" s="13" t="s">
+      <c r="D158" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E158" t="s">
         <v>847</v>
       </c>
-      <c r="F158" s="13" t="s">
+      <c r="F158" t="s">
         <v>848</v>
       </c>
-      <c r="G158" s="13" t="s">
+      <c r="G158" t="s">
         <v>849</v>
       </c>
-      <c r="H158" s="13" t="s">
+      <c r="H158" t="s">
         <v>850</v>
       </c>
-      <c r="I158" s="13" t="s">
+      <c r="I158" t="s">
         <v>851</v>
       </c>
-      <c r="J158" s="14" t="s">
+      <c r="J158" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K158" s="13" t="s">
+      <c r="K158" t="s">
         <v>1146</v>
       </c>
-      <c r="L158" s="14">
+      <c r="L158" s="13">
         <v>53</v>
       </c>
     </row>
     <row r="159" spans="1:12">
-      <c r="A159" s="13" t="s">
+      <c r="A159" t="s">
         <v>1188</v>
       </c>
-      <c r="B159" s="13" t="s">
+      <c r="B159" t="s">
         <v>593</v>
       </c>
       <c r="C159" s="6">
         <v>158</v>
       </c>
-      <c r="D159" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E159" s="13" t="s">
+      <c r="D159" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E159" t="s">
         <v>852</v>
       </c>
-      <c r="F159" s="13" t="s">
+      <c r="F159" t="s">
         <v>853</v>
       </c>
-      <c r="G159" s="13" t="s">
+      <c r="G159" t="s">
         <v>854</v>
       </c>
-      <c r="H159" s="13" t="s">
+      <c r="H159" t="s">
         <v>855</v>
       </c>
-      <c r="I159" s="13" t="s">
+      <c r="I159" t="s">
         <v>97</v>
       </c>
-      <c r="J159" s="14" t="s">
+      <c r="J159" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K159" s="13" t="s">
+      <c r="K159" t="s">
         <v>1147</v>
       </c>
-      <c r="L159" s="14">
+      <c r="L159" s="13">
         <v>54</v>
       </c>
     </row>
     <row r="160" spans="1:12">
-      <c r="A160" s="13" t="s">
+      <c r="A160" t="s">
         <v>1188</v>
       </c>
-      <c r="B160" s="13" t="s">
+      <c r="B160" t="s">
         <v>593</v>
       </c>
       <c r="C160" s="6">
         <v>159</v>
       </c>
-      <c r="D160" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E160" s="13" t="s">
+      <c r="D160" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E160" t="s">
         <v>856</v>
       </c>
-      <c r="F160" s="13" t="s">
+      <c r="F160" t="s">
         <v>857</v>
       </c>
-      <c r="G160" s="13" t="s">
+      <c r="G160" t="s">
         <v>858</v>
       </c>
-      <c r="H160" s="13" t="s">
+      <c r="H160" t="s">
         <v>859</v>
       </c>
-      <c r="I160" s="13" t="s">
+      <c r="I160" t="s">
         <v>860</v>
       </c>
-      <c r="J160" s="14" t="s">
+      <c r="J160" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K160" s="13" t="s">
+      <c r="K160" t="s">
         <v>1148</v>
       </c>
-      <c r="L160" s="14">
+      <c r="L160" s="13">
         <v>55</v>
       </c>
     </row>
     <row r="161" spans="1:12">
-      <c r="A161" s="13" t="s">
+      <c r="A161" t="s">
         <v>1188</v>
       </c>
-      <c r="B161" s="13" t="s">
+      <c r="B161" t="s">
         <v>593</v>
       </c>
       <c r="C161" s="2">
         <v>160</v>
       </c>
-      <c r="D161" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E161" s="13" t="s">
+      <c r="D161" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E161" t="s">
         <v>861</v>
       </c>
-      <c r="F161" s="13" t="s">
+      <c r="F161" t="s">
         <v>862</v>
       </c>
-      <c r="G161" s="13" t="s">
+      <c r="G161" t="s">
         <v>863</v>
       </c>
-      <c r="H161" s="13" t="s">
+      <c r="H161" t="s">
         <v>864</v>
       </c>
-      <c r="I161" s="13" t="s">
+      <c r="I161" t="s">
         <v>865</v>
       </c>
-      <c r="J161" s="14" t="s">
+      <c r="J161" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K161" s="13" t="s">
+      <c r="K161" t="s">
         <v>1149</v>
       </c>
-      <c r="L161" s="14">
+      <c r="L161" s="13">
         <v>56</v>
       </c>
     </row>
     <row r="162" spans="1:12">
-      <c r="A162" s="13" t="s">
+      <c r="A162" t="s">
         <v>1188</v>
       </c>
-      <c r="B162" s="13" t="s">
+      <c r="B162" t="s">
         <v>593</v>
       </c>
       <c r="C162" s="6">
         <v>161</v>
       </c>
-      <c r="D162" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E162" s="13" t="s">
+      <c r="D162" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E162" t="s">
         <v>866</v>
       </c>
-      <c r="F162" s="13" t="s">
+      <c r="F162" t="s">
         <v>867</v>
       </c>
-      <c r="G162" s="13" t="s">
+      <c r="G162" t="s">
         <v>868</v>
       </c>
-      <c r="H162" s="13" t="s">
+      <c r="H162" t="s">
         <v>869</v>
       </c>
-      <c r="I162" s="13" t="s">
+      <c r="I162" t="s">
         <v>870</v>
       </c>
-      <c r="J162" s="14" t="s">
+      <c r="J162" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K162" s="13" t="s">
+      <c r="K162" t="s">
         <v>1150</v>
       </c>
-      <c r="L162" s="14">
+      <c r="L162" s="13">
         <v>57</v>
       </c>
     </row>
     <row r="163" spans="1:12">
-      <c r="A163" s="13" t="s">
+      <c r="A163" t="s">
         <v>1188</v>
       </c>
-      <c r="B163" s="13" t="s">
+      <c r="B163" t="s">
         <v>593</v>
       </c>
       <c r="C163" s="6">
         <v>162</v>
       </c>
-      <c r="D163" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E163" s="13" t="s">
+      <c r="D163" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E163" t="s">
         <v>871</v>
       </c>
-      <c r="F163" s="13" t="s">
+      <c r="F163" t="s">
         <v>872</v>
       </c>
-      <c r="G163" s="13" t="s">
+      <c r="G163" t="s">
         <v>873</v>
       </c>
-      <c r="H163" s="13" t="s">
+      <c r="H163" t="s">
         <v>874</v>
       </c>
-      <c r="I163" s="13" t="s">
+      <c r="I163" t="s">
         <v>875</v>
       </c>
-      <c r="J163" s="14" t="s">
+      <c r="J163" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K163" s="13" t="s">
+      <c r="K163" t="s">
         <v>1151</v>
       </c>
-      <c r="L163" s="14">
+      <c r="L163" s="13">
         <v>58</v>
       </c>
     </row>
     <row r="164" spans="1:12">
-      <c r="A164" s="13" t="s">
+      <c r="A164" t="s">
         <v>1188</v>
       </c>
-      <c r="B164" s="13" t="s">
+      <c r="B164" t="s">
         <v>593</v>
       </c>
       <c r="C164" s="2">
         <v>163</v>
       </c>
-      <c r="D164" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E164" s="13" t="s">
+      <c r="D164" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E164" t="s">
         <v>876</v>
       </c>
-      <c r="F164" s="13" t="s">
+      <c r="F164" t="s">
         <v>877</v>
       </c>
-      <c r="G164" s="13" t="s">
+      <c r="G164" t="s">
         <v>878</v>
       </c>
-      <c r="H164" s="13" t="s">
+      <c r="H164" t="s">
         <v>879</v>
       </c>
-      <c r="I164" s="13" t="s">
+      <c r="I164" t="s">
         <v>880</v>
       </c>
-      <c r="J164" s="14" t="s">
+      <c r="J164" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K164" s="13" t="s">
+      <c r="K164" t="s">
         <v>1152</v>
       </c>
-      <c r="L164" s="14">
+      <c r="L164" s="13">
         <v>59</v>
       </c>
     </row>
     <row r="165" spans="1:12">
-      <c r="A165" s="13" t="s">
+      <c r="A165" t="s">
         <v>1188</v>
       </c>
-      <c r="B165" s="13" t="s">
+      <c r="B165" t="s">
         <v>593</v>
       </c>
       <c r="C165" s="6">
         <v>164</v>
       </c>
-      <c r="D165" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E165" s="13" t="s">
+      <c r="D165" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E165" t="s">
         <v>881</v>
       </c>
-      <c r="F165" s="13" t="s">
+      <c r="F165" t="s">
         <v>882</v>
       </c>
-      <c r="G165" s="13" t="s">
+      <c r="G165" t="s">
         <v>883</v>
       </c>
-      <c r="H165" s="13" t="s">
+      <c r="H165" t="s">
         <v>884</v>
       </c>
-      <c r="I165" s="13" t="s">
+      <c r="I165" t="s">
         <v>885</v>
       </c>
-      <c r="J165" s="14" t="s">
+      <c r="J165" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K165" s="13" t="s">
+      <c r="K165" t="s">
         <v>1120</v>
       </c>
-      <c r="L165" s="14">
+      <c r="L165" s="13">
         <v>60</v>
       </c>
     </row>
     <row r="166" spans="1:12">
-      <c r="A166" s="13" t="s">
+      <c r="A166" t="s">
         <v>1188</v>
       </c>
-      <c r="B166" s="13" t="s">
+      <c r="B166" t="s">
         <v>593</v>
       </c>
       <c r="C166" s="6">
         <v>165</v>
       </c>
-      <c r="D166" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E166" s="13" t="s">
+      <c r="D166" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E166" t="s">
         <v>886</v>
       </c>
-      <c r="F166" s="13" t="s">
+      <c r="F166" t="s">
         <v>887</v>
       </c>
-      <c r="G166" s="13" t="s">
+      <c r="G166" t="s">
         <v>888</v>
       </c>
-      <c r="H166" s="13" t="s">
+      <c r="H166" t="s">
         <v>889</v>
       </c>
-      <c r="I166" s="13" t="s">
+      <c r="I166" t="s">
         <v>890</v>
       </c>
-      <c r="J166" s="14" t="s">
+      <c r="J166" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K166" s="13" t="s">
+      <c r="K166" t="s">
         <v>1120</v>
       </c>
-      <c r="L166" s="14">
+      <c r="L166" s="13">
         <v>61</v>
       </c>
     </row>
     <row r="167" spans="1:12">
-      <c r="A167" s="13" t="s">
+      <c r="A167" t="s">
         <v>1188</v>
       </c>
-      <c r="B167" s="13" t="s">
+      <c r="B167" t="s">
         <v>593</v>
       </c>
       <c r="C167" s="2">
         <v>166</v>
       </c>
-      <c r="D167" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E167" s="13" t="s">
+      <c r="D167" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E167" t="s">
         <v>891</v>
       </c>
-      <c r="F167" s="13" t="s">
+      <c r="F167" t="s">
         <v>892</v>
       </c>
-      <c r="G167" s="13" t="s">
+      <c r="G167" t="s">
         <v>893</v>
       </c>
-      <c r="H167" s="13" t="s">
+      <c r="H167" t="s">
         <v>894</v>
       </c>
-      <c r="I167" s="13" t="s">
+      <c r="I167" t="s">
         <v>895</v>
       </c>
-      <c r="J167" s="14" t="s">
+      <c r="J167" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K167" s="13" t="s">
+      <c r="K167" t="s">
         <v>1153</v>
       </c>
-      <c r="L167" s="14">
+      <c r="L167" s="13">
         <v>62</v>
       </c>
     </row>
     <row r="168" spans="1:12">
-      <c r="A168" s="13" t="s">
+      <c r="A168" t="s">
         <v>1188</v>
       </c>
-      <c r="B168" s="13" t="s">
+      <c r="B168" t="s">
         <v>593</v>
       </c>
       <c r="C168" s="6">
         <v>167</v>
       </c>
-      <c r="D168" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E168" s="13" t="s">
+      <c r="D168" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E168" t="s">
         <v>896</v>
       </c>
-      <c r="F168" s="13" t="s">
+      <c r="F168" t="s">
         <v>897</v>
       </c>
-      <c r="G168" s="13" t="s">
+      <c r="G168" t="s">
         <v>898</v>
       </c>
-      <c r="H168" s="13" t="s">
+      <c r="H168" t="s">
         <v>899</v>
       </c>
-      <c r="I168" s="13" t="s">
+      <c r="I168" t="s">
         <v>900</v>
       </c>
-      <c r="J168" s="14" t="s">
+      <c r="J168" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K168" s="13" t="s">
+      <c r="K168" t="s">
         <v>1119</v>
       </c>
-      <c r="L168" s="14">
+      <c r="L168" s="13">
         <v>63</v>
       </c>
     </row>
     <row r="169" spans="1:12">
-      <c r="A169" s="13" t="s">
+      <c r="A169" t="s">
         <v>1188</v>
       </c>
-      <c r="B169" s="13" t="s">
+      <c r="B169" t="s">
         <v>593</v>
       </c>
       <c r="C169" s="6">
         <v>168</v>
       </c>
-      <c r="D169" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E169" s="13" t="s">
+      <c r="D169" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E169" t="s">
         <v>901</v>
       </c>
-      <c r="F169" s="13" t="s">
+      <c r="F169" t="s">
         <v>902</v>
       </c>
-      <c r="G169" s="13" t="s">
+      <c r="G169" t="s">
         <v>903</v>
       </c>
-      <c r="H169" s="13" t="s">
+      <c r="H169" t="s">
         <v>904</v>
       </c>
-      <c r="I169" s="13" t="s">
+      <c r="I169" t="s">
         <v>710</v>
       </c>
-      <c r="J169" s="14" t="s">
+      <c r="J169" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K169" s="13" t="s">
+      <c r="K169" t="s">
         <v>1154</v>
       </c>
-      <c r="L169" s="14">
+      <c r="L169" s="13">
         <v>64</v>
       </c>
     </row>
     <row r="170" spans="1:12">
-      <c r="A170" s="13" t="s">
+      <c r="A170" t="s">
         <v>1188</v>
       </c>
-      <c r="B170" s="13" t="s">
+      <c r="B170" t="s">
         <v>593</v>
       </c>
       <c r="C170" s="2">
         <v>169</v>
       </c>
-      <c r="D170" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E170" s="13" t="s">
+      <c r="D170" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E170" t="s">
         <v>905</v>
       </c>
-      <c r="F170" s="13" t="s">
+      <c r="F170" t="s">
         <v>906</v>
       </c>
-      <c r="G170" s="13" t="s">
+      <c r="G170" t="s">
         <v>907</v>
       </c>
-      <c r="H170" s="13" t="s">
+      <c r="H170" t="s">
         <v>908</v>
       </c>
-      <c r="I170" s="13" t="s">
+      <c r="I170" t="s">
         <v>909</v>
       </c>
-      <c r="J170" s="14" t="s">
+      <c r="J170" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K170" s="13" t="s">
+      <c r="K170" t="s">
         <v>1155</v>
       </c>
-      <c r="L170" s="14">
+      <c r="L170" s="13">
         <v>65</v>
       </c>
     </row>
     <row r="171" spans="1:12">
-      <c r="A171" s="13" t="s">
+      <c r="A171" t="s">
         <v>1188</v>
       </c>
-      <c r="B171" s="13" t="s">
+      <c r="B171" t="s">
         <v>593</v>
       </c>
       <c r="C171" s="6">
         <v>170</v>
       </c>
-      <c r="D171" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E171" s="13" t="s">
+      <c r="D171" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E171" t="s">
         <v>910</v>
       </c>
-      <c r="F171" s="13" t="s">
+      <c r="F171" t="s">
         <v>911</v>
       </c>
-      <c r="G171" s="13" t="s">
+      <c r="G171" t="s">
         <v>912</v>
       </c>
-      <c r="H171" s="13" t="s">
+      <c r="H171" t="s">
         <v>913</v>
       </c>
-      <c r="I171" s="13" t="s">
+      <c r="I171" t="s">
         <v>914</v>
       </c>
-      <c r="J171" s="14" t="s">
+      <c r="J171" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K171" s="13" t="s">
+      <c r="K171" t="s">
         <v>1115</v>
       </c>
-      <c r="L171" s="14">
+      <c r="L171" s="13">
         <v>66</v>
       </c>
     </row>
     <row r="172" spans="1:12">
-      <c r="A172" s="13" t="s">
+      <c r="A172" t="s">
         <v>1188</v>
       </c>
-      <c r="B172" s="13" t="s">
+      <c r="B172" t="s">
         <v>593</v>
       </c>
       <c r="C172" s="6">
         <v>171</v>
       </c>
-      <c r="D172" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E172" s="13" t="s">
+      <c r="D172" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E172" t="s">
         <v>915</v>
       </c>
-      <c r="F172" s="13" t="s">
+      <c r="F172" t="s">
         <v>916</v>
       </c>
-      <c r="G172" s="13" t="s">
+      <c r="G172" t="s">
         <v>917</v>
       </c>
-      <c r="H172" s="13" t="s">
+      <c r="H172" t="s">
         <v>918</v>
       </c>
-      <c r="I172" s="13" t="s">
+      <c r="I172" t="s">
         <v>919</v>
       </c>
-      <c r="J172" s="14" t="s">
+      <c r="J172" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K172" s="13" t="s">
+      <c r="K172" t="s">
         <v>1132</v>
       </c>
-      <c r="L172" s="14">
+      <c r="L172" s="13">
         <v>67</v>
       </c>
     </row>
     <row r="173" spans="1:12">
-      <c r="A173" s="13" t="s">
+      <c r="A173" t="s">
         <v>1188</v>
       </c>
-      <c r="B173" s="13" t="s">
+      <c r="B173" t="s">
         <v>593</v>
       </c>
       <c r="C173" s="2">
         <v>172</v>
       </c>
-      <c r="D173" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E173" s="13" t="s">
+      <c r="D173" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E173" t="s">
         <v>920</v>
       </c>
-      <c r="F173" s="13" t="s">
+      <c r="F173" t="s">
         <v>921</v>
       </c>
-      <c r="G173" s="13" t="s">
+      <c r="G173" t="s">
         <v>922</v>
       </c>
-      <c r="H173" s="13" t="s">
+      <c r="H173" t="s">
         <v>923</v>
       </c>
-      <c r="I173" s="13" t="s">
+      <c r="I173" t="s">
         <v>924</v>
       </c>
-      <c r="J173" s="14" t="s">
+      <c r="J173" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K173" s="13" t="s">
+      <c r="K173" t="s">
         <v>1156</v>
       </c>
-      <c r="L173" s="14">
+      <c r="L173" s="13">
         <v>68</v>
       </c>
     </row>
     <row r="174" spans="1:12">
-      <c r="A174" s="13" t="s">
+      <c r="A174" t="s">
         <v>1188</v>
       </c>
-      <c r="B174" s="13" t="s">
+      <c r="B174" t="s">
         <v>593</v>
       </c>
       <c r="C174" s="6">
         <v>173</v>
       </c>
-      <c r="D174" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E174" s="13" t="s">
+      <c r="D174" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E174" t="s">
         <v>925</v>
       </c>
-      <c r="F174" s="13" t="s">
+      <c r="F174" t="s">
         <v>926</v>
       </c>
-      <c r="G174" s="13" t="s">
+      <c r="G174" t="s">
         <v>927</v>
       </c>
-      <c r="H174" s="13" t="s">
+      <c r="H174" t="s">
         <v>928</v>
       </c>
-      <c r="I174" s="13" t="s">
+      <c r="I174" t="s">
         <v>929</v>
       </c>
-      <c r="J174" s="14" t="s">
+      <c r="J174" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K174" s="13" t="s">
+      <c r="K174" t="s">
         <v>1157</v>
       </c>
-      <c r="L174" s="14">
+      <c r="L174" s="13">
         <v>69</v>
       </c>
     </row>
     <row r="175" spans="1:12">
-      <c r="A175" s="13" t="s">
+      <c r="A175" t="s">
         <v>1188</v>
       </c>
-      <c r="B175" s="13" t="s">
+      <c r="B175" t="s">
         <v>593</v>
       </c>
       <c r="C175" s="6">
         <v>174</v>
       </c>
-      <c r="D175" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E175" s="13" t="s">
+      <c r="D175" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E175" t="s">
         <v>930</v>
       </c>
-      <c r="F175" s="13" t="s">
+      <c r="F175" t="s">
         <v>931</v>
       </c>
-      <c r="G175" s="13" t="s">
+      <c r="G175" t="s">
         <v>932</v>
       </c>
-      <c r="H175" s="13" t="s">
+      <c r="H175" t="s">
         <v>933</v>
       </c>
-      <c r="I175" s="13" t="s">
+      <c r="I175" t="s">
         <v>934</v>
       </c>
-      <c r="J175" s="14" t="s">
+      <c r="J175" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K175" s="13" t="s">
+      <c r="K175" t="s">
         <v>1158</v>
       </c>
-      <c r="L175" s="14">
+      <c r="L175" s="13">
         <v>70</v>
       </c>
     </row>
     <row r="176" spans="1:12">
-      <c r="A176" s="13" t="s">
+      <c r="A176" t="s">
         <v>1188</v>
       </c>
-      <c r="B176" s="13" t="s">
+      <c r="B176" t="s">
         <v>593</v>
       </c>
       <c r="C176" s="2">
         <v>175</v>
       </c>
-      <c r="D176" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E176" s="13" t="s">
+      <c r="D176" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E176" t="s">
         <v>935</v>
       </c>
-      <c r="F176" s="13" t="s">
+      <c r="F176" t="s">
         <v>936</v>
       </c>
-      <c r="G176" s="13" t="s">
+      <c r="G176" t="s">
         <v>937</v>
       </c>
-      <c r="H176" s="13" t="s">
+      <c r="H176" t="s">
         <v>938</v>
       </c>
-      <c r="I176" s="13" t="s">
+      <c r="I176" t="s">
         <v>939</v>
       </c>
-      <c r="J176" s="14" t="s">
+      <c r="J176" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K176" s="13" t="s">
+      <c r="K176" t="s">
         <v>1159</v>
       </c>
-      <c r="L176" s="14">
+      <c r="L176" s="13">
         <v>71</v>
       </c>
     </row>
     <row r="177" spans="1:12">
-      <c r="A177" s="13" t="s">
+      <c r="A177" t="s">
         <v>1188</v>
       </c>
-      <c r="B177" s="13" t="s">
+      <c r="B177" t="s">
         <v>593</v>
       </c>
       <c r="C177" s="6">
         <v>176</v>
       </c>
-      <c r="D177" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E177" s="13" t="s">
+      <c r="D177" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E177" t="s">
         <v>940</v>
       </c>
-      <c r="F177" s="13" t="s">
+      <c r="F177" t="s">
         <v>941</v>
       </c>
-      <c r="G177" s="13" t="s">
+      <c r="G177" t="s">
         <v>942</v>
       </c>
-      <c r="H177" s="13" t="s">
+      <c r="H177" t="s">
         <v>943</v>
       </c>
-      <c r="I177" s="13" t="s">
+      <c r="I177" t="s">
         <v>944</v>
       </c>
-      <c r="J177" s="14" t="s">
+      <c r="J177" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K177" s="13" t="s">
+      <c r="K177" t="s">
         <v>1160</v>
       </c>
-      <c r="L177" s="14">
+      <c r="L177" s="13">
         <v>72</v>
       </c>
     </row>
     <row r="178" spans="1:12">
-      <c r="A178" s="13" t="s">
+      <c r="A178" t="s">
         <v>1188</v>
       </c>
-      <c r="B178" s="13" t="s">
+      <c r="B178" t="s">
         <v>593</v>
       </c>
       <c r="C178" s="6">
         <v>177</v>
       </c>
-      <c r="D178" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E178" s="13" t="s">
+      <c r="D178" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E178" t="s">
         <v>945</v>
       </c>
-      <c r="F178" s="13" t="s">
+      <c r="F178" t="s">
         <v>946</v>
       </c>
-      <c r="G178" s="13" t="s">
+      <c r="G178" t="s">
         <v>947</v>
       </c>
-      <c r="H178" s="13" t="s">
+      <c r="H178" t="s">
         <v>948</v>
       </c>
-      <c r="I178" s="13" t="s">
+      <c r="I178" t="s">
         <v>949</v>
       </c>
-      <c r="J178" s="14" t="s">
+      <c r="J178" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K178" s="13" t="s">
+      <c r="K178" t="s">
         <v>1161</v>
       </c>
-      <c r="L178" s="14">
+      <c r="L178" s="13">
         <v>73</v>
       </c>
     </row>
     <row r="179" spans="1:12">
-      <c r="A179" s="13" t="s">
+      <c r="A179" t="s">
         <v>1188</v>
       </c>
-      <c r="B179" s="13" t="s">
+      <c r="B179" t="s">
         <v>593</v>
       </c>
       <c r="C179" s="2">
         <v>178</v>
       </c>
-      <c r="D179" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E179" s="13" t="s">
+      <c r="D179" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E179" t="s">
         <v>950</v>
       </c>
-      <c r="F179" s="13" t="s">
+      <c r="F179" t="s">
         <v>951</v>
       </c>
-      <c r="G179" s="13" t="s">
+      <c r="G179" t="s">
         <v>952</v>
       </c>
-      <c r="H179" s="13" t="s">
+      <c r="H179" t="s">
         <v>953</v>
       </c>
-      <c r="I179" s="13" t="s">
+      <c r="I179" t="s">
         <v>954</v>
       </c>
-      <c r="J179" s="14" t="s">
+      <c r="J179" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K179" s="13" t="s">
+      <c r="K179" t="s">
         <v>1162</v>
       </c>
-      <c r="L179" s="14">
+      <c r="L179" s="13">
         <v>74</v>
       </c>
     </row>
     <row r="180" spans="1:12">
-      <c r="A180" s="13" t="s">
+      <c r="A180" t="s">
         <v>1188</v>
       </c>
-      <c r="B180" s="13" t="s">
+      <c r="B180" t="s">
         <v>593</v>
       </c>
       <c r="C180" s="6">
         <v>179</v>
       </c>
-      <c r="D180" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E180" s="13" t="s">
+      <c r="D180" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E180" t="s">
         <v>955</v>
       </c>
-      <c r="F180" s="13" t="s">
+      <c r="F180" t="s">
         <v>621</v>
       </c>
-      <c r="G180" s="13" t="s">
+      <c r="G180" t="s">
         <v>407</v>
       </c>
-      <c r="H180" s="13" t="s">
+      <c r="H180" t="s">
         <v>956</v>
       </c>
-      <c r="I180" s="13" t="s">
+      <c r="I180" t="s">
         <v>957</v>
       </c>
-      <c r="J180" s="14" t="s">
+      <c r="J180" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K180" s="13" t="s">
+      <c r="K180" t="s">
         <v>1163</v>
       </c>
-      <c r="L180" s="14">
+      <c r="L180" s="13">
         <v>75</v>
       </c>
     </row>
     <row r="181" spans="1:12">
-      <c r="A181" s="13" t="s">
+      <c r="A181" t="s">
         <v>1188</v>
       </c>
-      <c r="B181" s="13" t="s">
+      <c r="B181" t="s">
         <v>593</v>
       </c>
       <c r="C181" s="6">
         <v>180</v>
       </c>
-      <c r="D181" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="E181" s="13" t="s">
+      <c r="D181" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E181" t="s">
         <v>958</v>
       </c>
-      <c r="F181" s="13" t="s">
+      <c r="F181" t="s">
         <v>959</v>
       </c>
-      <c r="G181" s="13" t="s">
+      <c r="G181" t="s">
         <v>960</v>
       </c>
-      <c r="H181" s="13" t="s">
+      <c r="H181" t="s">
         <v>961</v>
       </c>
-      <c r="I181" s="13" t="s">
+      <c r="I181" t="s">
         <v>962</v>
       </c>
-      <c r="J181" s="14" t="s">
+      <c r="J181" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K181" s="13" t="s">
+      <c r="K181" t="s">
         <v>1164</v>
       </c>
-      <c r="L181" s="14">
+      <c r="L181" s="13">
         <v>76</v>
       </c>
     </row>
     <row r="182" spans="1:12">
-      <c r="A182" s="13" t="s">
+      <c r="A182" t="s">
         <v>1188</v>
       </c>
-      <c r="B182" s="13" t="s">
+      <c r="B182" t="s">
         <v>593</v>
       </c>
       <c r="C182" s="2">
         <v>181</v>
       </c>
-      <c r="D182" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E182" s="13" t="s">
+      <c r="D182" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E182" t="s">
         <v>963</v>
       </c>
-      <c r="F182" s="13" t="s">
+      <c r="F182" t="s">
         <v>964</v>
       </c>
-      <c r="G182" s="13" t="s">
+      <c r="G182" t="s">
         <v>965</v>
       </c>
-      <c r="H182" s="13" t="s">
+      <c r="H182" t="s">
         <v>966</v>
       </c>
-      <c r="I182" s="13" t="s">
+      <c r="I182" t="s">
         <v>967</v>
       </c>
-      <c r="J182" s="14" t="s">
+      <c r="J182" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K182" s="13" t="s">
+      <c r="K182" t="s">
         <v>1104</v>
       </c>
-      <c r="L182" s="14">
+      <c r="L182" s="13">
         <v>77</v>
       </c>
     </row>
     <row r="183" spans="1:12">
-      <c r="A183" s="13" t="s">
+      <c r="A183" t="s">
         <v>1188</v>
       </c>
-      <c r="B183" s="13" t="s">
+      <c r="B183" t="s">
         <v>593</v>
       </c>
       <c r="C183" s="6">
         <v>182</v>
       </c>
-      <c r="D183" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E183" s="13" t="s">
+      <c r="D183" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E183" t="s">
         <v>968</v>
       </c>
-      <c r="F183" s="13" t="s">
+      <c r="F183" t="s">
         <v>969</v>
       </c>
-      <c r="G183" s="13" t="s">
+      <c r="G183" t="s">
         <v>970</v>
       </c>
-      <c r="H183" s="13" t="s">
+      <c r="H183" t="s">
         <v>971</v>
       </c>
-      <c r="I183" s="13" t="s">
+      <c r="I183" t="s">
         <v>972</v>
       </c>
-      <c r="J183" s="14" t="s">
+      <c r="J183" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K183" s="13" t="s">
+      <c r="K183" t="s">
         <v>1165</v>
       </c>
-      <c r="L183" s="14">
+      <c r="L183" s="13">
         <v>78</v>
       </c>
     </row>
     <row r="184" spans="1:12">
-      <c r="A184" s="13" t="s">
+      <c r="A184" t="s">
         <v>1188</v>
       </c>
-      <c r="B184" s="13" t="s">
+      <c r="B184" t="s">
         <v>593</v>
       </c>
       <c r="C184" s="6">
         <v>183</v>
       </c>
-      <c r="D184" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E184" s="13" t="s">
+      <c r="D184" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E184" t="s">
         <v>973</v>
       </c>
-      <c r="F184" s="13" t="s">
+      <c r="F184" t="s">
         <v>974</v>
       </c>
-      <c r="G184" s="13" t="s">
+      <c r="G184" t="s">
         <v>975</v>
       </c>
-      <c r="H184" s="13" t="s">
+      <c r="H184" t="s">
         <v>976</v>
       </c>
-      <c r="I184" s="13" t="s">
+      <c r="I184" t="s">
         <v>977</v>
       </c>
-      <c r="J184" s="14" t="s">
+      <c r="J184" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K184" s="13" t="s">
+      <c r="K184" t="s">
         <v>1166</v>
       </c>
-      <c r="L184" s="14">
+      <c r="L184" s="13">
         <v>79</v>
       </c>
     </row>
     <row r="185" spans="1:12">
-      <c r="A185" s="13" t="s">
+      <c r="A185" t="s">
         <v>1188</v>
       </c>
-      <c r="B185" s="13" t="s">
+      <c r="B185" t="s">
         <v>593</v>
       </c>
       <c r="C185" s="2">
         <v>184</v>
       </c>
-      <c r="D185" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E185" s="13" t="s">
+      <c r="D185" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E185" t="s">
         <v>978</v>
       </c>
-      <c r="F185" s="13" t="s">
+      <c r="F185" t="s">
         <v>979</v>
       </c>
-      <c r="G185" s="13" t="s">
+      <c r="G185" t="s">
         <v>980</v>
       </c>
-      <c r="H185" s="13" t="s">
+      <c r="H185" t="s">
         <v>981</v>
       </c>
-      <c r="I185" s="13" t="s">
+      <c r="I185" t="s">
         <v>982</v>
       </c>
-      <c r="J185" s="14" t="s">
+      <c r="J185" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K185" s="13" t="s">
+      <c r="K185" t="s">
         <v>1167</v>
       </c>
-      <c r="L185" s="14">
+      <c r="L185" s="13">
         <v>80</v>
       </c>
     </row>
     <row r="186" spans="1:12">
-      <c r="A186" s="13" t="s">
+      <c r="A186" t="s">
         <v>1188</v>
       </c>
-      <c r="B186" s="13" t="s">
+      <c r="B186" t="s">
         <v>593</v>
       </c>
       <c r="C186" s="6">
         <v>185</v>
       </c>
-      <c r="D186" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E186" s="13" t="s">
+      <c r="D186" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E186" t="s">
         <v>983</v>
       </c>
-      <c r="F186" s="13" t="s">
+      <c r="F186" t="s">
         <v>984</v>
       </c>
-      <c r="G186" s="13" t="s">
+      <c r="G186" t="s">
         <v>985</v>
       </c>
-      <c r="H186" s="13" t="s">
+      <c r="H186" t="s">
         <v>986</v>
       </c>
-      <c r="I186" s="13" t="s">
+      <c r="I186" t="s">
         <v>987</v>
       </c>
-      <c r="J186" s="14" t="s">
+      <c r="J186" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K186" s="13" t="s">
+      <c r="K186" t="s">
         <v>1155</v>
       </c>
-      <c r="L186" s="14">
+      <c r="L186" s="13">
         <v>81</v>
       </c>
     </row>
     <row r="187" spans="1:12">
-      <c r="A187" s="13" t="s">
+      <c r="A187" t="s">
         <v>1188</v>
       </c>
-      <c r="B187" s="13" t="s">
+      <c r="B187" t="s">
         <v>593</v>
       </c>
       <c r="C187" s="6">
         <v>186</v>
       </c>
-      <c r="D187" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E187" s="13" t="s">
+      <c r="D187" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E187" t="s">
         <v>988</v>
       </c>
-      <c r="F187" s="13" t="s">
+      <c r="F187" t="s">
         <v>989</v>
       </c>
-      <c r="G187" s="13" t="s">
+      <c r="G187" t="s">
         <v>990</v>
       </c>
-      <c r="H187" s="13" t="s">
+      <c r="H187" t="s">
         <v>991</v>
       </c>
-      <c r="I187" s="13" t="s">
+      <c r="I187" t="s">
         <v>992</v>
       </c>
-      <c r="J187" s="14" t="s">
+      <c r="J187" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K187" s="13" t="s">
+      <c r="K187" t="s">
         <v>1168</v>
       </c>
-      <c r="L187" s="14">
+      <c r="L187" s="13">
         <v>82</v>
       </c>
     </row>
     <row r="188" spans="1:12">
-      <c r="A188" s="13" t="s">
+      <c r="A188" t="s">
         <v>1188</v>
       </c>
-      <c r="B188" s="13" t="s">
+      <c r="B188" t="s">
         <v>593</v>
       </c>
       <c r="C188" s="2">
         <v>187</v>
       </c>
-      <c r="D188" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E188" s="13" t="s">
+      <c r="D188" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E188" t="s">
         <v>993</v>
       </c>
-      <c r="F188" s="13" t="s">
+      <c r="F188" t="s">
         <v>994</v>
       </c>
-      <c r="G188" s="13" t="s">
+      <c r="G188" t="s">
         <v>995</v>
       </c>
-      <c r="H188" s="13" t="s">
+      <c r="H188" t="s">
         <v>996</v>
       </c>
-      <c r="I188" s="13" t="s">
+      <c r="I188" t="s">
         <v>997</v>
       </c>
-      <c r="J188" s="14" t="s">
+      <c r="J188" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K188" s="13" t="s">
+      <c r="K188" t="s">
         <v>1169</v>
       </c>
-      <c r="L188" s="14">
+      <c r="L188" s="13">
         <v>83</v>
       </c>
     </row>
     <row r="189" spans="1:12">
-      <c r="A189" s="13" t="s">
+      <c r="A189" t="s">
         <v>1188</v>
       </c>
-      <c r="B189" s="13" t="s">
+      <c r="B189" t="s">
         <v>593</v>
       </c>
       <c r="C189" s="6">
         <v>188</v>
       </c>
-      <c r="D189" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E189" s="13" t="s">
+      <c r="D189" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E189" t="s">
         <v>998</v>
       </c>
-      <c r="F189" s="13" t="s">
+      <c r="F189" t="s">
         <v>999</v>
       </c>
-      <c r="G189" s="13" t="s">
+      <c r="G189" t="s">
         <v>1000</v>
       </c>
-      <c r="H189" s="13" t="s">
+      <c r="H189" t="s">
         <v>1001</v>
       </c>
-      <c r="I189" s="13" t="s">
+      <c r="I189" t="s">
         <v>1002</v>
       </c>
-      <c r="J189" s="14" t="s">
+      <c r="J189" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K189" s="13" t="s">
+      <c r="K189" t="s">
         <v>1170</v>
       </c>
-      <c r="L189" s="14">
+      <c r="L189" s="13">
         <v>84</v>
       </c>
     </row>
     <row r="190" spans="1:12">
-      <c r="A190" s="13" t="s">
+      <c r="A190" t="s">
         <v>1188</v>
       </c>
-      <c r="B190" s="13" t="s">
+      <c r="B190" t="s">
         <v>593</v>
       </c>
       <c r="C190" s="6">
         <v>189</v>
       </c>
-      <c r="D190" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E190" s="13" t="s">
+      <c r="D190" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E190" t="s">
         <v>1003</v>
       </c>
-      <c r="F190" s="13" t="s">
+      <c r="F190" t="s">
         <v>1004</v>
       </c>
-      <c r="G190" s="13" t="s">
+      <c r="G190" t="s">
         <v>1005</v>
       </c>
-      <c r="H190" s="13" t="s">
+      <c r="H190" t="s">
         <v>1006</v>
       </c>
-      <c r="I190" s="13" t="s">
+      <c r="I190" t="s">
         <v>1007</v>
       </c>
-      <c r="J190" s="14" t="s">
+      <c r="J190" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K190" s="13" t="s">
+      <c r="K190" t="s">
         <v>1171</v>
       </c>
-      <c r="L190" s="14">
+      <c r="L190" s="13">
         <v>85</v>
       </c>
     </row>
     <row r="191" spans="1:12">
-      <c r="A191" s="13" t="s">
+      <c r="A191" t="s">
         <v>1188</v>
       </c>
-      <c r="B191" s="13" t="s">
+      <c r="B191" t="s">
         <v>593</v>
       </c>
       <c r="C191" s="2">
         <v>190</v>
       </c>
-      <c r="D191" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="E191" s="13" t="s">
+      <c r="D191" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E191" t="s">
         <v>1008</v>
       </c>
-      <c r="F191" s="13" t="s">
+      <c r="F191" t="s">
         <v>1009</v>
       </c>
-      <c r="G191" s="13" t="s">
+      <c r="G191" t="s">
         <v>1010</v>
       </c>
-      <c r="H191" s="13" t="s">
+      <c r="H191" t="s">
         <v>1011</v>
       </c>
-      <c r="I191" s="13" t="s">
+      <c r="I191" t="s">
         <v>1012</v>
       </c>
-      <c r="J191" s="14" t="s">
+      <c r="J191" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K191" s="13" t="s">
+      <c r="K191" t="s">
         <v>1172</v>
       </c>
-      <c r="L191" s="14">
+      <c r="L191" s="13">
         <v>86</v>
       </c>
     </row>
     <row r="192" spans="1:12">
-      <c r="A192" s="13" t="s">
+      <c r="A192" t="s">
         <v>1188</v>
       </c>
-      <c r="B192" s="13" t="s">
+      <c r="B192" t="s">
         <v>593</v>
       </c>
       <c r="C192" s="6">
         <v>191</v>
       </c>
-      <c r="D192" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E192" s="13" t="s">
+      <c r="D192" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E192" t="s">
         <v>1013</v>
       </c>
-      <c r="F192" s="13" t="s">
+      <c r="F192" t="s">
         <v>1014</v>
       </c>
-      <c r="G192" s="13" t="s">
+      <c r="G192" t="s">
         <v>1015</v>
       </c>
-      <c r="H192" s="13" t="s">
+      <c r="H192" t="s">
         <v>1016</v>
       </c>
-      <c r="I192" s="13" t="s">
+      <c r="I192" t="s">
         <v>1017</v>
       </c>
-      <c r="J192" s="14" t="s">
+      <c r="J192" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K192" s="13" t="s">
+      <c r="K192" t="s">
         <v>1173</v>
       </c>
-      <c r="L192" s="14">
+      <c r="L192" s="13">
         <v>87</v>
       </c>
     </row>
     <row r="193" spans="1:12">
-      <c r="A193" s="13" t="s">
+      <c r="A193" t="s">
         <v>1188</v>
       </c>
-      <c r="B193" s="13" t="s">
+      <c r="B193" t="s">
         <v>593</v>
       </c>
       <c r="C193" s="6">
         <v>192</v>
       </c>
-      <c r="D193" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E193" s="13" t="s">
+      <c r="D193" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E193" t="s">
         <v>1018</v>
       </c>
-      <c r="F193" s="13" t="s">
+      <c r="F193" t="s">
         <v>1019</v>
       </c>
-      <c r="G193" s="13" t="s">
+      <c r="G193" t="s">
         <v>1020</v>
       </c>
-      <c r="H193" s="13" t="s">
+      <c r="H193" t="s">
         <v>1021</v>
       </c>
-      <c r="I193" s="13" t="s">
+      <c r="I193" t="s">
         <v>1022</v>
       </c>
-      <c r="J193" s="14" t="s">
+      <c r="J193" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K193" s="13" t="s">
+      <c r="K193" t="s">
         <v>1174</v>
       </c>
-      <c r="L193" s="14">
+      <c r="L193" s="13">
         <v>88</v>
       </c>
     </row>
     <row r="194" spans="1:12">
-      <c r="A194" s="13" t="s">
+      <c r="A194" t="s">
         <v>1188</v>
       </c>
-      <c r="B194" s="13" t="s">
+      <c r="B194" t="s">
         <v>593</v>
       </c>
       <c r="C194" s="2">
         <v>193</v>
       </c>
-      <c r="D194" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E194" s="13" t="s">
+      <c r="D194" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E194" t="s">
         <v>1023</v>
       </c>
-      <c r="F194" s="13" t="s">
+      <c r="F194" t="s">
         <v>1024</v>
       </c>
-      <c r="G194" s="13" t="s">
+      <c r="G194" t="s">
         <v>1025</v>
       </c>
-      <c r="H194" s="13" t="s">
+      <c r="H194" t="s">
         <v>1026</v>
       </c>
-      <c r="I194" s="13" t="s">
+      <c r="I194" t="s">
         <v>1027</v>
       </c>
-      <c r="J194" s="14" t="s">
+      <c r="J194" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K194" s="13" t="s">
+      <c r="K194" t="s">
         <v>1129</v>
       </c>
-      <c r="L194" s="14">
+      <c r="L194" s="13">
         <v>89</v>
       </c>
     </row>
     <row r="195" spans="1:12">
-      <c r="A195" s="13" t="s">
+      <c r="A195" t="s">
         <v>1188</v>
       </c>
-      <c r="B195" s="13" t="s">
+      <c r="B195" t="s">
         <v>593</v>
       </c>
       <c r="C195" s="6">
         <v>194</v>
       </c>
-      <c r="D195" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E195" s="13" t="s">
+      <c r="D195" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E195" t="s">
         <v>1028</v>
       </c>
-      <c r="F195" s="13" t="s">
+      <c r="F195" t="s">
         <v>1029</v>
       </c>
-      <c r="G195" s="13" t="s">
+      <c r="G195" t="s">
         <v>1030</v>
       </c>
-      <c r="H195" s="13" t="s">
+      <c r="H195" t="s">
         <v>1031</v>
       </c>
-      <c r="I195" s="13" t="s">
+      <c r="I195" t="s">
         <v>1032</v>
       </c>
-      <c r="J195" s="14" t="s">
+      <c r="J195" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K195" s="13" t="s">
+      <c r="K195" t="s">
         <v>1175</v>
       </c>
-      <c r="L195" s="14">
+      <c r="L195" s="13">
         <v>90</v>
       </c>
     </row>
     <row r="196" spans="1:12">
-      <c r="A196" s="13" t="s">
+      <c r="A196" t="s">
         <v>1188</v>
       </c>
-      <c r="B196" s="13" t="s">
+      <c r="B196" t="s">
         <v>593</v>
       </c>
       <c r="C196" s="6">
         <v>195</v>
       </c>
-      <c r="D196" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E196" s="13" t="s">
+      <c r="D196" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E196" t="s">
         <v>1033</v>
       </c>
-      <c r="F196" s="13" t="s">
+      <c r="F196" t="s">
         <v>1034</v>
       </c>
-      <c r="G196" s="13" t="s">
+      <c r="G196" t="s">
         <v>802</v>
       </c>
-      <c r="H196" s="13" t="s">
+      <c r="H196" t="s">
         <v>1035</v>
       </c>
-      <c r="I196" s="13" t="s">
+      <c r="I196" t="s">
         <v>1036</v>
       </c>
-      <c r="J196" s="14" t="s">
+      <c r="J196" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K196" s="13" t="s">
+      <c r="K196" t="s">
         <v>1176</v>
       </c>
-      <c r="L196" s="14">
+      <c r="L196" s="13">
         <v>91</v>
       </c>
     </row>
     <row r="197" spans="1:12">
-      <c r="A197" s="13" t="s">
+      <c r="A197" t="s">
         <v>1188</v>
       </c>
-      <c r="B197" s="13" t="s">
+      <c r="B197" t="s">
         <v>593</v>
       </c>
       <c r="C197" s="2">
         <v>196</v>
       </c>
-      <c r="D197" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E197" s="13" t="s">
+      <c r="D197" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E197" t="s">
         <v>1037</v>
       </c>
-      <c r="F197" s="13" t="s">
+      <c r="F197" t="s">
         <v>1038</v>
       </c>
-      <c r="G197" s="13" t="s">
+      <c r="G197" t="s">
         <v>1039</v>
       </c>
-      <c r="H197" s="13" t="s">
+      <c r="H197" t="s">
         <v>1040</v>
       </c>
-      <c r="I197" s="13" t="s">
+      <c r="I197" t="s">
         <v>1041</v>
       </c>
-      <c r="J197" s="14" t="s">
+      <c r="J197" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K197" s="13" t="s">
+      <c r="K197" t="s">
         <v>1177</v>
       </c>
-      <c r="L197" s="14">
+      <c r="L197" s="13">
         <v>92</v>
       </c>
     </row>
     <row r="198" spans="1:12">
-      <c r="A198" s="13" t="s">
+      <c r="A198" t="s">
         <v>1188</v>
       </c>
-      <c r="B198" s="13" t="s">
+      <c r="B198" t="s">
         <v>593</v>
       </c>
       <c r="C198" s="6">
         <v>197</v>
       </c>
-      <c r="D198" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E198" s="13" t="s">
+      <c r="D198" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E198" t="s">
         <v>1042</v>
       </c>
-      <c r="F198" s="13" t="s">
+      <c r="F198" t="s">
         <v>1043</v>
       </c>
-      <c r="G198" s="13" t="s">
+      <c r="G198" t="s">
         <v>1044</v>
       </c>
-      <c r="H198" s="13" t="s">
+      <c r="H198" t="s">
         <v>1045</v>
       </c>
-      <c r="I198" s="13" t="s">
+      <c r="I198" t="s">
         <v>1046</v>
       </c>
-      <c r="J198" s="14" t="s">
+      <c r="J198" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K198" s="13" t="s">
+      <c r="K198" t="s">
         <v>1178</v>
       </c>
-      <c r="L198" s="14">
+      <c r="L198" s="13">
         <v>93</v>
       </c>
     </row>
     <row r="199" spans="1:12">
-      <c r="A199" s="13" t="s">
+      <c r="A199" t="s">
         <v>1188</v>
       </c>
-      <c r="B199" s="13" t="s">
+      <c r="B199" t="s">
         <v>593</v>
       </c>
       <c r="C199" s="6">
         <v>198</v>
       </c>
-      <c r="D199" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E199" s="13" t="s">
+      <c r="D199" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E199" t="s">
         <v>1047</v>
       </c>
-      <c r="F199" s="13" t="s">
+      <c r="F199" t="s">
         <v>1048</v>
       </c>
-      <c r="G199" s="13" t="s">
+      <c r="G199" t="s">
         <v>1049</v>
       </c>
-      <c r="H199" s="13" t="s">
+      <c r="H199" t="s">
         <v>1050</v>
       </c>
-      <c r="I199" s="13" t="s">
+      <c r="I199" t="s">
         <v>1051</v>
       </c>
-      <c r="J199" s="14" t="s">
+      <c r="J199" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K199" s="13" t="s">
+      <c r="K199" t="s">
         <v>1179</v>
       </c>
-      <c r="L199" s="14">
+      <c r="L199" s="13">
         <v>94</v>
       </c>
     </row>
     <row r="200" spans="1:12">
-      <c r="A200" s="13" t="s">
+      <c r="A200" t="s">
         <v>1188</v>
       </c>
-      <c r="B200" s="13" t="s">
+      <c r="B200" t="s">
         <v>593</v>
       </c>
       <c r="C200" s="2">
         <v>199</v>
       </c>
-      <c r="D200" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E200" s="13" t="s">
+      <c r="D200" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E200" t="s">
         <v>1052</v>
       </c>
-      <c r="F200" s="13" t="s">
+      <c r="F200" t="s">
         <v>1053</v>
       </c>
-      <c r="G200" s="13" t="s">
+      <c r="G200" t="s">
         <v>1054</v>
       </c>
-      <c r="H200" s="13" t="s">
+      <c r="H200" t="s">
         <v>1055</v>
       </c>
-      <c r="I200" s="13" t="s">
+      <c r="I200" t="s">
         <v>1056</v>
       </c>
-      <c r="J200" s="14" t="s">
+      <c r="J200" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K200" s="13" t="s">
+      <c r="K200" t="s">
         <v>1180</v>
       </c>
-      <c r="L200" s="14">
+      <c r="L200" s="13">
         <v>95</v>
       </c>
     </row>
     <row r="201" spans="1:12">
-      <c r="A201" s="13" t="s">
+      <c r="A201" t="s">
         <v>1188</v>
       </c>
-      <c r="B201" s="13" t="s">
+      <c r="B201" t="s">
         <v>593</v>
       </c>
       <c r="C201" s="6">
         <v>200</v>
       </c>
-      <c r="D201" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="E201" s="13" t="s">
+      <c r="D201" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E201" t="s">
         <v>1057</v>
       </c>
-      <c r="F201" s="13" t="s">
+      <c r="F201" t="s">
         <v>1058</v>
       </c>
-      <c r="G201" s="13" t="s">
+      <c r="G201" t="s">
         <v>1059</v>
       </c>
-      <c r="H201" s="13" t="s">
+      <c r="H201" t="s">
         <v>1060</v>
       </c>
-      <c r="I201" s="13" t="s">
+      <c r="I201" t="s">
         <v>1061</v>
       </c>
-      <c r="J201" s="14" t="s">
+      <c r="J201" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K201" s="13" t="s">
+      <c r="K201" t="s">
         <v>1181</v>
       </c>
-      <c r="L201" s="14">
+      <c r="L201" s="13">
         <v>96</v>
       </c>
     </row>
     <row r="202" spans="1:12">
-      <c r="A202" s="13" t="s">
+      <c r="A202" t="s">
         <v>1188</v>
       </c>
-      <c r="B202" s="13" t="s">
+      <c r="B202" t="s">
         <v>593</v>
       </c>
       <c r="C202" s="6">
         <v>201</v>
       </c>
-      <c r="D202" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="E202" s="13" t="s">
+      <c r="D202" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E202" t="s">
         <v>1062</v>
       </c>
-      <c r="F202" s="13" t="s">
+      <c r="F202" t="s">
         <v>1063</v>
       </c>
-      <c r="G202" s="13" t="s">
+      <c r="G202" t="s">
         <v>1064</v>
       </c>
-      <c r="H202" s="13" t="s">
+      <c r="H202" t="s">
         <v>1065</v>
       </c>
-      <c r="I202" s="13" t="s">
+      <c r="I202" t="s">
         <v>1066</v>
       </c>
-      <c r="J202" s="14" t="s">
+      <c r="J202" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K202" s="13" t="s">
+      <c r="K202" t="s">
         <v>1182</v>
       </c>
-      <c r="L202" s="14">
+      <c r="L202" s="13">
         <v>97</v>
       </c>
     </row>
     <row r="203" spans="1:12">
-      <c r="A203" s="13" t="s">
+      <c r="A203" t="s">
         <v>1188</v>
       </c>
-      <c r="B203" s="13" t="s">
+      <c r="B203" t="s">
         <v>593</v>
       </c>
       <c r="C203" s="2">
         <v>202</v>
       </c>
-      <c r="D203" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E203" s="13" t="s">
+      <c r="D203" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E203" t="s">
         <v>1067</v>
       </c>
-      <c r="F203" s="13" t="s">
+      <c r="F203" t="s">
         <v>1068</v>
       </c>
-      <c r="G203" s="13" t="s">
+      <c r="G203" t="s">
         <v>1069</v>
       </c>
-      <c r="H203" s="13" t="s">
+      <c r="H203" t="s">
         <v>1070</v>
       </c>
-      <c r="I203" s="13" t="s">
+      <c r="I203" t="s">
         <v>1071</v>
       </c>
-      <c r="J203" s="14" t="s">
+      <c r="J203" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K203" s="13" t="s">
+      <c r="K203" t="s">
         <v>1183</v>
       </c>
-      <c r="L203" s="14">
+      <c r="L203" s="13">
         <v>98</v>
       </c>
     </row>
     <row r="204" spans="1:12">
-      <c r="A204" s="13" t="s">
+      <c r="A204" t="s">
         <v>1188</v>
       </c>
-      <c r="B204" s="13" t="s">
+      <c r="B204" t="s">
         <v>593</v>
       </c>
       <c r="C204" s="6">
         <v>203</v>
       </c>
-      <c r="D204" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E204" s="13" t="s">
+      <c r="D204" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E204" t="s">
         <v>1072</v>
       </c>
-      <c r="F204" s="13" t="s">
+      <c r="F204" t="s">
         <v>1073</v>
       </c>
-      <c r="G204" s="13" t="s">
+      <c r="G204" t="s">
         <v>1074</v>
       </c>
-      <c r="H204" s="13" t="s">
+      <c r="H204" t="s">
         <v>1075</v>
       </c>
-      <c r="I204" s="13" t="s">
+      <c r="I204" t="s">
         <v>1076</v>
       </c>
-      <c r="J204" s="14" t="s">
+      <c r="J204" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="K204" s="13" t="s">
+      <c r="K204" t="s">
         <v>1184</v>
       </c>
-      <c r="L204" s="14">
+      <c r="L204" s="13">
         <v>99</v>
       </c>
     </row>
     <row r="205" spans="1:12">
-      <c r="A205" s="13" t="s">
+      <c r="A205" t="s">
         <v>1188</v>
       </c>
-      <c r="B205" s="13" t="s">
+      <c r="B205" t="s">
         <v>593</v>
       </c>
       <c r="C205" s="6">
         <v>204</v>
       </c>
-      <c r="D205" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E205" s="13" t="s">
+      <c r="D205" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E205" t="s">
         <v>1077</v>
       </c>
-      <c r="F205" s="13" t="s">
+      <c r="F205" t="s">
         <v>1078</v>
       </c>
-      <c r="G205" s="13" t="s">
+      <c r="G205" t="s">
         <v>1079</v>
       </c>
-      <c r="H205" s="13" t="s">
+      <c r="H205" t="s">
         <v>1080</v>
       </c>
-      <c r="I205" s="13" t="s">
+      <c r="I205" t="s">
         <v>1081</v>
       </c>
-      <c r="J205" s="14" t="s">
+      <c r="J205" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K205" s="13" t="s">
+      <c r="K205" t="s">
         <v>1129</v>
       </c>
-      <c r="L205" s="14">
+      <c r="L205" s="13">
         <v>100</v>
       </c>
     </row>
     <row r="206" spans="1:12">
-      <c r="A206" s="13" t="s">
+      <c r="A206" t="s">
         <v>1188</v>
       </c>
-      <c r="B206" s="13" t="s">
+      <c r="B206" t="s">
         <v>593</v>
       </c>
       <c r="C206" s="2">
         <v>205</v>
       </c>
-      <c r="D206" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E206" s="13" t="s">
+      <c r="D206" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E206" t="s">
         <v>1082</v>
       </c>
-      <c r="F206" s="13" t="s">
+      <c r="F206" t="s">
         <v>1083</v>
       </c>
-      <c r="G206" s="13" t="s">
+      <c r="G206" t="s">
         <v>1084</v>
       </c>
-      <c r="H206" s="13" t="s">
+      <c r="H206" t="s">
         <v>1085</v>
       </c>
-      <c r="I206" s="13" t="s">
+      <c r="I206" t="s">
         <v>1086</v>
       </c>
-      <c r="J206" s="14" t="s">
+      <c r="J206" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K206" s="13" t="s">
+      <c r="K206" t="s">
         <v>1185</v>
       </c>
-      <c r="L206" s="14">
+      <c r="L206" s="13">
         <v>101</v>
       </c>
     </row>
     <row r="207" spans="1:12">
-      <c r="A207" s="13" t="s">
+      <c r="A207" t="s">
         <v>1188</v>
       </c>
-      <c r="B207" s="13" t="s">
+      <c r="B207" t="s">
         <v>593</v>
       </c>
       <c r="C207" s="6">
         <v>206</v>
       </c>
-      <c r="D207" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E207" s="13" t="s">
+      <c r="D207" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E207" t="s">
         <v>1087</v>
       </c>
-      <c r="F207" s="13" t="s">
+      <c r="F207" t="s">
         <v>1088</v>
       </c>
-      <c r="G207" s="13" t="s">
+      <c r="G207" t="s">
         <v>1089</v>
       </c>
-      <c r="H207" s="13" t="s">
+      <c r="H207" t="s">
         <v>1090</v>
       </c>
-      <c r="I207" s="13" t="s">
+      <c r="I207" t="s">
         <v>1091</v>
       </c>
-      <c r="J207" s="14" t="s">
+      <c r="J207" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K207" s="13" t="s">
+      <c r="K207" t="s">
         <v>1129</v>
       </c>
-      <c r="L207" s="14">
+      <c r="L207" s="13">
         <v>102</v>
       </c>
     </row>
     <row r="208" spans="1:12">
-      <c r="A208" s="13" t="s">
+      <c r="A208" t="s">
         <v>1188</v>
       </c>
-      <c r="B208" s="13" t="s">
+      <c r="B208" t="s">
         <v>593</v>
       </c>
       <c r="C208" s="6">
         <v>207</v>
       </c>
-      <c r="D208" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="E208" s="13" t="s">
+      <c r="D208" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E208" t="s">
         <v>1092</v>
       </c>
-      <c r="F208" s="13" t="s">
+      <c r="F208" t="s">
         <v>1093</v>
       </c>
-      <c r="G208" s="13" t="s">
+      <c r="G208" t="s">
         <v>1094</v>
       </c>
-      <c r="H208" s="13" t="s">
+      <c r="H208" t="s">
         <v>1095</v>
       </c>
-      <c r="I208" s="13" t="s">
+      <c r="I208" t="s">
         <v>1096</v>
       </c>
-      <c r="J208" s="14" t="s">
+      <c r="J208" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="K208" s="13" t="s">
+      <c r="K208" t="s">
         <v>1113</v>
       </c>
-      <c r="L208" s="14">
+      <c r="L208" s="13">
         <v>103</v>
       </c>
     </row>
     <row r="209" spans="1:12">
-      <c r="A209" s="13" t="s">
+      <c r="A209" t="s">
         <v>1188</v>
       </c>
-      <c r="B209" s="13" t="s">
+      <c r="B209" t="s">
         <v>593</v>
       </c>
       <c r="C209" s="2">
         <v>208</v>
       </c>
-      <c r="D209" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E209" s="13" t="s">
+      <c r="D209" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E209" t="s">
         <v>1097</v>
       </c>
-      <c r="F209" s="13" t="s">
+      <c r="F209" t="s">
         <v>111</v>
       </c>
-      <c r="G209" s="13" t="s">
+      <c r="G209" t="s">
         <v>113</v>
       </c>
-      <c r="H209" s="13" t="s">
+      <c r="H209" t="s">
         <v>1098</v>
       </c>
-      <c r="I209" s="13" t="s">
+      <c r="I209" t="s">
         <v>1099</v>
       </c>
-      <c r="J209" s="14" t="s">
+      <c r="J209" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="K209" s="13" t="s">
+      <c r="K209" t="s">
         <v>1129</v>
       </c>
-      <c r="L209" s="14">
+      <c r="L209" s="13">
         <v>104</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="duplicateValues" dxfId="16" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" sqref="J2:J105" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -12123,8 +12192,9 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/qs.xlsx
+++ b/qs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cyn20598134-my.sharepoint.com/personal/cx2691_msdn365_net/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{36BC63BE-84FA-4E99-9A4C-54200D0A93C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9D7177F-55D4-4A4C-B585-ED5B5D9B4FF6}"/>
+  <xr:revisionPtr revIDLastSave="156" documentId="13_ncr:1_{36BC63BE-84FA-4E99-9A4C-54200D0A93C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D3BAC10-6FEB-428F-8EF1-A375217BB08A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2104" uniqueCount="1197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2239" uniqueCount="1271">
   <si>
     <t>Form</t>
   </si>
@@ -3624,6 +3624,229 @@
   </si>
   <si>
     <t>الدرس المعدل</t>
+  </si>
+  <si>
+    <t>ما نوع المهمة التي يتم فيها مراجعة كفاءة الادارة المالية فيها؟</t>
+  </si>
+  <si>
+    <t>مهمة التزام</t>
+  </si>
+  <si>
+    <t>مهمة تشغيلية</t>
+  </si>
+  <si>
+    <t>مهمة جودة</t>
+  </si>
+  <si>
+    <t>مهمة منافية للجهالة</t>
+  </si>
+  <si>
+    <t>وفقًا للمعايير، أيٌّ مما يلي يُعد الأقل أهمية عند تحديد مدى كفاية خطة التدقيق السنوية؟</t>
+  </si>
+  <si>
+    <t>الكفاية</t>
+  </si>
+  <si>
+    <t>التوزيع الفعال</t>
+  </si>
+  <si>
+    <t>الفعالية من حيث التكلفة</t>
+  </si>
+  <si>
+    <t>وفقًا لإرشادات معهد المدققين الداخليين ،أيٌّ مما يلي يُعد الأقل احتمالًا لأن يكون رقابة مالية رئيسية في عملية الحسابات الدائنة في المنظمة؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> طلب الموافقة على الإضافات والتعديلات إلى قائمة الموردين الرئيسية، عندما يكون الخطر الكامن للموردين الوهميين مرتفعًا. 
+</t>
+  </si>
+  <si>
+    <t>مراقبة المبالغ المدفوعة في كل فترة ومقارنتها بالميزانية لتحديد المشكلات المحتملة.</t>
+  </si>
+  <si>
+    <t>مقارنة عناوين الموظفين بعناوين الموردين لتحديد الاحتيال المحتمل من قبل الموظفين</t>
+  </si>
+  <si>
+    <t>مراقبة شكاوى جودة العملاء مقارنة بالفترة السابقة لتحديد مشكلات الموردين</t>
+  </si>
+  <si>
+    <t>أيٌّ مما يلي يُعد دورًا مناسبًا لنشاط التدقيق الداخلي فيما يتعلق ببرنامج إدارة المخاطر في المنظمة؟</t>
+  </si>
+  <si>
+    <t>تحديد وإدارة المخاطر بما يتماشى مع شهية المنظمة للمخاطر</t>
+  </si>
+  <si>
+    <t>ضمان وجود عملية مناسبة وفعالة لإدارة المخاطر</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> الحصول على فهم كافٍ لاستراتيجيات التخفيف الرئيسية من المخاطر في المنظمة</t>
+  </si>
+  <si>
+    <t>تحديد وضمان وجود ضوابط مناسبة للتخفيف من المخاطر</t>
+  </si>
+  <si>
+    <t>أيٌّ من العبارات التالية صحيحة فيما يتعلق بالضوابط الداخلية؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> في المهام التأكيدية، يجب على المراجعين الداخليين التخطيط لتقييم فعالية جميع الضوابط على مستوى المنشأة</t>
+  </si>
+  <si>
+    <t>يمكن للضوابط على مستوى المنشأة المصممة بشكل سيئ أو التي تعاني من قصور أن تمنع ضوابط العمليات المصممة جيدًا من العمل كما هو مقصود</t>
+  </si>
+  <si>
+    <t>ثناء تخطيط المهمة، يجب على المراجعين الداخليين عدم مناقشة المخاطر والضوابط الرئيسية المحددة مع إدارة المجال محل المراجعة، لتجنب تنبيههم إلى اختبارات التدقيق المحتملة.</t>
+  </si>
+  <si>
+    <t>تعد مراجعة خرائط العمليات ومخططات التدفق طريقة مناسبة للمراجع الداخلي لتحديد جميع المخاطر والضوابط الرئيسية أثناء تخطيط المهمة.</t>
+  </si>
+  <si>
+    <t>أيٌّ من الأساليب التالية سيساعد المراجع الداخلي بشكل أفضل في تحديد ما إذا كانت قاعدة بيانات أحد متاجر التجزئة التي تحتوي على 100,000 عميل تتضمن حسابات مكررة؟</t>
+  </si>
+  <si>
+    <t>تصنيف معلومات العملاء إلى طبقات (Stratifying)</t>
+  </si>
+  <si>
+    <t>استخراج معلومات العملاء (Extracting)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> تصفية معلومات العملاء (Filtering)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> فرز معلومات العملاء (Sorting)</t>
+  </si>
+  <si>
+    <t>بأيٍّ من الطرق التالية يمكن لنشاط التدقيق الداخلي تحديد فرص جديدة للمهام؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> من خلال تعريف الأنشطة حسب العمليات التجارية.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> من خلال النظر إلى العوامل الخارجية، مثل شكاوى المنتجات</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> من خلال النظر إلى الأنشطة حسب مراكز التكلفة التجارية</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> من خلال تعريف الأنشطة حسب الهيكل التنظيمي</t>
+  </si>
+  <si>
+    <t>نتيجة لتحمل الإدارة العليا للمخاطر، توجد مخاطر متبقية تتجاوز شهية المنظمة للمخاطر. أيٌّ من الإجراءات التالية سيكون الأنسب للرئيس التنفيذي للتدقيق؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> تجاهل مسؤولية معالجة المخاطر المتبقية</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> تحمل مسؤولية معالجة المخاطر المتبقية</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> التأكد من أن الإدارة العليا تقر بالمخاطر المتبقية</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> التواصل مع مجلس الإدارة بشأن قضية المخاطر المتبقية</t>
+  </si>
+  <si>
+    <t>أيٌّ من أساليب المعاينة التالية يُستخدم عادةً عندما يريد المراجع الداخلي اختبار عينة كبيرة لاكتشاف الاحتيال؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاينة الطبقية (Stratified sampling)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاينة العشوائية غير المنظمة (Haphazard sampling)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> المعاينة الاحتمالية المتناسبة مع الحجم (Probability-proportional-to-size sampling)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> معاينة الاكتشافية (الاستنتاجية) (Discovery sampling)</t>
+  </si>
+  <si>
+    <t>أي من أساليب المعاينة الإحصائية التالية يستخدمه المدقق الداخلي عادةً إذا كان يرغب في الاختبار للكشف عن الاحتيال وكان معدل الانحراف المتوقع منخفضًا جدًا؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> معاينة السمات (Attribute sampling)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> معاينة الاكتشاف (Discovery sampling)</t>
+  </si>
+  <si>
+    <t>عندما يتم ملاحظة نتيجة جوهرية في وقت مبكر أثناء مراجعة وظيفة الحسابات الدائنة، ما هو أفضل إجراء تالٍ لإبلاغ القضية؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إبلاغ الإدارة المحاسبية من خلال مذكرة مرحلية مؤقتة</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> تدوين البند في أوراق العمل لإدراجه في تقرير التدقيق النهائي</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> الدعوة إلى اجتماع ومناقشة القضية مع لجنة التدقيق</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> تنبيه الرئيس التنفيذي فور اكتشاف القضية</t>
+  </si>
+  <si>
+    <t>أثناء مرحلة التخطيط لمهمة تأكيد، يسعى مدقق داخلي إلى فهم مدى نجاح المنطقة الخاضعة للمراجعة في تحقيق أهدافها. أي من تقنيات جمع المعلومات التالية من المرجح أن يستخدمها المدقق؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> مراجعة مؤشرات الأداء الرئيسية للمنطقة الخاضعة للمراجعة</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> إجراء استعراض تفصيلي للعمليات الرئيسية للمنطقة الخاضعة للمراجعة</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> مقابلة مع المدير بخصوص خطة العمل الخاصة بالمنطقة</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> مراجعة نتائج التدقيقات السابقة وعمليات المتابعة الخاصة بالمنطقة الخاضعة للمراجعة</t>
+  </si>
+  <si>
+    <t>أي من الخيارات التالية من المرجح أن يعكس أفضل أهداف ممكنة للمهمة؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أهداف المهمة المستمدة من نتائج تقييم المخاطر من خبراء وظيفة المخاطر في الشركة</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أهداف المهمة المستمدة من نتائج تقييم المخاطر الخاصة بالإدارة العليا</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أهداف المهمة المستمدة من نتائج تقييم المخاطر الخاصة بنشاط التدقيق الداخلي نفسه</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أهداف المهمة المستمدة من نتائج تقييم المخاطر الخاصة بكل من الإدارة العليا وخبراء وظيفة المخاطر في الشركة</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عند مراجعة عمليات التعامل مع النقد في المنظمة ، أي مما يلي هو أكثر أشكال الادلة الشفوية موثوقية يمكن للمراجع الداخلي الحصول عليها؟ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">شهادة من الصراف الذي يقوم بالعمليات التي تتم مراجعتها </t>
+  </si>
+  <si>
+    <t>شهادة من مشرف الصراف الذي يعرف كيفية تنفيذ العمليات</t>
+  </si>
+  <si>
+    <t>شهادة من شخص مطلع مستقل عن واجب الصرافة</t>
+  </si>
+  <si>
+    <t>شهادة من مدير يشرف على جميع أنشطة الصرافة التي تتم مراجعتها</t>
+  </si>
+  <si>
+    <t>أي من التالي يُعد أفضل مثال على أدلة تدقيق موثوقة؟</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> تقرير شفهي من أحد الموظفين حول تنفيذ أحد الضوابط</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> مستند تم الحصول عليه مباشرة من طرف خارجي مستقل</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ملخص أعدته الإدارة للمعاملات المالية</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ملاحظة غير موثقة من أحد أعضاء فريق التدقيق</t>
+  </si>
+  <si>
+    <t>و- إضافية</t>
+  </si>
+  <si>
+    <t>اسألة إضافية</t>
   </si>
 </sst>
 </file>
@@ -3784,7 +4007,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -3834,12 +4057,47 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{CF73B589-3A71-41BD-93A9-80867E296F12}"/>
   </cellStyles>
   <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3876,30 +4134,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -4008,22 +4242,26 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E5854F4D-195B-480B-8DEF-6E512026576C}" name="Table1" displayName="Table1" ref="A1:L209" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13">
-  <autoFilter ref="A1:L209" xr:uid="{E5854F4D-195B-480B-8DEF-6E512026576C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E5854F4D-195B-480B-8DEF-6E512026576C}" name="Table1" displayName="Table1" ref="A1:L224" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13">
+  <autoFilter ref="A1:L224" xr:uid="{E5854F4D-195B-480B-8DEF-6E512026576C}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{2051CF24-7DAC-4F6B-8197-05C7C1C70668}" name="Form" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{B11E43A6-8751-426D-BDCA-8D231219A4E3}" name="Form Title" dataDxfId="11"/>
     <tableColumn id="3" xr3:uid="{993C43D2-F1BE-48FF-8757-29410E0DCE1D}" name="Question No." dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{79DA49F4-33C7-4D56-992B-9DA561BF07AA}" name="Lesson" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{BC0C681B-9283-4418-9C39-700FC8BC49CF}" name="Question" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{C4A61FD1-6D11-43A8-9F8D-7F6A2A51629D}" name="Option A" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{7EB9F918-F521-4393-A511-DE1B851F24F7}" name="Option B" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{23795A09-2AF7-4E3B-A609-6CC4FEBADA69}" name="Option C" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{EFC7D106-5258-4441-A928-4E24345249E3}" name="Option D" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{492489E1-BCF7-425C-8262-A39D6CA4941B}" name="Correct Answer" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{30CB9AAF-31B8-499E-9CED-39A18CB68145}" name="Modifications / Corrections" dataDxfId="2"/>
-    <tableColumn id="12" xr3:uid="{9D99E0A3-0063-4DC7-9F73-D46FD9EFBCA6}" name="Old number" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{79DA49F4-33C7-4D56-992B-9DA561BF07AA}" name="Lesson" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{BC0C681B-9283-4418-9C39-700FC8BC49CF}" name="Question" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{C4A61FD1-6D11-43A8-9F8D-7F6A2A51629D}" name="Option A" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{7EB9F918-F521-4393-A511-DE1B851F24F7}" name="Option B" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{23795A09-2AF7-4E3B-A609-6CC4FEBADA69}" name="Option C" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{EFC7D106-5258-4441-A928-4E24345249E3}" name="Option D" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{492489E1-BCF7-425C-8262-A39D6CA4941B}" name="Correct Answer" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{30CB9AAF-31B8-499E-9CED-39A18CB68145}" name="Modifications / Corrections" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{9D99E0A3-0063-4DC7-9F73-D46FD9EFBCA6}" name="Old number" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4189,7 +4427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W209"/>
+  <dimension ref="A1:W224"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -8230,7 +8468,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="106" spans="1:12">
+    <row r="106" spans="1:12" ht="28.5">
       <c r="A106" t="s">
         <v>1188</v>
       </c>
@@ -8243,7 +8481,7 @@
       <c r="D106" t="s">
         <v>1192</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E106" s="20" t="s">
         <v>594</v>
       </c>
       <c r="F106" t="s">
@@ -8268,7 +8506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:12">
+    <row r="107" spans="1:12" ht="28.5">
       <c r="A107" t="s">
         <v>1188</v>
       </c>
@@ -8281,7 +8519,7 @@
       <c r="D107" t="s">
         <v>1192</v>
       </c>
-      <c r="E107" t="s">
+      <c r="E107" s="20" t="s">
         <v>599</v>
       </c>
       <c r="F107" t="s">
@@ -8306,7 +8544,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:12">
+    <row r="108" spans="1:12" ht="28.5">
       <c r="A108" t="s">
         <v>1188</v>
       </c>
@@ -8319,7 +8557,7 @@
       <c r="D108" t="s">
         <v>1194</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E108" s="20" t="s">
         <v>604</v>
       </c>
       <c r="F108" t="s">
@@ -8344,7 +8582,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:12">
+    <row r="109" spans="1:12" ht="28.5">
       <c r="A109" t="s">
         <v>1188</v>
       </c>
@@ -8357,7 +8595,7 @@
       <c r="D109" t="s">
         <v>1192</v>
       </c>
-      <c r="E109" t="s">
+      <c r="E109" s="20" t="s">
         <v>609</v>
       </c>
       <c r="F109" t="s">
@@ -8382,7 +8620,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:12">
+    <row r="110" spans="1:12" ht="28.5">
       <c r="A110" t="s">
         <v>1188</v>
       </c>
@@ -8395,7 +8633,7 @@
       <c r="D110" t="s">
         <v>1192</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E110" s="20" t="s">
         <v>614</v>
       </c>
       <c r="F110" t="s">
@@ -8433,7 +8671,7 @@
       <c r="D111" t="s">
         <v>1190</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E111" s="20" t="s">
         <v>619</v>
       </c>
       <c r="F111" t="s">
@@ -8458,7 +8696,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:12">
+    <row r="112" spans="1:12" ht="42.75">
       <c r="A112" t="s">
         <v>1188</v>
       </c>
@@ -8471,7 +8709,7 @@
       <c r="D112" t="s">
         <v>1190</v>
       </c>
-      <c r="E112" t="s">
+      <c r="E112" s="20" t="s">
         <v>624</v>
       </c>
       <c r="F112" t="s">
@@ -8509,7 +8747,7 @@
       <c r="D113" t="s">
         <v>1192</v>
       </c>
-      <c r="E113" t="s">
+      <c r="E113" s="20" t="s">
         <v>629</v>
       </c>
       <c r="F113" t="s">
@@ -8534,7 +8772,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:12">
+    <row r="114" spans="1:12" ht="71.25">
       <c r="A114" t="s">
         <v>1188</v>
       </c>
@@ -8547,7 +8785,7 @@
       <c r="D114" t="s">
         <v>1190</v>
       </c>
-      <c r="E114" t="s">
+      <c r="E114" s="20" t="s">
         <v>634</v>
       </c>
       <c r="F114" t="s">
@@ -8572,7 +8810,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:12">
+    <row r="115" spans="1:12" ht="28.5">
       <c r="A115" t="s">
         <v>1188</v>
       </c>
@@ -8585,7 +8823,7 @@
       <c r="D115" t="s">
         <v>1190</v>
       </c>
-      <c r="E115" t="s">
+      <c r="E115" s="20" t="s">
         <v>639</v>
       </c>
       <c r="F115" t="s">
@@ -8623,7 +8861,7 @@
       <c r="D116" t="s">
         <v>1190</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E116" s="20" t="s">
         <v>644</v>
       </c>
       <c r="F116" t="s">
@@ -8648,7 +8886,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="117" spans="1:12">
+    <row r="117" spans="1:12" ht="57">
       <c r="A117" t="s">
         <v>1188</v>
       </c>
@@ -8661,7 +8899,7 @@
       <c r="D117" t="s">
         <v>1190</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E117" s="20" t="s">
         <v>648</v>
       </c>
       <c r="F117" t="s">
@@ -8699,7 +8937,7 @@
       <c r="D118" t="s">
         <v>1190</v>
       </c>
-      <c r="E118" t="s">
+      <c r="E118" s="20" t="s">
         <v>653</v>
       </c>
       <c r="F118" t="s">
@@ -8724,7 +8962,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="119" spans="1:12">
+    <row r="119" spans="1:12" ht="57">
       <c r="A119" t="s">
         <v>1188</v>
       </c>
@@ -8737,7 +8975,7 @@
       <c r="D119" t="s">
         <v>1190</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E119" s="20" t="s">
         <v>658</v>
       </c>
       <c r="F119" t="s">
@@ -8762,7 +9000,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="120" spans="1:12">
+    <row r="120" spans="1:12" ht="57">
       <c r="A120" t="s">
         <v>1188</v>
       </c>
@@ -8775,7 +9013,7 @@
       <c r="D120" t="s">
         <v>1190</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E120" s="20" t="s">
         <v>663</v>
       </c>
       <c r="F120" t="s">
@@ -8813,7 +9051,7 @@
       <c r="D121" t="s">
         <v>1192</v>
       </c>
-      <c r="E121" t="s">
+      <c r="E121" s="20" t="s">
         <v>668</v>
       </c>
       <c r="F121" t="s">
@@ -8838,7 +9076,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="122" spans="1:12">
+    <row r="122" spans="1:12" ht="28.5">
       <c r="A122" t="s">
         <v>1188</v>
       </c>
@@ -8851,7 +9089,7 @@
       <c r="D122" t="s">
         <v>1192</v>
       </c>
-      <c r="E122" t="s">
+      <c r="E122" s="20" t="s">
         <v>673</v>
       </c>
       <c r="F122" t="s">
@@ -8876,7 +9114,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="123" spans="1:12">
+    <row r="123" spans="1:12" ht="28.5">
       <c r="A123" t="s">
         <v>1188</v>
       </c>
@@ -8889,7 +9127,7 @@
       <c r="D123" t="s">
         <v>1192</v>
       </c>
-      <c r="E123" t="s">
+      <c r="E123" s="20" t="s">
         <v>678</v>
       </c>
       <c r="F123" t="s">
@@ -8914,7 +9152,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="124" spans="1:12">
+    <row r="124" spans="1:12" ht="42.75">
       <c r="A124" t="s">
         <v>1188</v>
       </c>
@@ -8927,7 +9165,7 @@
       <c r="D124" t="s">
         <v>1192</v>
       </c>
-      <c r="E124" t="s">
+      <c r="E124" s="20" t="s">
         <v>683</v>
       </c>
       <c r="F124" t="s">
@@ -8952,7 +9190,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="125" spans="1:12">
+    <row r="125" spans="1:12" ht="71.25">
       <c r="A125" t="s">
         <v>1188</v>
       </c>
@@ -8965,7 +9203,7 @@
       <c r="D125" t="s">
         <v>1190</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E125" s="20" t="s">
         <v>688</v>
       </c>
       <c r="F125" t="s">
@@ -8990,7 +9228,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="126" spans="1:12">
+    <row r="126" spans="1:12" ht="28.5">
       <c r="A126" t="s">
         <v>1188</v>
       </c>
@@ -9003,7 +9241,7 @@
       <c r="D126" t="s">
         <v>1192</v>
       </c>
-      <c r="E126" t="s">
+      <c r="E126" s="20" t="s">
         <v>693</v>
       </c>
       <c r="F126" t="s">
@@ -9041,7 +9279,7 @@
       <c r="D127" t="s">
         <v>1190</v>
       </c>
-      <c r="E127" t="s">
+      <c r="E127" s="20" t="s">
         <v>698</v>
       </c>
       <c r="F127" t="s">
@@ -9066,7 +9304,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="128" spans="1:12">
+    <row r="128" spans="1:12" ht="42.75">
       <c r="A128" t="s">
         <v>1188</v>
       </c>
@@ -9079,7 +9317,7 @@
       <c r="D128" t="s">
         <v>1190</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E128" s="20" t="s">
         <v>703</v>
       </c>
       <c r="F128" t="s">
@@ -9104,7 +9342,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="129" spans="1:12">
+    <row r="129" spans="1:12" ht="71.25">
       <c r="A129" t="s">
         <v>1188</v>
       </c>
@@ -9117,7 +9355,7 @@
       <c r="D129" t="s">
         <v>1190</v>
       </c>
-      <c r="E129" t="s">
+      <c r="E129" s="20" t="s">
         <v>708</v>
       </c>
       <c r="F129" t="s">
@@ -9142,7 +9380,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="130" spans="1:12">
+    <row r="130" spans="1:12" ht="28.5">
       <c r="A130" t="s">
         <v>1188</v>
       </c>
@@ -9155,7 +9393,7 @@
       <c r="D130" t="s">
         <v>1190</v>
       </c>
-      <c r="E130" t="s">
+      <c r="E130" s="20" t="s">
         <v>711</v>
       </c>
       <c r="F130" t="s">
@@ -9180,7 +9418,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="131" spans="1:12">
+    <row r="131" spans="1:12" ht="57">
       <c r="A131" t="s">
         <v>1188</v>
       </c>
@@ -9193,7 +9431,7 @@
       <c r="D131" t="s">
         <v>1190</v>
       </c>
-      <c r="E131" t="s">
+      <c r="E131" s="20" t="s">
         <v>716</v>
       </c>
       <c r="F131" t="s">
@@ -9231,7 +9469,7 @@
       <c r="D132" t="s">
         <v>1190</v>
       </c>
-      <c r="E132" t="s">
+      <c r="E132" s="20" t="s">
         <v>721</v>
       </c>
       <c r="F132" t="s">
@@ -9256,7 +9494,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="133" spans="1:12">
+    <row r="133" spans="1:12" ht="28.5">
       <c r="A133" t="s">
         <v>1188</v>
       </c>
@@ -9269,7 +9507,7 @@
       <c r="D133" t="s">
         <v>1193</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E133" s="20" t="s">
         <v>726</v>
       </c>
       <c r="F133" t="s">
@@ -9294,7 +9532,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="134" spans="1:12">
+    <row r="134" spans="1:12" ht="28.5">
       <c r="A134" t="s">
         <v>1188</v>
       </c>
@@ -9307,7 +9545,7 @@
       <c r="D134" t="s">
         <v>1193</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E134" s="20" t="s">
         <v>731</v>
       </c>
       <c r="F134" t="s">
@@ -9332,7 +9570,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="135" spans="1:12">
+    <row r="135" spans="1:12" ht="85.5">
       <c r="A135" t="s">
         <v>1188</v>
       </c>
@@ -9345,7 +9583,7 @@
       <c r="D135" t="s">
         <v>1193</v>
       </c>
-      <c r="E135" t="s">
+      <c r="E135" s="20" t="s">
         <v>736</v>
       </c>
       <c r="F135" t="s">
@@ -9383,7 +9621,7 @@
       <c r="D136" t="s">
         <v>1192</v>
       </c>
-      <c r="E136" t="s">
+      <c r="E136" s="20" t="s">
         <v>741</v>
       </c>
       <c r="F136" t="s">
@@ -9408,7 +9646,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="137" spans="1:12">
+    <row r="137" spans="1:12" ht="28.5">
       <c r="A137" t="s">
         <v>1188</v>
       </c>
@@ -9421,7 +9659,7 @@
       <c r="D137" t="s">
         <v>1191</v>
       </c>
-      <c r="E137" t="s">
+      <c r="E137" s="20" t="s">
         <v>746</v>
       </c>
       <c r="F137" t="s">
@@ -9446,7 +9684,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="138" spans="1:12">
+    <row r="138" spans="1:12" ht="28.5">
       <c r="A138" t="s">
         <v>1188</v>
       </c>
@@ -9459,7 +9697,7 @@
       <c r="D138" t="s">
         <v>1190</v>
       </c>
-      <c r="E138" t="s">
+      <c r="E138" s="20" t="s">
         <v>751</v>
       </c>
       <c r="F138" t="s">
@@ -9484,7 +9722,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="139" spans="1:12">
+    <row r="139" spans="1:12" ht="42.75">
       <c r="A139" t="s">
         <v>1188</v>
       </c>
@@ -9497,7 +9735,7 @@
       <c r="D139" t="s">
         <v>1190</v>
       </c>
-      <c r="E139" t="s">
+      <c r="E139" s="20" t="s">
         <v>756</v>
       </c>
       <c r="F139" t="s">
@@ -9522,7 +9760,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="140" spans="1:12">
+    <row r="140" spans="1:12" ht="28.5">
       <c r="A140" t="s">
         <v>1188</v>
       </c>
@@ -9535,7 +9773,7 @@
       <c r="D140" t="s">
         <v>1192</v>
       </c>
-      <c r="E140" t="s">
+      <c r="E140" s="20" t="s">
         <v>761</v>
       </c>
       <c r="F140" t="s">
@@ -9560,7 +9798,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="141" spans="1:12">
+    <row r="141" spans="1:12" ht="28.5">
       <c r="A141" t="s">
         <v>1188</v>
       </c>
@@ -9573,7 +9811,7 @@
       <c r="D141" t="s">
         <v>1190</v>
       </c>
-      <c r="E141" t="s">
+      <c r="E141" s="20" t="s">
         <v>766</v>
       </c>
       <c r="F141" t="s">
@@ -9598,7 +9836,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="142" spans="1:12">
+    <row r="142" spans="1:12" ht="28.5">
       <c r="A142" t="s">
         <v>1188</v>
       </c>
@@ -9611,7 +9849,7 @@
       <c r="D142" t="s">
         <v>1190</v>
       </c>
-      <c r="E142" t="s">
+      <c r="E142" s="20" t="s">
         <v>771</v>
       </c>
       <c r="F142" t="s">
@@ -9636,7 +9874,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="143" spans="1:12">
+    <row r="143" spans="1:12" ht="28.5">
       <c r="A143" t="s">
         <v>1188</v>
       </c>
@@ -9649,7 +9887,7 @@
       <c r="D143" t="s">
         <v>1190</v>
       </c>
-      <c r="E143" t="s">
+      <c r="E143" s="20" t="s">
         <v>776</v>
       </c>
       <c r="F143" t="s">
@@ -9674,7 +9912,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="144" spans="1:12">
+    <row r="144" spans="1:12" ht="57">
       <c r="A144" t="s">
         <v>1188</v>
       </c>
@@ -9687,7 +9925,7 @@
       <c r="D144" t="s">
         <v>1193</v>
       </c>
-      <c r="E144" t="s">
+      <c r="E144" s="20" t="s">
         <v>779</v>
       </c>
       <c r="F144" t="s">
@@ -9712,7 +9950,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="145" spans="1:12">
+    <row r="145" spans="1:12" ht="28.5">
       <c r="A145" t="s">
         <v>1188</v>
       </c>
@@ -9725,7 +9963,7 @@
       <c r="D145" t="s">
         <v>1191</v>
       </c>
-      <c r="E145" t="s">
+      <c r="E145" s="20" t="s">
         <v>784</v>
       </c>
       <c r="F145" t="s">
@@ -9750,7 +9988,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="146" spans="1:12">
+    <row r="146" spans="1:12" ht="28.5">
       <c r="A146" t="s">
         <v>1188</v>
       </c>
@@ -9763,7 +10001,7 @@
       <c r="D146" t="s">
         <v>1192</v>
       </c>
-      <c r="E146" t="s">
+      <c r="E146" s="20" t="s">
         <v>789</v>
       </c>
       <c r="F146" t="s">
@@ -9801,7 +10039,7 @@
       <c r="D147" t="s">
         <v>1190</v>
       </c>
-      <c r="E147" t="s">
+      <c r="E147" s="20" t="s">
         <v>793</v>
       </c>
       <c r="F147" t="s">
@@ -9826,7 +10064,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="148" spans="1:12">
+    <row r="148" spans="1:12" ht="28.5">
       <c r="A148" t="s">
         <v>1188</v>
       </c>
@@ -9839,7 +10077,7 @@
       <c r="D148" t="s">
         <v>1194</v>
       </c>
-      <c r="E148" t="s">
+      <c r="E148" s="20" t="s">
         <v>798</v>
       </c>
       <c r="F148" t="s">
@@ -9864,7 +10102,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="149" spans="1:12">
+    <row r="149" spans="1:12" ht="42.75">
       <c r="A149" t="s">
         <v>1188</v>
       </c>
@@ -9877,7 +10115,7 @@
       <c r="D149" t="s">
         <v>1190</v>
       </c>
-      <c r="E149" t="s">
+      <c r="E149" s="20" t="s">
         <v>803</v>
       </c>
       <c r="F149" t="s">
@@ -9902,7 +10140,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="150" spans="1:12">
+    <row r="150" spans="1:12" ht="42.75">
       <c r="A150" t="s">
         <v>1188</v>
       </c>
@@ -9915,7 +10153,7 @@
       <c r="D150" t="s">
         <v>1190</v>
       </c>
-      <c r="E150" t="s">
+      <c r="E150" s="20" t="s">
         <v>808</v>
       </c>
       <c r="F150" t="s">
@@ -9940,7 +10178,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="151" spans="1:12">
+    <row r="151" spans="1:12" ht="28.5">
       <c r="A151" t="s">
         <v>1188</v>
       </c>
@@ -9953,7 +10191,7 @@
       <c r="D151" t="s">
         <v>1193</v>
       </c>
-      <c r="E151" t="s">
+      <c r="E151" s="20" t="s">
         <v>813</v>
       </c>
       <c r="F151" t="s">
@@ -9978,7 +10216,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="152" spans="1:12">
+    <row r="152" spans="1:12" ht="28.5">
       <c r="A152" t="s">
         <v>1188</v>
       </c>
@@ -9991,7 +10229,7 @@
       <c r="D152" t="s">
         <v>1192</v>
       </c>
-      <c r="E152" t="s">
+      <c r="E152" s="20" t="s">
         <v>818</v>
       </c>
       <c r="F152" t="s">
@@ -10029,7 +10267,7 @@
       <c r="D153" t="s">
         <v>1192</v>
       </c>
-      <c r="E153" t="s">
+      <c r="E153" s="20" t="s">
         <v>823</v>
       </c>
       <c r="F153" t="s">
@@ -10054,7 +10292,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="154" spans="1:12">
+    <row r="154" spans="1:12" ht="42.75">
       <c r="A154" t="s">
         <v>1188</v>
       </c>
@@ -10067,7 +10305,7 @@
       <c r="D154" t="s">
         <v>1192</v>
       </c>
-      <c r="E154" t="s">
+      <c r="E154" s="20" t="s">
         <v>827</v>
       </c>
       <c r="F154" t="s">
@@ -10105,7 +10343,7 @@
       <c r="D155" t="s">
         <v>1192</v>
       </c>
-      <c r="E155" t="s">
+      <c r="E155" s="20" t="s">
         <v>832</v>
       </c>
       <c r="F155" t="s">
@@ -10130,7 +10368,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="156" spans="1:12">
+    <row r="156" spans="1:12" ht="28.5">
       <c r="A156" t="s">
         <v>1188</v>
       </c>
@@ -10143,7 +10381,7 @@
       <c r="D156" t="s">
         <v>1190</v>
       </c>
-      <c r="E156" t="s">
+      <c r="E156" s="20" t="s">
         <v>837</v>
       </c>
       <c r="F156" t="s">
@@ -10181,7 +10419,7 @@
       <c r="D157" t="s">
         <v>1193</v>
       </c>
-      <c r="E157" t="s">
+      <c r="E157" s="20" t="s">
         <v>842</v>
       </c>
       <c r="F157" t="s">
@@ -10219,7 +10457,7 @@
       <c r="D158" t="s">
         <v>1190</v>
       </c>
-      <c r="E158" t="s">
+      <c r="E158" s="20" t="s">
         <v>847</v>
       </c>
       <c r="F158" t="s">
@@ -10257,7 +10495,7 @@
       <c r="D159" t="s">
         <v>1190</v>
       </c>
-      <c r="E159" t="s">
+      <c r="E159" s="20" t="s">
         <v>852</v>
       </c>
       <c r="F159" t="s">
@@ -10282,7 +10520,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="160" spans="1:12">
+    <row r="160" spans="1:12" ht="71.25">
       <c r="A160" t="s">
         <v>1188</v>
       </c>
@@ -10295,7 +10533,7 @@
       <c r="D160" t="s">
         <v>1190</v>
       </c>
-      <c r="E160" t="s">
+      <c r="E160" s="20" t="s">
         <v>856</v>
       </c>
       <c r="F160" t="s">
@@ -10333,7 +10571,7 @@
       <c r="D161" t="s">
         <v>1193</v>
       </c>
-      <c r="E161" t="s">
+      <c r="E161" s="20" t="s">
         <v>861</v>
       </c>
       <c r="F161" t="s">
@@ -10358,7 +10596,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="162" spans="1:12">
+    <row r="162" spans="1:12" ht="28.5">
       <c r="A162" t="s">
         <v>1188</v>
       </c>
@@ -10371,7 +10609,7 @@
       <c r="D162" t="s">
         <v>1194</v>
       </c>
-      <c r="E162" t="s">
+      <c r="E162" s="20" t="s">
         <v>866</v>
       </c>
       <c r="F162" t="s">
@@ -10396,7 +10634,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="163" spans="1:12">
+    <row r="163" spans="1:12" ht="42.75">
       <c r="A163" t="s">
         <v>1188</v>
       </c>
@@ -10409,7 +10647,7 @@
       <c r="D163" t="s">
         <v>1193</v>
       </c>
-      <c r="E163" t="s">
+      <c r="E163" s="20" t="s">
         <v>871</v>
       </c>
       <c r="F163" t="s">
@@ -10434,7 +10672,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="164" spans="1:12">
+    <row r="164" spans="1:12" ht="42.75">
       <c r="A164" t="s">
         <v>1188</v>
       </c>
@@ -10447,7 +10685,7 @@
       <c r="D164" t="s">
         <v>1190</v>
       </c>
-      <c r="E164" t="s">
+      <c r="E164" s="20" t="s">
         <v>876</v>
       </c>
       <c r="F164" t="s">
@@ -10485,7 +10723,7 @@
       <c r="D165" t="s">
         <v>1193</v>
       </c>
-      <c r="E165" t="s">
+      <c r="E165" s="20" t="s">
         <v>881</v>
       </c>
       <c r="F165" t="s">
@@ -10523,7 +10761,7 @@
       <c r="D166" t="s">
         <v>1190</v>
       </c>
-      <c r="E166" t="s">
+      <c r="E166" s="20" t="s">
         <v>886</v>
       </c>
       <c r="F166" t="s">
@@ -10561,7 +10799,7 @@
       <c r="D167" t="s">
         <v>1192</v>
       </c>
-      <c r="E167" t="s">
+      <c r="E167" s="20" t="s">
         <v>891</v>
       </c>
       <c r="F167" t="s">
@@ -10586,7 +10824,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="168" spans="1:12">
+    <row r="168" spans="1:12" ht="42.75">
       <c r="A168" t="s">
         <v>1188</v>
       </c>
@@ -10599,7 +10837,7 @@
       <c r="D168" t="s">
         <v>1190</v>
       </c>
-      <c r="E168" t="s">
+      <c r="E168" s="20" t="s">
         <v>896</v>
       </c>
       <c r="F168" t="s">
@@ -10624,7 +10862,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="169" spans="1:12">
+    <row r="169" spans="1:12" ht="42.75">
       <c r="A169" t="s">
         <v>1188</v>
       </c>
@@ -10637,7 +10875,7 @@
       <c r="D169" t="s">
         <v>1190</v>
       </c>
-      <c r="E169" t="s">
+      <c r="E169" s="20" t="s">
         <v>901</v>
       </c>
       <c r="F169" t="s">
@@ -10675,7 +10913,7 @@
       <c r="D170" t="s">
         <v>1190</v>
       </c>
-      <c r="E170" t="s">
+      <c r="E170" s="20" t="s">
         <v>905</v>
       </c>
       <c r="F170" t="s">
@@ -10713,7 +10951,7 @@
       <c r="D171" t="s">
         <v>1192</v>
       </c>
-      <c r="E171" t="s">
+      <c r="E171" s="20" t="s">
         <v>910</v>
       </c>
       <c r="F171" t="s">
@@ -10738,7 +10976,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="172" spans="1:12">
+    <row r="172" spans="1:12" ht="71.25">
       <c r="A172" t="s">
         <v>1188</v>
       </c>
@@ -10751,7 +10989,7 @@
       <c r="D172" t="s">
         <v>1190</v>
       </c>
-      <c r="E172" t="s">
+      <c r="E172" s="20" t="s">
         <v>915</v>
       </c>
       <c r="F172" t="s">
@@ -10776,7 +11014,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="173" spans="1:12">
+    <row r="173" spans="1:12" ht="28.5">
       <c r="A173" t="s">
         <v>1188</v>
       </c>
@@ -10789,7 +11027,7 @@
       <c r="D173" t="s">
         <v>1192</v>
       </c>
-      <c r="E173" t="s">
+      <c r="E173" s="20" t="s">
         <v>920</v>
       </c>
       <c r="F173" t="s">
@@ -10827,7 +11065,7 @@
       <c r="D174" t="s">
         <v>1193</v>
       </c>
-      <c r="E174" t="s">
+      <c r="E174" s="20" t="s">
         <v>925</v>
       </c>
       <c r="F174" t="s">
@@ -10852,7 +11090,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="175" spans="1:12">
+    <row r="175" spans="1:12" ht="57">
       <c r="A175" t="s">
         <v>1188</v>
       </c>
@@ -10865,7 +11103,7 @@
       <c r="D175" t="s">
         <v>1190</v>
       </c>
-      <c r="E175" t="s">
+      <c r="E175" s="20" t="s">
         <v>930</v>
       </c>
       <c r="F175" t="s">
@@ -10890,7 +11128,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="176" spans="1:12">
+    <row r="176" spans="1:12" ht="28.5">
       <c r="A176" t="s">
         <v>1188</v>
       </c>
@@ -10903,7 +11141,7 @@
       <c r="D176" t="s">
         <v>1190</v>
       </c>
-      <c r="E176" t="s">
+      <c r="E176" s="20" t="s">
         <v>935</v>
       </c>
       <c r="F176" t="s">
@@ -10928,7 +11166,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="177" spans="1:12">
+    <row r="177" spans="1:12" ht="28.5">
       <c r="A177" t="s">
         <v>1188</v>
       </c>
@@ -10941,7 +11179,7 @@
       <c r="D177" t="s">
         <v>1192</v>
       </c>
-      <c r="E177" t="s">
+      <c r="E177" s="20" t="s">
         <v>940</v>
       </c>
       <c r="F177" t="s">
@@ -10966,7 +11204,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="178" spans="1:12">
+    <row r="178" spans="1:12" ht="28.5">
       <c r="A178" t="s">
         <v>1188</v>
       </c>
@@ -10979,7 +11217,7 @@
       <c r="D178" t="s">
         <v>1193</v>
       </c>
-      <c r="E178" t="s">
+      <c r="E178" s="20" t="s">
         <v>945</v>
       </c>
       <c r="F178" t="s">
@@ -11017,7 +11255,7 @@
       <c r="D179" t="s">
         <v>1192</v>
       </c>
-      <c r="E179" t="s">
+      <c r="E179" s="20" t="s">
         <v>950</v>
       </c>
       <c r="F179" t="s">
@@ -11042,7 +11280,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="180" spans="1:12">
+    <row r="180" spans="1:12" ht="28.5">
       <c r="A180" t="s">
         <v>1188</v>
       </c>
@@ -11055,7 +11293,7 @@
       <c r="D180" t="s">
         <v>1190</v>
       </c>
-      <c r="E180" t="s">
+      <c r="E180" s="20" t="s">
         <v>955</v>
       </c>
       <c r="F180" t="s">
@@ -11093,7 +11331,7 @@
       <c r="D181" t="s">
         <v>1191</v>
       </c>
-      <c r="E181" t="s">
+      <c r="E181" s="20" t="s">
         <v>958</v>
       </c>
       <c r="F181" t="s">
@@ -11118,7 +11356,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="182" spans="1:12">
+    <row r="182" spans="1:12" ht="28.5">
       <c r="A182" t="s">
         <v>1188</v>
       </c>
@@ -11131,7 +11369,7 @@
       <c r="D182" t="s">
         <v>1190</v>
       </c>
-      <c r="E182" t="s">
+      <c r="E182" s="20" t="s">
         <v>963</v>
       </c>
       <c r="F182" t="s">
@@ -11169,7 +11407,7 @@
       <c r="D183" t="s">
         <v>1192</v>
       </c>
-      <c r="E183" t="s">
+      <c r="E183" s="20" t="s">
         <v>968</v>
       </c>
       <c r="F183" t="s">
@@ -11207,7 +11445,7 @@
       <c r="D184" t="s">
         <v>1192</v>
       </c>
-      <c r="E184" t="s">
+      <c r="E184" s="20" t="s">
         <v>973</v>
       </c>
       <c r="F184" t="s">
@@ -11245,7 +11483,7 @@
       <c r="D185" t="s">
         <v>1190</v>
       </c>
-      <c r="E185" t="s">
+      <c r="E185" s="20" t="s">
         <v>978</v>
       </c>
       <c r="F185" t="s">
@@ -11270,7 +11508,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="186" spans="1:12">
+    <row r="186" spans="1:12" ht="28.5">
       <c r="A186" t="s">
         <v>1188</v>
       </c>
@@ -11283,7 +11521,7 @@
       <c r="D186" t="s">
         <v>1190</v>
       </c>
-      <c r="E186" t="s">
+      <c r="E186" s="20" t="s">
         <v>983</v>
       </c>
       <c r="F186" t="s">
@@ -11308,7 +11546,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="187" spans="1:12">
+    <row r="187" spans="1:12" ht="42.75">
       <c r="A187" t="s">
         <v>1188</v>
       </c>
@@ -11321,7 +11559,7 @@
       <c r="D187" t="s">
         <v>1193</v>
       </c>
-      <c r="E187" t="s">
+      <c r="E187" s="20" t="s">
         <v>988</v>
       </c>
       <c r="F187" t="s">
@@ -11346,7 +11584,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="188" spans="1:12">
+    <row r="188" spans="1:12" ht="28.5">
       <c r="A188" t="s">
         <v>1188</v>
       </c>
@@ -11359,7 +11597,7 @@
       <c r="D188" t="s">
         <v>1193</v>
       </c>
-      <c r="E188" t="s">
+      <c r="E188" s="20" t="s">
         <v>993</v>
       </c>
       <c r="F188" t="s">
@@ -11384,7 +11622,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="189" spans="1:12">
+    <row r="189" spans="1:12" ht="28.5">
       <c r="A189" t="s">
         <v>1188</v>
       </c>
@@ -11397,7 +11635,7 @@
       <c r="D189" t="s">
         <v>1192</v>
       </c>
-      <c r="E189" t="s">
+      <c r="E189" s="20" t="s">
         <v>998</v>
       </c>
       <c r="F189" t="s">
@@ -11435,7 +11673,7 @@
       <c r="D190" t="s">
         <v>1193</v>
       </c>
-      <c r="E190" t="s">
+      <c r="E190" s="20" t="s">
         <v>1003</v>
       </c>
       <c r="F190" t="s">
@@ -11460,7 +11698,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="191" spans="1:12">
+    <row r="191" spans="1:12" ht="71.25">
       <c r="A191" t="s">
         <v>1188</v>
       </c>
@@ -11473,7 +11711,7 @@
       <c r="D191" t="s">
         <v>1191</v>
       </c>
-      <c r="E191" t="s">
+      <c r="E191" s="20" t="s">
         <v>1008</v>
       </c>
       <c r="F191" t="s">
@@ -11498,7 +11736,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="192" spans="1:12">
+    <row r="192" spans="1:12" ht="28.5">
       <c r="A192" t="s">
         <v>1188</v>
       </c>
@@ -11511,7 +11749,7 @@
       <c r="D192" t="s">
         <v>1192</v>
       </c>
-      <c r="E192" t="s">
+      <c r="E192" s="20" t="s">
         <v>1013</v>
       </c>
       <c r="F192" t="s">
@@ -11536,7 +11774,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="193" spans="1:12">
+    <row r="193" spans="1:12" ht="42.75">
       <c r="A193" t="s">
         <v>1188</v>
       </c>
@@ -11549,7 +11787,7 @@
       <c r="D193" t="s">
         <v>1190</v>
       </c>
-      <c r="E193" t="s">
+      <c r="E193" s="20" t="s">
         <v>1018</v>
       </c>
       <c r="F193" t="s">
@@ -11574,7 +11812,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="194" spans="1:12">
+    <row r="194" spans="1:12" ht="28.5">
       <c r="A194" t="s">
         <v>1188</v>
       </c>
@@ -11587,7 +11825,7 @@
       <c r="D194" t="s">
         <v>1190</v>
       </c>
-      <c r="E194" t="s">
+      <c r="E194" s="20" t="s">
         <v>1023</v>
       </c>
       <c r="F194" t="s">
@@ -11612,7 +11850,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="195" spans="1:12">
+    <row r="195" spans="1:12" ht="42.75">
       <c r="A195" t="s">
         <v>1188</v>
       </c>
@@ -11625,7 +11863,7 @@
       <c r="D195" t="s">
         <v>1193</v>
       </c>
-      <c r="E195" t="s">
+      <c r="E195" s="20" t="s">
         <v>1028</v>
       </c>
       <c r="F195" t="s">
@@ -11650,7 +11888,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="196" spans="1:12">
+    <row r="196" spans="1:12" ht="28.5">
       <c r="A196" t="s">
         <v>1188</v>
       </c>
@@ -11663,7 +11901,7 @@
       <c r="D196" t="s">
         <v>1194</v>
       </c>
-      <c r="E196" t="s">
+      <c r="E196" s="20" t="s">
         <v>1033</v>
       </c>
       <c r="F196" t="s">
@@ -11701,7 +11939,7 @@
       <c r="D197" t="s">
         <v>1190</v>
       </c>
-      <c r="E197" t="s">
+      <c r="E197" s="20" t="s">
         <v>1037</v>
       </c>
       <c r="F197" t="s">
@@ -11739,7 +11977,7 @@
       <c r="D198" t="s">
         <v>1190</v>
       </c>
-      <c r="E198" t="s">
+      <c r="E198" s="20" t="s">
         <v>1042</v>
       </c>
       <c r="F198" t="s">
@@ -11764,7 +12002,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="199" spans="1:12">
+    <row r="199" spans="1:12" ht="28.5">
       <c r="A199" t="s">
         <v>1188</v>
       </c>
@@ -11777,7 +12015,7 @@
       <c r="D199" t="s">
         <v>1190</v>
       </c>
-      <c r="E199" t="s">
+      <c r="E199" s="20" t="s">
         <v>1047</v>
       </c>
       <c r="F199" t="s">
@@ -11802,7 +12040,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="200" spans="1:12">
+    <row r="200" spans="1:12" ht="28.5">
       <c r="A200" t="s">
         <v>1188</v>
       </c>
@@ -11815,7 +12053,7 @@
       <c r="D200" t="s">
         <v>1193</v>
       </c>
-      <c r="E200" t="s">
+      <c r="E200" s="20" t="s">
         <v>1052</v>
       </c>
       <c r="F200" t="s">
@@ -11840,7 +12078,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="201" spans="1:12">
+    <row r="201" spans="1:12" ht="28.5">
       <c r="A201" t="s">
         <v>1188</v>
       </c>
@@ -11853,7 +12091,7 @@
       <c r="D201" t="s">
         <v>1194</v>
       </c>
-      <c r="E201" t="s">
+      <c r="E201" s="20" t="s">
         <v>1057</v>
       </c>
       <c r="F201" t="s">
@@ -11878,7 +12116,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="202" spans="1:12">
+    <row r="202" spans="1:12" ht="42.75">
       <c r="A202" t="s">
         <v>1188</v>
       </c>
@@ -11891,7 +12129,7 @@
       <c r="D202" t="s">
         <v>1191</v>
       </c>
-      <c r="E202" t="s">
+      <c r="E202" s="20" t="s">
         <v>1062</v>
       </c>
       <c r="F202" t="s">
@@ -11929,7 +12167,7 @@
       <c r="D203" t="s">
         <v>1190</v>
       </c>
-      <c r="E203" t="s">
+      <c r="E203" s="20" t="s">
         <v>1067</v>
       </c>
       <c r="F203" t="s">
@@ -11954,7 +12192,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="204" spans="1:12">
+    <row r="204" spans="1:12" ht="57">
       <c r="A204" t="s">
         <v>1188</v>
       </c>
@@ -11967,7 +12205,7 @@
       <c r="D204" t="s">
         <v>1190</v>
       </c>
-      <c r="E204" t="s">
+      <c r="E204" s="20" t="s">
         <v>1072</v>
       </c>
       <c r="F204" t="s">
@@ -12005,7 +12243,7 @@
       <c r="D205" t="s">
         <v>1190</v>
       </c>
-      <c r="E205" t="s">
+      <c r="E205" s="20" t="s">
         <v>1077</v>
       </c>
       <c r="F205" t="s">
@@ -12030,7 +12268,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="206" spans="1:12">
+    <row r="206" spans="1:12" ht="42.75">
       <c r="A206" t="s">
         <v>1188</v>
       </c>
@@ -12043,7 +12281,7 @@
       <c r="D206" t="s">
         <v>1193</v>
       </c>
-      <c r="E206" t="s">
+      <c r="E206" s="20" t="s">
         <v>1082</v>
       </c>
       <c r="F206" t="s">
@@ -12081,7 +12319,7 @@
       <c r="D207" t="s">
         <v>1192</v>
       </c>
-      <c r="E207" t="s">
+      <c r="E207" s="20" t="s">
         <v>1087</v>
       </c>
       <c r="F207" t="s">
@@ -12106,7 +12344,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="208" spans="1:12">
+    <row r="208" spans="1:12" ht="28.5">
       <c r="A208" t="s">
         <v>1188</v>
       </c>
@@ -12119,7 +12357,7 @@
       <c r="D208" t="s">
         <v>1193</v>
       </c>
-      <c r="E208" t="s">
+      <c r="E208" s="20" t="s">
         <v>1092</v>
       </c>
       <c r="F208" t="s">
@@ -12144,7 +12382,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="209" spans="1:12">
+    <row r="209" spans="1:12" ht="42.75">
       <c r="A209" t="s">
         <v>1188</v>
       </c>
@@ -12157,7 +12395,7 @@
       <c r="D209" t="s">
         <v>1190</v>
       </c>
-      <c r="E209" t="s">
+      <c r="E209" s="20" t="s">
         <v>1097</v>
       </c>
       <c r="F209" t="s">
@@ -12182,9 +12420,519 @@
         <v>104</v>
       </c>
     </row>
+    <row r="210" spans="1:12">
+      <c r="A210" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B210" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C210" s="6">
+        <v>209</v>
+      </c>
+      <c r="D210" s="17" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E210" s="19" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F210" s="17" t="s">
+        <v>1198</v>
+      </c>
+      <c r="G210" s="17" t="s">
+        <v>1199</v>
+      </c>
+      <c r="H210" s="17" t="s">
+        <v>1200</v>
+      </c>
+      <c r="I210" s="17" t="s">
+        <v>1201</v>
+      </c>
+      <c r="J210" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="K210" s="17"/>
+      <c r="L210" s="18"/>
+    </row>
+    <row r="211" spans="1:12">
+      <c r="A211" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B211" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C211" s="6">
+        <v>210</v>
+      </c>
+      <c r="D211" s="17" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E211" s="19" t="s">
+        <v>1202</v>
+      </c>
+      <c r="F211" s="17" t="s">
+        <v>1203</v>
+      </c>
+      <c r="G211" s="17" t="s">
+        <v>750</v>
+      </c>
+      <c r="H211" s="17" t="s">
+        <v>1204</v>
+      </c>
+      <c r="I211" s="17" t="s">
+        <v>1205</v>
+      </c>
+      <c r="J211" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K211" s="17"/>
+      <c r="L211" s="18"/>
+    </row>
+    <row r="212" spans="1:12" ht="42.75">
+      <c r="A212" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B212" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C212" s="2">
+        <v>211</v>
+      </c>
+      <c r="D212" s="17" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E212" s="19" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F212" s="19" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G212" s="17" t="s">
+        <v>1208</v>
+      </c>
+      <c r="H212" s="17" t="s">
+        <v>1209</v>
+      </c>
+      <c r="I212" s="17" t="s">
+        <v>1210</v>
+      </c>
+      <c r="J212" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K212" s="17"/>
+      <c r="L212" s="18"/>
+    </row>
+    <row r="213" spans="1:12" ht="28.5">
+      <c r="A213" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B213" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C213" s="6">
+        <v>212</v>
+      </c>
+      <c r="D213" s="17" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E213" s="19" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F213" s="17" t="s">
+        <v>1212</v>
+      </c>
+      <c r="G213" s="17" t="s">
+        <v>1213</v>
+      </c>
+      <c r="H213" s="17" t="s">
+        <v>1214</v>
+      </c>
+      <c r="I213" s="17" t="s">
+        <v>1215</v>
+      </c>
+      <c r="J213" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="K213" s="17"/>
+      <c r="L213" s="18"/>
+    </row>
+    <row r="214" spans="1:12">
+      <c r="A214" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B214" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C214" s="6">
+        <v>213</v>
+      </c>
+      <c r="D214" s="17" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E214" s="19" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F214" s="17" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G214" s="17" t="s">
+        <v>1218</v>
+      </c>
+      <c r="H214" s="17" t="s">
+        <v>1219</v>
+      </c>
+      <c r="I214" s="17" t="s">
+        <v>1220</v>
+      </c>
+      <c r="J214" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="K214" s="17"/>
+      <c r="L214" s="18"/>
+    </row>
+    <row r="215" spans="1:12" ht="28.5">
+      <c r="A215" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B215" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C215" s="2">
+        <v>214</v>
+      </c>
+      <c r="D215" s="17" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E215" s="19" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F215" s="17" t="s">
+        <v>1222</v>
+      </c>
+      <c r="G215" s="17" t="s">
+        <v>1223</v>
+      </c>
+      <c r="H215" s="17" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I215" s="17" t="s">
+        <v>1225</v>
+      </c>
+      <c r="J215" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="K215" s="17"/>
+      <c r="L215" s="18"/>
+    </row>
+    <row r="216" spans="1:12">
+      <c r="A216" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B216" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C216" s="6">
+        <v>215</v>
+      </c>
+      <c r="D216" s="17" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E216" s="19" t="s">
+        <v>1226</v>
+      </c>
+      <c r="F216" s="17" t="s">
+        <v>1227</v>
+      </c>
+      <c r="G216" s="17" t="s">
+        <v>1228</v>
+      </c>
+      <c r="H216" s="17" t="s">
+        <v>1229</v>
+      </c>
+      <c r="I216" s="17" t="s">
+        <v>1230</v>
+      </c>
+      <c r="J216" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="K216" s="17"/>
+      <c r="L216" s="18"/>
+    </row>
+    <row r="217" spans="1:12" ht="28.5">
+      <c r="A217" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B217" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C217" s="6">
+        <v>216</v>
+      </c>
+      <c r="D217" s="17" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E217" s="19" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F217" s="17" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G217" s="17" t="s">
+        <v>1233</v>
+      </c>
+      <c r="H217" s="17" t="s">
+        <v>1234</v>
+      </c>
+      <c r="I217" s="17" t="s">
+        <v>1235</v>
+      </c>
+      <c r="J217" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="K217" s="17"/>
+      <c r="L217" s="18"/>
+    </row>
+    <row r="218" spans="1:12" ht="28.5">
+      <c r="A218" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B218" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C218" s="2">
+        <v>217</v>
+      </c>
+      <c r="D218" s="17" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E218" s="19" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F218" s="17" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G218" s="17" t="s">
+        <v>1238</v>
+      </c>
+      <c r="H218" s="17" t="s">
+        <v>1239</v>
+      </c>
+      <c r="I218" s="17" t="s">
+        <v>1240</v>
+      </c>
+      <c r="J218" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="K218" s="17"/>
+      <c r="L218" s="18"/>
+    </row>
+    <row r="219" spans="1:12" ht="28.5">
+      <c r="A219" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B219" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C219" s="6">
+        <v>218</v>
+      </c>
+      <c r="D219" s="17" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E219" s="19" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F219" s="17" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G219" s="17" t="s">
+        <v>1242</v>
+      </c>
+      <c r="H219" s="17" t="s">
+        <v>1243</v>
+      </c>
+      <c r="I219" s="17" t="s">
+        <v>1238</v>
+      </c>
+      <c r="J219" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="K219" s="17"/>
+      <c r="L219" s="18"/>
+    </row>
+    <row r="220" spans="1:12" ht="28.5">
+      <c r="A220" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B220" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C220" s="6">
+        <v>219</v>
+      </c>
+      <c r="D220" s="17" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E220" s="19" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F220" s="17" t="s">
+        <v>1245</v>
+      </c>
+      <c r="G220" s="17" t="s">
+        <v>1246</v>
+      </c>
+      <c r="H220" s="17" t="s">
+        <v>1247</v>
+      </c>
+      <c r="I220" s="17" t="s">
+        <v>1248</v>
+      </c>
+      <c r="J220" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K220" s="17"/>
+      <c r="L220" s="18"/>
+    </row>
+    <row r="221" spans="1:12" ht="42.75">
+      <c r="A221" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B221" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C221" s="2">
+        <v>220</v>
+      </c>
+      <c r="D221" s="17" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E221" s="19" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F221" s="17" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G221" s="17" t="s">
+        <v>1251</v>
+      </c>
+      <c r="H221" s="17" t="s">
+        <v>1252</v>
+      </c>
+      <c r="I221" s="17" t="s">
+        <v>1253</v>
+      </c>
+      <c r="J221" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K221" s="17"/>
+      <c r="L221" s="18"/>
+    </row>
+    <row r="222" spans="1:12">
+      <c r="A222" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B222" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C222" s="6">
+        <v>221</v>
+      </c>
+      <c r="D222" s="17" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E222" s="19" t="s">
+        <v>1254</v>
+      </c>
+      <c r="F222" s="17" t="s">
+        <v>1255</v>
+      </c>
+      <c r="G222" s="17" t="s">
+        <v>1256</v>
+      </c>
+      <c r="H222" s="17" t="s">
+        <v>1257</v>
+      </c>
+      <c r="I222" s="17" t="s">
+        <v>1258</v>
+      </c>
+      <c r="J222" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="K222" s="17"/>
+      <c r="L222" s="18"/>
+    </row>
+    <row r="223" spans="1:12" ht="28.5">
+      <c r="A223" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B223" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C223" s="6">
+        <v>222</v>
+      </c>
+      <c r="D223" s="17" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E223" s="19" t="s">
+        <v>1259</v>
+      </c>
+      <c r="F223" s="17" t="s">
+        <v>1260</v>
+      </c>
+      <c r="G223" s="17" t="s">
+        <v>1261</v>
+      </c>
+      <c r="H223" s="17" t="s">
+        <v>1262</v>
+      </c>
+      <c r="I223" s="17" t="s">
+        <v>1263</v>
+      </c>
+      <c r="J223" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="K223" s="17"/>
+      <c r="L223" s="18"/>
+    </row>
+    <row r="224" spans="1:12">
+      <c r="A224" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B224" s="17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="C224" s="2">
+        <v>223</v>
+      </c>
+      <c r="D224" s="17" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E224" s="19" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F224" s="17" t="s">
+        <v>1265</v>
+      </c>
+      <c r="G224" s="17" t="s">
+        <v>1266</v>
+      </c>
+      <c r="H224" s="17" t="s">
+        <v>1267</v>
+      </c>
+      <c r="I224" s="17" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J224" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="K224" s="17"/>
+      <c r="L224" s="18"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" sqref="J2:J105" xr:uid="{00000000-0002-0000-0000-000000000000}">
